--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WCORREA\Documents\ISDIN_Shopping_de_precios\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE794A12-FC4F-4385-BEE0-ABACC37DEE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20F8B97-F0C9-4DC9-90C2-06F796E141A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{60233B49-B589-B346-B71C-4D486694C55A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$514</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$581</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2872" uniqueCount="839">
   <si>
     <t>Producto</t>
   </si>
@@ -1938,6 +1938,624 @@
   </si>
   <si>
     <t>https://www.cutis.com.co/isdinceutics-salicylic-renewal-30ml/p</t>
+  </si>
+  <si>
+    <t>Laskin</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/eryfotona-ak-nmsc-spf-99-50ml-flid-isdi?srsltid=AfmBOoqajYIr4FULRRthYuW3-KmIpF-hDl6H6O8RFy5zTySRgE9hLArP</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/essential-cleansing-200ml-oil-base-clean?_pos=1&amp;_sid=520745000&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdin-fotoprotector-pediatrics-gel-cream-isdin%C2%AE?_pos=2&amp;_sid=e94934467&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoprot-invisible-stick-spf50-10g-isdin?_pos=1&amp;_sid=c2b7bf035&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoprot-fusion-water-magic-by-alcaraz?srsltid=AfmBOopqsE8lIBNgc4E1YJQcy5uSJdX7fUy9ph9lqks6Q_F1pLmG-LdD</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoprotec-fusion-gel-sport-spf-50-100ml?_pos=1&amp;_sid=37f59b04f&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotop-fusion-water-col-light-spf50-50ml?_pos=1&amp;_sid=0b71c0477&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotop-fusion-water-col-medium-spf50-50ml?_pos=2&amp;_sid=0b71c0477&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fusion-water-magic-spf-50-isdin%C2%AE?_pos=1&amp;_sid=3207ee7d2&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoprotec-pediatrics-fision-water-50ml?srsltid=AfmBOoqq5j59XYzMFA4VyDGM7JhXPUSsbojYQgxw5oDJVhqCG102ptfw</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoprotector-spf-50-250ml-gel-crema?_pos=1&amp;_sid=4e2804c3b&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/foto-ultra-100-50ml-active-unify-ff?_pos=2&amp;_sid=62a048b95&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/foto-ultra-100-50ml-active-unify-color?_pos=1&amp;_sid=62a048b95&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdin-fotoprotector-magic-repair-50ml</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/reparador-labial-fluid-10-ml-isdin?_pos=1&amp;_sid=1da354c34&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/a-g-e-reverse-day-50ml-cream-isdinceuti?srsltid=AfmBOoqMVJvHzOLWvGqWHaAIZ3w_ivWSYbaV24CoBuJAedpKRuBqw6jj</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/a-g-e-age-reverse-night-50ml-crema-repar?_pos=1&amp;_sid=a24239ed5&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/flavo-c-30ml-serum-isdinceutics?_pos=1&amp;_sid=2a9d540fb&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/hyaluronic-concentrate-30ml-serum-isdinc?_pos=1&amp;_sid=7c34e631e&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/hyaluronic-moisture-normal-cream-50g-isd?_pos=1&amp;_sid=6f9c48e6c&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/k-ox-eyes-15gr-cream-isdinceutics?_pos=2&amp;_sid=80c075cb9&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/melaclear-advanced-serum-30ml-isdinceut?_pos=1&amp;_sid=1deb452d2&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/vital-eyes-15gr-crema-isdinceutics?_pos=1&amp;_sid=34fa6f106&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/retinal-intense-50ml-serum-isdinceutics?_pos=1&amp;_sid=c083a09f4&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdin-fotoprotector-pediatrics-stick-20g?srsltid=AfmBOopkdGtyZSzBBb4fhL-ujgjUKvcM_z_O1P9vAdCC6QeU4NehDFZ1</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoprotect-uv-mineral-brush-spf-50-2gr?_pos=1&amp;_sid=ff2decddf&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoprotector-compact-light-spf-50-10gr?srsltid=AfmBOoozsBArCJGklZqa3JjOV5j_okaT2Pd_44UngFzBuvvTzOMMtBkp</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoprotector-fusion-fluid-mineral-spf50?_pos=5&amp;_sid=3ce86d8ab&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotop-fusion-water-col-bronz-spf50-50ml?_pos=3&amp;_sid=b5ba19b41&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoprot-fusion-water-urban-spf-30-50ml?_pos=2&amp;_sid=30da8fe70&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoprotector-fusion-water-magic-gl-50ml?_pos=1&amp;_sid=53a36d7c4&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoprot-transparent-spf-50-250ml-spray?srsltid=AfmBOorqPQXV8gEhZSigizJZjpgmvaqDYGXlPFOHk8CUk83zVROCSD_z</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoultra-redness-spf50-x-50ml-isdin?_pos=1&amp;_sid=fdc18e217&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/foto-ultra-100-50ml-spot-prevent-spf-51?_pos=1&amp;_sid=b02e06879&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/fotoultra-100-spot-prevent-color-spf50?_pos=2&amp;_sid=d3d08e4c5&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdin-fotoprotec-magic-repair-color-50ml?srsltid=AfmBOooc2NsVaMWEeqekNkNRNdUiEVWoH-A9Es6_oR4CAYKdaQkwYdhT</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/ultra-suave-daylisdin-400ml-shampoo?_pos=1&amp;_sid=444677080&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/germisdin-500ml-gel-de-bano-syndet?_pos=1&amp;_sid=c051e5e73&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/anticaida-lambdapil-shampoo-200ml?_pos=1&amp;_sid=94972668f&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/nutradeica-ds-50ml-gel-crema-facial?_pos=1&amp;_sid=97248bac2&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/anticaspa-grasa-nutradeica-200ml-shampo?_pos=1&amp;_sid=a3461daa4&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isd-crema-emol-pro-amp-nutratopic-50ml?_pos=1&amp;_sid=6edad3634&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/nutratopic-pro-amp-400ml-gel-de-bano-emu?_pos=1&amp;_sid=9a8505bb4&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/nutratopic-pro-amp-400ml-locion-emolient?_pos=1&amp;_psq=NUTRATOPIC+LOTION+400ML&amp;_ss=e&amp;_v=1.0</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/baby-naturals-nutraisdin-pomada-de-panal?srsltid=AfmBOoq-LgO2bhHaMBsEnEwtJemaj7DOIo9wx9gn0oKJ7iEgQw0DYrar</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/baby-naturals-nutraisdin-gel-champu-400m?_pos=1&amp;_sid=afaa20697&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/reparador-labial-stick-rojo-4g?_pos=1&amp;_sid=dfdfa9bd2&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/reparador-labial-stick-rosa?_pos=2&amp;_sid=6f945075d&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/reparador-labial-stick-granate-4g?_pos=1&amp;_sid=0ff523dbc&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/reparador-labial-acido-hialuronico-4gr?_pos=1&amp;_sid=4fe719064&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/si-nails-2-5ml-fortalecedor-de-unas?_pos=1&amp;_sid=d8d752101&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/niogermox-3-3ml-solucion-topica-una?_pos=1&amp;_sid=a8a322ba5&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/micellar-solution-4-en-1-400ml-isdin?_pos=1&amp;_sid=613657c30&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/ureadin-bath-gel-hydrating-400ml-isdin?_pos=1&amp;_sid=07b0ba64e&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/ureadin-podos-75ml-gel-oil-hidrat-isd?_pos=1&amp;_sid=ea576f988&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/ureadin-ultra-10-400ml-locion-plus-repar?_pos=1&amp;_sid=ae74f5a8c&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/ureadin-lotion-10-hidrat-isdin-1000ml?_pos=1&amp;_sid=834e38f88&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/ureadin-ultra-20-100ml-crema-anti-rugosi?_pos=1&amp;_sid=f5978cf5e&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/ureadin-manos-plus-50ml-crema-repair?_pos=1&amp;_sid=093618c0b&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/woman-reafirmante-firming-200ml?_pos=1&amp;_sid=281775c23&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdinceutics-hyaluronic-eyes-15g?_pos=1&amp;_sid=1b300de73&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/hyaluronic-moisture-oily-y-cobination-cr?_pos=1&amp;_sid=133e64fc6&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdinceutics-hyaluronic-booster-x-10-amp?_pos=1&amp;_sid=472f0c0a1&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdinceutics-essential-purifier-150-ml?_pos=1&amp;_sid=85546c272&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdinceutics-essential-scrub-100-g?_pos=1&amp;_sid=aee61eb38&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/search?options%5Bunavailable_products%5D=last&amp;options%5Bprefix%5D=last&amp;options%5Bfields%5D=title%2Cvendor%2Cproduct_type%2Cvariants.title&amp;q=ISDINCEUTICS+RETINAL+EYES+20ML</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdinceutics-salicylic-renewal-serum30ml?_pos=1&amp;_sid=67f169499&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>Falabella</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/72971956/Hidratante-facial-Isdin-Para-Piel-Normal-50-/72971956</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682163/Hidratante-Corporal-Ureadin-Utra-10-Isdin-para-Piel-seca-400-ml/12682163</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682128/Bloqueador-Solar-Eryfotona-AK-NMSC-Isdin-para-Piel-Sensible-50-ml/12682128</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682132/Bloqueador-Solar-Fusion-Water-con-Color-Isdin-para-Piel-Mixta-50-ml/12682132</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/29086847/Bloqueador-Solar-Foto-Ultra-100-Active-Unify-Isdin-para-Todo-tipo-de-piel-50-ml/29086847</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/29086848/Bloqueador-Solar-Fotoultra-Active-Unify-Color-50-ml-Isdin-para-Todo-tipo-de-piel-50-ml/29086848</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73148089/Protector-solar-FUSION-WATER-MAGIC-REPAIR-SPF50-50ML-Crema-ISDIN-Crema-50ml/73148089</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com/falabella-cl/product/80004010/Fotoprotector-Fusion-Water-Magic-Pediatrics-Spf-50-50Ml-Isdin/80004010</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/31652096/Serum-Isdinceutics-Rejuvenate-Flavo-C-Isdin-para-Todo-tipo-de-piel-30-ml/31652096</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/29073409/Tratamiento-Antiedad-Anti-arrugas-para-Rostro-Age-Reverse-Day-Isdin-50-ml/29073409</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682179/Contorno-de-Ojos-K-Ox-Eyes-Isdin-para-Piel-Normal-15-ml/12682179</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682154/Hidratante-Facial-Nutradeica-DS-Isdin-para-Piel-Grasa-50-ml/12682154</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73133689/Bloqueador-Fp-Invisible-Stick-Spf50-10G-en-barra-Isdin-10-gr/73133689</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682170/Tratamiento-antiedad-Age-Reverse-Night-Noche-Isdin-para-Piel-Normal-50-ml/12682170</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73259531/Protector-solar-Fotoprotector-Fusion-Water-Magic-By-Alcaraz-Emulsion-Isdin-50-ml/73259531</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/20233919/Hidratante-Facial-Isdinceutics-Hyaluronic-Concentrate-Isdin-para-Todo-tipo-de-piel-30-ml/20233919</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/19508501/Contorno-de-Ojos-Rejuvenate-Vital-Eyes-Noche-Isdin-para-Todo-tipo-de-piel-15-ml/19508501</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73051045/Protector-solar-Isdin-FotoUltra-100-Fotoprotecto-Spot-Prevent-Color-SPF-50+-Crema-ISDIN-Crema-50ml/73051045</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73148088/Protector-solar-Fusion-Water-MAgic-REPAIR-COLOR-SPF50-50ML-Crema-ISDIN-Crema-50ml/73148088</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73265847/Fotoprotector-ISDIN-Fusion-Gel-SPORT-SPF50-Protector-solar-corporal-para-el-deporte-Isdin-para-Todo-tipo-de-piel-100-ml/73265847</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73129676/Bloqueador-FP-GEL-CREAM-SPF50-250ML-Crema-ISDIN-Gel-250ml/73129676</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/37776295/Bloqueador-Solar-Fusion-Water-Color-Light-Isdin-para-Todo-tipo-de-piel-50-ml/37776295</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/46172384/Limpiador-Essential-Cleansing-Isdin-para-Todo-tipo-de-piel-200-ml/46172384</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/63668172/Bloqueador-Corporal-Adultos-Wet-Skin-Transparent-en-Spray-Isdin-250-ml/63668172</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/63668173/Tratamiento-antiedad-Noche-Isdinceutics-Retinal-Intense-Isdin-para-Todo-tipo-de-piel-50-ml/63668173</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/72757444/Bloqueador-Liquido-Fusion-Water-Magic-SPF50-ISDIN-50-ml/72757444</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/72914712/Locion-Babynaturals-Body-Lotion-Isdin-para-Bebes400-ml/72914712</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/72914713/Jabon-Babynaturals-Gel-Shampoo-Isdin-para-Bebes-400-ml/72914713</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/72914711/Crema-Babynaturals-Pomada-Isdin-para-Bebes-100-ml/72914711</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73233722/Suero-MELACLEAR-ADVANCED-SERUM-DESPIGMANTANTE-Isdin-para-Todo-tipo-de-piel-30-ml/73233722</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73390088/Protector-solar-Fotoprotector-Pediatrics-Stick-en-Barra-Isdin-20-Gr/73390088</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/122877665/Fotoprotector-Isdin-Uv-Mineral-Brush-Polvo-50spf-X-2g/122877666</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/122787136/Polvo-Compacto-Isdin-Fotoprotector-Spf50-Arena-10g/122787137</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/37776294/Bloqueador-Solar-Fusion-Water-Color-Bronze-Isdin-para-Todo-tipo-de-piel-50-ml/37776294</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682133/Bloqueador-Solar-Fusion-Water-Urban-Isdin-para-Piel-Mixta-50-ml/12682133</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73390092/Protector-solar-Fotoprotector-Fusion-Water-Magic-Glow-en-Crema-Isdin-50-ml/73390092</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/122877557/Fotoprotector-Isdin-Hydrolotion-+-50spf-200ml/122877558</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/123173276/Fotoprotector-Isdin-Hydro-Oil-SPF-30-Proteccion-Alta-X-200-Ml/123173278</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73531835/bloqueador-fp-fw-body-glow-spf-30-en-crema-isdin-200-ml/73531835</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/search?Ntt=FU+SPOT+PREVENT+SPF50+50ML</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73051046/Fotoprotector-para-labios-FP-LIPSTICK-SPF-50+-4G-Barra-ISDIN-4-g/73051046</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682168/Limpiador-Germisdin-Gel-de-Bano-Isdin-para-Piel-Normal-500-ml/12682168</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/125963015/locion-isdin-lambdapil-anticaida-x-125ml/125963016</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682156/Hidratante-Facial-Nutratopic-Pro-AMP-Emoliente-Isdin-para-Todo-tipo-de-piel-50-ml/12682156</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682157/Limpiador-Nutratopic-de-Bano-Isdin-para-Piel-Sensible-400-ml/12682157</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682158/Hidratante-Corporal-Nutratopic-Pro-AMP-Isdin-para-Piel-Sensible-400-ml/12682158</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/prod13940005/Tratamiento-Labios-Reparador-Stick-Isdin-4-Gr/73390089</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/prod13940005/Tratamiento-Labios-Reparador-Stick-Isdin-4-Gr/73390090</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/prod13940005/Tratamiento-Labios-Reparador-Stick-Isdin-4-Gr/73390091</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682153/Protector-para-Labios-Isdin-para-Todo-tipo-de-piel-4-g/12682153</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/72970532/Balsamo-Reparador-Labial-Isdin-para-Todo-tipo-de-piel-30-ml/72970532</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682150/Tratamiento-para-Unas-Si-Nails-Isdin-para-Todo-tipo-de-piel-2.5-ml/12682150</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682151/Agua-Micelar-Solution-4-en-1-Isdin-para-Piel-Normal-400-ml/12682151</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682152/Agua-Micelar-Solution-4-en-1-Isdin-para-Piel-Normal-100-ml/12682152</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682160/Tratamiento-para-Pies-Ureadin-Podos-Isdin-para-Piel-Normal-75-ml/12682160</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/12682161/Tratamiento-para-Manos-Ureadin-Plus-Repair-Isdin-para-Piel-Normal-50-ml/12682161</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/46172382/Reafirmante-para-Cuerpo-Isdin-250-ml/46172382</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73398122/Contorno-de-ojos-Ceutics-Hyaluronic-Eyes-Isdin-para-Todo-tipo-de-piel-15-gr/73398122</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/72971958/Hidratante-facial-Isdin-Para-Piel-Mixta-50-/72971958</t>
+  </si>
+  <si>
+    <t>Pasteur</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-faciales-eryfotona-ak-nmsc-fluido-spf-99-caja-50-ml-867250/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-hidratantes-isdin-eryfotona-night-emulsion-frasco-50-ml-867039/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-faciales-isdin-invisible-stick-fotoprotector-spf-50-frasco-10-g-867036/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-infantiles-isdin-pediatrics-stick-fotoprotector-barra-20-g-867041/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-maquillaje-dermoprotector-isdin-uv-mineral-brush-spf-50--tubo-2-g-867293/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-faciales-isdin-fusion-fluido-spf-50--caja-50-ml-045228/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-faciales-isdin-fotop--fusion-mineral-fluido-frasco-50-ml-867263/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-faciales-isdin-fotoprotector-fusion-water-magic-by-alcaraz-frasco-50-ml-867038/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-faciales-isdin-fusion-water-magic-fotoprotector-spf-50-frasco-50-ml-867015/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-con-color-isdin-fusion-water-magic-spf-50-color-medium-frasco-50-ml-867001/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-con-color-isdin-fusion-water-magic-spf-50-color-bronze-caja-50-ml-867003/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-con-color-isdin-fusion-water-magic-spf-50-color-light-frasco-50-ml-867002/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-faciales-isdin-fusion-water-magic-urban-spf-30-frasco-50-ml-867268/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-faciales-isdin-fotoprotector-fusion-water-magic-glow-frasco-50-ml-867045/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-infantiles-isdin-fusion-water-magic-spf-50-pediatric-frasco-50-ml-867215/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-corporales-isdin-fotoprotector-gel-crema-spf-50--tubo-250-ml-045222/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-infantiles-isdin-pediatrics-gel-crema-fotoprotector-spf-50-tubo-250-ml-867014/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-corporales-fotoprotec-isdin-hydro-lotion-spf-50-frasco-200-ml-867269/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-corporales-fotoprotector-hydrooil-spf-30-200-ml-867285/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-corporales-isdin-fotoprotector-fusion-gel-sport-spf-50-frasco-100-ml-867037/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-corporales-isdin-fotoprotector-transparen-spray-wet-skin-spf-50-frasco-250-ml-867009/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-corporales-isdin-fotoprotector-body-glow-spf-30-tubo-200-ml-867048/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-faciales-isdin-fotoultra-redness-spf-50-frasco-50-ml-867032/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-faciales-isdin-fotoultra-100-fluido-spf-50--active-unify-caja-50-ml-867282/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-con-color-isdin-fotoultra-100-color-spf-50--active-unify-caja-50-ml-867287/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-faciales-fotoultra-100-spot-prevent-fluido-caja-50-ml-867281/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-con-color-isdin-foto-ultra-100-spot-prev-spf-50--color-frasco-50-ml-867027/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-faciales-fotoultra-age-repair-water-spf-50-caja-50-ml-867254/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-maquillaje-dermoprotector-con-color-isdin-fotoprotector-fusion-water-magic-repair-color-frasco-50-ml-867035/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-cuidado-de-labios-isdin-protector-labial-spf-50-barra-4-g-867259/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-cuidado-de-labios-isdin-protector-labial-hv-spf-30-barra-4-g-867260/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-cuidado-de-labios-isdin-protector-labial-spf-30-barra-4-g-867261/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-otros-tratamientos-shampoo-y-acondicionador-isdin-dayl-shampoo-ultra-suave-frasco-400-ml-867271/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-jabones-y-limpiadores-germisdin-gel-bano-frasco-500-ml-867265/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-protector-cutaneo-isdin-cicapost-crema-tubo-50-g-867047/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-otros-tratamientos-anticaida-isdin-lambdapil-champu-anticaida-frasco-200-ml-867272/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-otros-tratamientos-anticaida-isdin-lambdapil-locion-anticaida-melatonin-spray-100-ml-867046/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-hidratantes-isdin-nutradeica-ds-gel-crema-caja-50-ml-867255/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-otros-tratamientos-anticaspa-isdin-nutradeica-champu-anticaspa-grasa-frasco-200-ml-867273/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-hidratantes-nutratopic-pro-amp-piel-react-crema-caja-50-ml-867310/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-jabones-y-limpiadores-nutratopic-pro-amp-gel-bano-frasco-400-ml-867312/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-hidratantes-nutratopic-pro-amp-emoliente-locion-frasco-400-ml-867311/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-proteccion-solar-hidratantes-isdin-baby-naturals-nutraisdin-pomada-del-panal-tubo-100-ml-867020/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-proteccion-solar-hidratantes-isdin-babynaturals-body-lotion-frasco-400-ml-867021/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-proteccion-solar-bano-isdin-baby-naturals-nutraisdin-gel-champu-frasco-400-ml-867019/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-cuidado-de-labios-isdin-reparador-labial-rojo-barra-4-g-867043/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-cuidado-de-labios-isdin-reparador-labial-rosa-barra-4-g-867044/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-cuidado-de-labios-isdin-reparador-labial-granate-barra-4-g-867042/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-cuidado-de-labios-isdin-reparador-labial-barra-4-g-867262/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-cuidado-de-labios-isdin-reparador-labial-fluido-tubo-10-ml-867010/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-cuidado-de-labios-isdin-reparador-balsamo-labial-10-ml-867022/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-otros-tratamientos-ciudado-de-las-unas-isdin-si-nails-caja-2-5-ml-867264/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-medicamentos-y-tratamientos--niogermox-solucion-topica-8--caja-3-3-ml-867253/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-limpiadores-y-desmaquillantes-isdin-micellar-solution-frasco-400-ml-867251/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-limpiadores-y-desmaquillantes-isdin-micellar-solution-frasco-100-ml-867256/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-jabones-y-limpiadores-ureadin-bath-gel-frasco-400-ml-867401/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-hidratantes-ureadin-podos-pies-secos-caja-75-ml-045819/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-hidratantes-ureadin-ultra-10-locion-caja-200-ml-867212/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-hidratantes-ureadin-ultra-10-locion-caja-400-ml-867213/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-hidratantes-isdin-ureadin-lotion-10-frasco-1000-ml-867011/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-hidratantes-ureadin-ultra-20-crema-caja-100-ml-867214/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-hidratantes-ureadin-ultra-30-exfoliante-crema-caja-50-ml-045827/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-hidratantes-ureadin-manos-plus-repair-crema-tubo-50-ml-867267/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-reductores-y-reafirmantes-isdin-woman-crema-reafirmante-tubo-200-ml-867005/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-hidratantes-isdin-woman-crema-anti-estrias-tubo-250-ml-867004/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-reductores-y-reafirmantes-cuidado-intimo-isdin-woman-higiene-intima-gel-frasco-200-ml-867028/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-mascarillas-y-serum-isdinceutics-flavo-c-serum-caja-30-ml-867258/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-contorno-de-ojos-isdinceutics-k-ox-eyes-crema-caja-15-g-867257/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-contorno-de-ojos-isdinceutics-vital-eyes-caja-15-g-867280/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-contorno-de-ojos-isdinceutics-hyaluronic-eyes-gel-pote-15-g-867040/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-mascarillas-y-serum-isdin-hyaluronic-concentrate-serum-frasco-30-ml-867276/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-hidratantes-isdinceutics-hyaluronic-moisture-normal-to-dry-skin-caja-50-g-867025/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-hidratantes-isdinceutics-hyaluronic-moisture-normal-to-dry-skin-refill-caja-50-g-867026/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-hidratantes-isdinceutics-hyaluronic-moisture-oily---combination-skin-caja-50-g-867023/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-hidratantes-isdinceutics-hyaluronic-moisture-oily---combination-skin-refill-caja-50-g-867024/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-limpiadores-y-desmaquillantes-isdinceutics-essential-cleansing-aceite-limpiador-frasco-200-ml-867008/p</t>
+  </si>
+  <si>
+    <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-mascarillas-y-serum-isdinceutics-retinal-intense-serum-facial-frasco-50-ml-867029/p</t>
   </si>
 </sst>
 </file>
@@ -2473,13 +3091,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C4ECE9E-4A28-6340-B936-CE442F4057E5}">
-  <dimension ref="A1:N514"/>
+  <dimension ref="A1:N718"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="62.33203125" customWidth="1"/>
     <col min="2" max="2" width="29.5" customWidth="1"/>
     <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="255.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
@@ -10255,9 +10873,2871 @@
         <v>632</v>
       </c>
     </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A515" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B515" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C515" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D515" s="3" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A516" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B516" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C516" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D516" s="5" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A517" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B517" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C517" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D517" s="5" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A518" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B518" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C518" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D518" s="5" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A519" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B519" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C519" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D519" s="5" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A520" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B520" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C520" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D520" s="5" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A521" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B521" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C521" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D521" s="5" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A522" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B522" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C522" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D522" s="5" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A523" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B523" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C523" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D523" s="5" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A524" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B524" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C524" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D524" s="5" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A525" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B525" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C525" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D525" s="5" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A526" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B526" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C526" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D526" s="5" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A527" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B527" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D527" s="5" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A528" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B528" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C528" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D528" s="5" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A529" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B529" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C529" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D529" s="3" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A530" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B530" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C530" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D530" s="5" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A531" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B531" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D531" s="5" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A532" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B532" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C532" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D532" s="5" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A533" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B533" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C533" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D533" s="5" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A534" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B534" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C534" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D534" s="5" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A535" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B535" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D535" s="5" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A536" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B536" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C536" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D536" s="5" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A537" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B537" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C537" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D537" s="5" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A538" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B538" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C538" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D538" s="5" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A539" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B539" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C539" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D539" s="3" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A540" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B540" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C540" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D540" s="3" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A541" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B541" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C541" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D541" s="3" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A542" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B542" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C542" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D542" s="3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A543" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B543" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C543" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D543" s="3" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A544" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B544" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C544" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D544" s="3" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A545" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B545" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C545" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D545" s="3" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A546" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B546" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C546" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D546" s="3" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A547" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B547" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C547" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D547" s="3" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A548" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B548" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C548" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D548" s="3" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A549" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B549" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C549" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D549" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A550" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B550" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C550" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D550" s="3" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A551" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B551" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C551" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D551" s="3" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A552" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B552" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C552" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D552" s="3" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A553" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B553" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C553" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D553" s="3" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A554" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B554" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C554" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D554" s="3" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A555" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B555" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C555" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D555" s="3" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A556" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B556" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C556" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D556" s="3" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A557" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B557" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C557" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D557" s="3" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A558" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B558" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C558" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D558" s="3" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A559" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B559" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C559" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D559" s="3" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A560" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B560" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C560" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D560" s="3" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A561" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B561" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C561" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D561" s="3" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A562" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B562" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C562" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D562" s="3" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A563" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B563" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C563" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D563" s="3" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A564" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B564" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C564" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D564" s="3" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A565" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B565" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C565" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D565" s="3" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A566" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B566" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C566" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D566" s="3" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A567" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B567" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C567" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D567" s="3" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A568" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B568" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C568" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D568" s="3" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A569" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B569" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C569" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D569" s="3" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A570" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B570" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C570" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D570" s="3" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A571" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B571" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C571" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D571" s="3" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A572" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B572" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C572" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D572" s="3" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A573" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B573" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C573" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D573" s="3" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A574" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B574" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C574" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D574" s="3" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A575" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B575" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C575" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D575" s="3" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A576" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B576" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C576" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D576" s="3" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A577" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B577" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C577" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D577" s="3" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A578" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B578" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C578" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D578" s="3" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A579" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B579" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C579" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D579" s="3" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A580" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B580" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C580" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D580" s="3" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A581" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B581" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C581" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="D581" s="3" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A582" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B582" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C582" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D582" s="5" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A583" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B583" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C583" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D583" s="3" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A584" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B584" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C584" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D584" s="3" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A585" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B585" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C585" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D585" s="5" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A586" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B586" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C586" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D586" s="5" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A587" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B587" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C587" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D587" s="5" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A588" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B588" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C588" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D588" s="5" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A589" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B589" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C589" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D589" s="5" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A590" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B590" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C590" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D590" s="5" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A591" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B591" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C591" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D591" s="5" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A592" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B592" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C592" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D592" s="5" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A593" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B593" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C593" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D593" s="3" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A594" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B594" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C594" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D594" s="5" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A595" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B595" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C595" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D595" s="5" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A596" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B596" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C596" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D596" s="5" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A597" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B597" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C597" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D597" s="5" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A598" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B598" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C598" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D598" s="5" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A599" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B599" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C599" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D599" s="5" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A600" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B600" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C600" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D600" s="5" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A601" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B601" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C601" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D601" s="5" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A602" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B602" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C602" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D602" s="5" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A603" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B603" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C603" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D603" s="5" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A604" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B604" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C604" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D604" s="5" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A605" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B605" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C605" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D605" s="5" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A606" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B606" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C606" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D606" s="5" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A607" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B607" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C607" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D607" s="29" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A608" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B608" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C608" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D608" s="5" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A609" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B609" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C609" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D609" s="3" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A610" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B610" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C610" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D610" s="3" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A611" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B611" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C611" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D611" s="5" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A612" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B612" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C612" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D612" s="3" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A613" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B613" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C613" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D613" s="3" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A614" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B614" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C614" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D614" s="3" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A615" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B615" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C615" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D615" s="3" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A616" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B616" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C616" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D616" s="3" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A617" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B617" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C617" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D617" s="3" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A618" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B618" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C618" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D618" s="3" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A619" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B619" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C619" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D619" s="3" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A620" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B620" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C620" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D620" s="3" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A621" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B621" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C621" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D621" s="3" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A622" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B622" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C622" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D622" s="3" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A623" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B623" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C623" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D623" s="3" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A624" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B624" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C624" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D624" s="3" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A625" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B625" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C625" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D625" s="3" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="626" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A626" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B626" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C626" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D626" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="627" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A627" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B627" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C627" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D627" s="5" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="628" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A628" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B628" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C628" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D628" s="5" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="629" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A629" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B629" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C629" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D629" s="5" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="630" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A630" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B630" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C630" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D630" s="5" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="631" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A631" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B631" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C631" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D631" s="5" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="632" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A632" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B632" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C632" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D632" s="5" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="633" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A633" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B633" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C633" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D633" s="5" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="634" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A634" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B634" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C634" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D634" s="5" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="635" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A635" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B635" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C635" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D635" s="5" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="636" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A636" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B636" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C636" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D636" s="5" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="637" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A637" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B637" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C637" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D637" s="5" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="638" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A638" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B638" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C638" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D638" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="E638" s="3"/>
+      <c r="F638" s="5"/>
+      <c r="G638" s="3"/>
+    </row>
+    <row r="639" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A639" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B639" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C639" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D639" s="5" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="640" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A640" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B640" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C640" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D640" s="5" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A641" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B641" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C641" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D641" s="5" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A642" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B642" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C642" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D642" s="5" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A643" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B643" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C643" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D643" s="5" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A644" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B644" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C644" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D644" s="5" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A645" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B645" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C645" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D645" s="5" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A646" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B646" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C646" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D646" s="5" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A647" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B647" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C647" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D647" s="5" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A648" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B648" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C648" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D648" s="5" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A649" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B649" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C649" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D649" s="5" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A650" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B650" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C650" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D650" s="5" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A651" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B651" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C651" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D651" s="5" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A652" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B652" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C652" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D652" s="5" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A653" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C653" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D653" s="5" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A654" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B654" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D654" s="5" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A655" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B655" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C655" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D655" s="5" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A656" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B656" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D656" s="5" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A657" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B657" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C657" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D657" s="5" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A658" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B658" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D658" s="5" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A659" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B659" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C659" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D659" s="5" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A660" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B660" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D660" s="5" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A661" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B661" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C661" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D661" s="5" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A662" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B662" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C662" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D662" s="5" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A663" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B663" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C663" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D663" s="5" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A664" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B664" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D664" s="5" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A665" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B665" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C665" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D665" s="5" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A666" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B666" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D666" s="5" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A667" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B667" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C667" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D667" s="5" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A668" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B668" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D668" s="5" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A669" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B669" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D669" s="5" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A670" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B670" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D670" s="5" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A671" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B671" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D671" s="5" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A672" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B672" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D672" s="5" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A673" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B673" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C673" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D673" s="5" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A674" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B674" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C674" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D674" s="5" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A675" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B675" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C675" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D675" s="5" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A676" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B676" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C676" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D676" s="5" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A677" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B677" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C677" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D677" s="5" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A678" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B678" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C678" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D678" s="5" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A679" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B679" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C679" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D679" s="5" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A680" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B680" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C680" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D680" s="5" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A681" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B681" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C681" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D681" s="5" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A682" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B682" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C682" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D682" s="5" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A683" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B683" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C683" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D683" s="5" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A684" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B684" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C684" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D684" s="5" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A685" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B685" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C685" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D685" s="5" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A686" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B686" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C686" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D686" s="5" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A687" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B687" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C687" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D687" s="5" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A688" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B688" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C688" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D688" s="5" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A689" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B689" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C689" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D689" s="5" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A690" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B690" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C690" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D690" s="5" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A691" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B691" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C691" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D691" s="5" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A692" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B692" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C692" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D692" s="5" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A693" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B693" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C693" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D693" s="5" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A694" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B694" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C694" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D694" s="5" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A695" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B695" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C695" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D695" s="5" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A696" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B696" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C696" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D696" s="5" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A697" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B697" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C697" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D697" s="5" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A698" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B698" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C698" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D698" s="5" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A699" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B699" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C699" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D699" s="5" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A700" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B700" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C700" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D700" s="5" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A701" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B701" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C701" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D701" s="5" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A702" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B702" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C702" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D702" s="5" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A703" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B703" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C703" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D703" s="5" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A704" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B704" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C704" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D704" s="5" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A705" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B705" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C705" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D705" s="5" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A706" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B706" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C706" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D706" s="5" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A707" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B707" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C707" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D707" s="5" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A708" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B708" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C708" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D708" s="5" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A709" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B709" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C709" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D709" s="5" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A710" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B710" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C710" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D710" s="5" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A711" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B711" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C711" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D711" s="5" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A712" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B712" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C712" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D712" s="5" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A713" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B713" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C713" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D713" s="5" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A714" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B714" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C714" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D714" s="5" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A715" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B715" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C715" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D715" s="5" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A716" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B716" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C716" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D716" s="5" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A717" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B717" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C717" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D717" s="5" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A718" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B718" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C718" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="D718" s="5" t="s">
+        <v>838</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D514" xr:uid="{2C4ECE9E-4A28-6340-B936-CE442F4057E5}"/>
+  <autoFilter ref="A1:D581" xr:uid="{2C4ECE9E-4A28-6340-B936-CE442F4057E5}"/>
   <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D704" r:id="rId1" xr:uid="{C4A764D9-65E4-467B-BC7B-5C3E51C52CDA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WCORREA\Documents\ISDIN_Shopping_de_precios\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20F8B97-F0C9-4DC9-90C2-06F796E141A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1679A06-45CF-4985-81E2-48B5FD34E6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{60233B49-B589-B346-B71C-4D486694C55A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$581</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$718</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -752,9 +752,6 @@
     <t>FP UV MINERAL BRUSH 50+ 2G</t>
   </si>
   <si>
-    <t>https://www.google.com/search?q=https://www.bellapiel.com.co/fotoprotector-isdin-uv-mineral-brush-5599/p</t>
-  </si>
-  <si>
     <t>FOTOPROTECTOR COMPACT LIGHT</t>
   </si>
   <si>
@@ -884,9 +881,6 @@
     <t>LAMBDAPIL HAIR LOSS MELATONIN LOT 100ML</t>
   </si>
   <si>
-    <t>https://www.bellapiel.com.co/isdin-lambdapil-locion-anticaida-</t>
-  </si>
-  <si>
     <t>NUTRADEICA OILY DRANDRUFF SHAMPOO 200ML</t>
   </si>
   <si>
@@ -2556,6 +2550,12 @@
   </si>
   <si>
     <t>https://www.farmaciaspasteur.com.co/dermocosmetica-mascarillas-y-serum-mascarillas-y-serum-isdinceutics-retinal-intense-serum-facial-frasco-50-ml-867029/p</t>
+  </si>
+  <si>
+    <t>https://www.bellapiel.com.co/fotoprotector-isdin-uv-mineral-brush-spf-50-5765/p?srsltid=AfmBOorCjFuDi9n_LxUFHns3FQ8_Fh8Jj5DzhdJxX9LwOQiEspF8R61N</t>
+  </si>
+  <si>
+    <t>https://www.bellapiel.com.co/isdin-lambdapil-locion-anticaida-melatonin-concentrate-x-100ml-6935/p</t>
   </si>
 </sst>
 </file>
@@ -6348,12 +6348,12 @@
         <v>8</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>237</v>
+        <v>837</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>16</v>
@@ -6362,12 +6362,12 @@
         <v>8</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>16</v>
@@ -6376,12 +6376,12 @@
         <v>8</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="194" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A194" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>16</v>
@@ -6390,12 +6390,12 @@
         <v>8</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="195" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>16</v>
@@ -6404,12 +6404,12 @@
         <v>8</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>16</v>
@@ -6418,12 +6418,12 @@
         <v>8</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="197" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>16</v>
@@ -6432,12 +6432,12 @@
         <v>8</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="198" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A198" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>16</v>
@@ -6446,12 +6446,12 @@
         <v>8</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="199" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>16</v>
@@ -6460,12 +6460,12 @@
         <v>8</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>16</v>
@@ -6474,12 +6474,12 @@
         <v>8</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>16</v>
@@ -6488,12 +6488,12 @@
         <v>8</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>16</v>
@@ -6502,12 +6502,12 @@
         <v>8</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>16</v>
@@ -6516,12 +6516,12 @@
         <v>8</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>16</v>
@@ -6530,12 +6530,12 @@
         <v>8</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>16</v>
@@ -6544,12 +6544,12 @@
         <v>8</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="206" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>16</v>
@@ -6558,12 +6558,12 @@
         <v>8</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="207" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A207" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>16</v>
@@ -6572,12 +6572,12 @@
         <v>8</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="208" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A208" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>16</v>
@@ -6586,12 +6586,12 @@
         <v>8</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="209" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A209" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>16</v>
@@ -6600,12 +6600,12 @@
         <v>8</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="210" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>16</v>
@@ -6614,12 +6614,12 @@
         <v>8</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="211" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A211" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>16</v>
@@ -6628,12 +6628,12 @@
         <v>8</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="212" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A212" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>16</v>
@@ -6642,12 +6642,12 @@
         <v>8</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="213" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A213" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>16</v>
@@ -6656,12 +6656,12 @@
         <v>8</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>281</v>
+        <v>838</v>
       </c>
     </row>
     <row r="214" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A214" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>16</v>
@@ -6670,12 +6670,12 @@
         <v>8</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="215" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A215" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>16</v>
@@ -6684,12 +6684,12 @@
         <v>8</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="216" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>16</v>
@@ -6698,12 +6698,12 @@
         <v>8</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="217" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A217" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>16</v>
@@ -6712,12 +6712,12 @@
         <v>8</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>16</v>
@@ -6726,12 +6726,12 @@
         <v>8</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>16</v>
@@ -6740,12 +6740,12 @@
         <v>8</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>16</v>
@@ -6754,12 +6754,12 @@
         <v>8</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>16</v>
@@ -6768,7 +6768,7 @@
         <v>8</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.35">
@@ -6782,12 +6782,12 @@
         <v>8</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>16</v>
@@ -6796,12 +6796,12 @@
         <v>8</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="224" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A224" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>16</v>
@@ -6810,12 +6810,12 @@
         <v>8</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="225" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A225" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>16</v>
@@ -6824,12 +6824,12 @@
         <v>8</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="226" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>16</v>
@@ -6838,7 +6838,7 @@
         <v>8</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="227" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.35">
@@ -6852,12 +6852,12 @@
         <v>8</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="228" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A228" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>16</v>
@@ -6866,12 +6866,12 @@
         <v>8</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="229" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A229" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>16</v>
@@ -6880,12 +6880,12 @@
         <v>8</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="230" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>16</v>
@@ -6894,12 +6894,12 @@
         <v>8</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="231" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A231" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>16</v>
@@ -6908,12 +6908,12 @@
         <v>8</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="232" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>16</v>
@@ -6922,12 +6922,12 @@
         <v>8</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="233" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A233" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>16</v>
@@ -6936,12 +6936,12 @@
         <v>8</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="234" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>16</v>
@@ -6950,12 +6950,12 @@
         <v>8</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="235" spans="1:4" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>16</v>
@@ -6964,12 +6964,12 @@
         <v>8</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>16</v>
@@ -6978,12 +6978,12 @@
         <v>8</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>16</v>
@@ -6992,12 +6992,12 @@
         <v>8</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>16</v>
@@ -7006,12 +7006,12 @@
         <v>8</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>16</v>
@@ -7020,12 +7020,12 @@
         <v>8</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>16</v>
@@ -7034,12 +7034,12 @@
         <v>8</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>16</v>
@@ -7048,12 +7048,12 @@
         <v>8</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="242" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A242" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>16</v>
@@ -7062,12 +7062,12 @@
         <v>8</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="243" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A243" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>16</v>
@@ -7076,12 +7076,12 @@
         <v>8</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="244" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>16</v>
@@ -7090,12 +7090,12 @@
         <v>8</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="245" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A245" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>16</v>
@@ -7104,12 +7104,12 @@
         <v>8</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="246" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>16</v>
@@ -7118,12 +7118,12 @@
         <v>8</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="247" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A247" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>16</v>
@@ -7132,12 +7132,12 @@
         <v>8</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>16</v>
@@ -7146,12 +7146,12 @@
         <v>8</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A249" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>16</v>
@@ -7160,12 +7160,12 @@
         <v>8</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>16</v>
@@ -7174,7 +7174,7 @@
         <v>8</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.35">
@@ -7188,7 +7188,7 @@
         <v>4</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.35">
@@ -7202,7 +7202,7 @@
         <v>4</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.35">
@@ -7216,12 +7216,12 @@
         <v>4</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="254" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>16</v>
@@ -7230,12 +7230,12 @@
         <v>4</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="255" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A255" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>16</v>
@@ -7244,12 +7244,12 @@
         <v>4</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="256" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A256" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>16</v>
@@ -7258,12 +7258,12 @@
         <v>4</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="257" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A257" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>16</v>
@@ -7272,12 +7272,12 @@
         <v>4</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="258" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A258" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>16</v>
@@ -7286,12 +7286,12 @@
         <v>4</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="259" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A259" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>16</v>
@@ -7300,12 +7300,12 @@
         <v>4</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>16</v>
@@ -7314,12 +7314,12 @@
         <v>4</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>16</v>
@@ -7328,12 +7328,12 @@
         <v>4</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>16</v>
@@ -7342,12 +7342,12 @@
         <v>4</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>16</v>
@@ -7356,12 +7356,12 @@
         <v>4</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>16</v>
@@ -7370,12 +7370,12 @@
         <v>4</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>16</v>
@@ -7384,12 +7384,12 @@
         <v>4</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="266" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>16</v>
@@ -7398,12 +7398,12 @@
         <v>4</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="267" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A267" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>16</v>
@@ -7412,12 +7412,12 @@
         <v>4</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="268" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>16</v>
@@ -7426,12 +7426,12 @@
         <v>4</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="269" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A269" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>16</v>
@@ -7440,12 +7440,12 @@
         <v>4</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="270" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>16</v>
@@ -7454,12 +7454,12 @@
         <v>4</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="271" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A271" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>16</v>
@@ -7468,12 +7468,12 @@
         <v>4</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>16</v>
@@ -7482,12 +7482,12 @@
         <v>4</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>16</v>
@@ -7496,12 +7496,12 @@
         <v>4</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>16</v>
@@ -7510,12 +7510,12 @@
         <v>4</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>16</v>
@@ -7524,12 +7524,12 @@
         <v>4</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A276" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>16</v>
@@ -7538,12 +7538,12 @@
         <v>4</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>16</v>
@@ -7552,12 +7552,12 @@
         <v>4</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="278" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>16</v>
@@ -7566,12 +7566,12 @@
         <v>4</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="279" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A279" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>16</v>
@@ -7580,12 +7580,12 @@
         <v>4</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="280" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>16</v>
@@ -7594,12 +7594,12 @@
         <v>4</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="281" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A281" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>16</v>
@@ -7608,12 +7608,12 @@
         <v>4</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="282" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>16</v>
@@ -7622,12 +7622,12 @@
         <v>4</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="283" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A283" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>16</v>
@@ -7636,12 +7636,12 @@
         <v>4</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A284" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>16</v>
@@ -7650,12 +7650,12 @@
         <v>4</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A285" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>16</v>
@@ -7664,12 +7664,12 @@
         <v>4</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>16</v>
@@ -7678,12 +7678,12 @@
         <v>4</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A287" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>16</v>
@@ -7692,12 +7692,12 @@
         <v>4</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A288" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>16</v>
@@ -7706,12 +7706,12 @@
         <v>4</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A289" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>16</v>
@@ -7720,12 +7720,12 @@
         <v>4</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="290" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>16</v>
@@ -7734,12 +7734,12 @@
         <v>4</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="291" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A291" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>16</v>
@@ -7748,12 +7748,12 @@
         <v>4</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="292" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>16</v>
@@ -7762,12 +7762,12 @@
         <v>4</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="293" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A293" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>16</v>
@@ -7776,12 +7776,12 @@
         <v>4</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="294" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A294" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>16</v>
@@ -7790,12 +7790,12 @@
         <v>4</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="295" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A295" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>16</v>
@@ -7804,12 +7804,12 @@
         <v>4</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>16</v>
@@ -7818,12 +7818,12 @@
         <v>4</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A297" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>16</v>
@@ -7832,12 +7832,12 @@
         <v>4</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>16</v>
@@ -7846,12 +7846,12 @@
         <v>4</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A299" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>16</v>
@@ -7860,12 +7860,12 @@
         <v>4</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A300" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>16</v>
@@ -7874,12 +7874,12 @@
         <v>4</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A301" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>16</v>
@@ -7888,12 +7888,12 @@
         <v>4</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="302" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A302" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>16</v>
@@ -7902,12 +7902,12 @@
         <v>4</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="303" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A303" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>16</v>
@@ -7916,12 +7916,12 @@
         <v>4</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="304" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A304" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>16</v>
@@ -7930,12 +7930,12 @@
         <v>4</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="305" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A305" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>16</v>
@@ -7944,12 +7944,12 @@
         <v>4</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="306" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A306" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>16</v>
@@ -7958,12 +7958,12 @@
         <v>4</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="307" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A307" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>16</v>
@@ -7972,12 +7972,12 @@
         <v>4</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A308" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>16</v>
@@ -7986,12 +7986,12 @@
         <v>4</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A309" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>16</v>
@@ -8000,12 +8000,12 @@
         <v>4</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A310" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>16</v>
@@ -8014,12 +8014,12 @@
         <v>4</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A311" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>16</v>
@@ -8028,12 +8028,12 @@
         <v>4</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A312" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>16</v>
@@ -8042,12 +8042,12 @@
         <v>4</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A313" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>16</v>
@@ -8056,12 +8056,12 @@
         <v>4</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="314" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A314" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>16</v>
@@ -8070,12 +8070,12 @@
         <v>4</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="315" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A315" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>16</v>
@@ -8084,12 +8084,12 @@
         <v>4</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="316" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>16</v>
@@ -8098,7 +8098,7 @@
         <v>4</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="317" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.35">
@@ -8112,12 +8112,12 @@
         <v>6</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="318" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>16</v>
@@ -8126,12 +8126,12 @@
         <v>6</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="319" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A319" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>16</v>
@@ -8140,12 +8140,12 @@
         <v>6</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="320" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A320" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>16</v>
@@ -8154,12 +8154,12 @@
         <v>6</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="321" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A321" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>16</v>
@@ -8168,12 +8168,12 @@
         <v>6</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="322" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>16</v>
@@ -8182,12 +8182,12 @@
         <v>6</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="323" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A323" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>16</v>
@@ -8196,12 +8196,12 @@
         <v>6</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="324" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>16</v>
@@ -8210,12 +8210,12 @@
         <v>6</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="325" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A325" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>16</v>
@@ -8224,12 +8224,12 @@
         <v>6</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="326" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>16</v>
@@ -8238,7 +8238,7 @@
         <v>6</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="327" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
@@ -8252,12 +8252,12 @@
         <v>6</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="328" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A328" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>16</v>
@@ -8266,12 +8266,12 @@
         <v>6</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="329" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A329" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>16</v>
@@ -8280,12 +8280,12 @@
         <v>6</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="330" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>16</v>
@@ -8294,12 +8294,12 @@
         <v>6</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="331" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A331" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>16</v>
@@ -8308,12 +8308,12 @@
         <v>6</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A332" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>16</v>
@@ -8322,12 +8322,12 @@
         <v>6</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A333" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>16</v>
@@ -8336,12 +8336,12 @@
         <v>6</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>16</v>
@@ -8350,12 +8350,12 @@
         <v>6</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A335" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>16</v>
@@ -8364,7 +8364,7 @@
         <v>6</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.35">
@@ -8378,12 +8378,12 @@
         <v>6</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A337" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>16</v>
@@ -8392,12 +8392,12 @@
         <v>6</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A338" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>16</v>
@@ -8406,12 +8406,12 @@
         <v>6</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A339" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>16</v>
@@ -8420,12 +8420,12 @@
         <v>6</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A340" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>16</v>
@@ -8434,12 +8434,12 @@
         <v>6</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A341" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>16</v>
@@ -8448,12 +8448,12 @@
         <v>6</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A342" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>16</v>
@@ -8462,12 +8462,12 @@
         <v>6</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>16</v>
@@ -8476,12 +8476,12 @@
         <v>6</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A344" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>16</v>
@@ -8490,12 +8490,12 @@
         <v>6</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A345" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>16</v>
@@ -8504,12 +8504,12 @@
         <v>6</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A346" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>16</v>
@@ -8518,12 +8518,12 @@
         <v>6</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A347" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>16</v>
@@ -8532,12 +8532,12 @@
         <v>6</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A348" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>16</v>
@@ -8546,12 +8546,12 @@
         <v>6</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A349" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>16</v>
@@ -8560,12 +8560,12 @@
         <v>6</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A350" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>16</v>
@@ -8574,12 +8574,12 @@
         <v>6</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A351" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>16</v>
@@ -8588,12 +8588,12 @@
         <v>6</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A352" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>16</v>
@@ -8602,12 +8602,12 @@
         <v>6</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A353" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>16</v>
@@ -8616,12 +8616,12 @@
         <v>6</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A354" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>16</v>
@@ -8630,12 +8630,12 @@
         <v>6</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A355" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>16</v>
@@ -8644,12 +8644,12 @@
         <v>6</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A356" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>16</v>
@@ -8658,12 +8658,12 @@
         <v>6</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A357" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>16</v>
@@ -8672,12 +8672,12 @@
         <v>6</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A358" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>16</v>
@@ -8686,12 +8686,12 @@
         <v>6</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A359" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>16</v>
@@ -8700,12 +8700,12 @@
         <v>6</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A360" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>16</v>
@@ -8714,7 +8714,7 @@
         <v>6</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.35">
@@ -8728,7 +8728,7 @@
         <v>7</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.35">
@@ -8742,12 +8742,12 @@
         <v>7</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A363" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>16</v>
@@ -8756,12 +8756,12 @@
         <v>7</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A364" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>16</v>
@@ -8770,12 +8770,12 @@
         <v>7</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A365" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>16</v>
@@ -8784,12 +8784,12 @@
         <v>7</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A366" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>16</v>
@@ -8798,12 +8798,12 @@
         <v>7</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A367" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>16</v>
@@ -8812,12 +8812,12 @@
         <v>7</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A368" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>16</v>
@@ -8826,12 +8826,12 @@
         <v>7</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A369" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>16</v>
@@ -8840,12 +8840,12 @@
         <v>7</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A370" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>16</v>
@@ -8854,12 +8854,12 @@
         <v>7</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A371" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>16</v>
@@ -8868,12 +8868,12 @@
         <v>7</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A372" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>16</v>
@@ -8882,12 +8882,12 @@
         <v>7</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A373" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>16</v>
@@ -8896,12 +8896,12 @@
         <v>7</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A374" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>16</v>
@@ -8910,12 +8910,12 @@
         <v>7</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A375" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>16</v>
@@ -8924,12 +8924,12 @@
         <v>7</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A376" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>16</v>
@@ -8938,12 +8938,12 @@
         <v>7</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A377" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>16</v>
@@ -8952,12 +8952,12 @@
         <v>7</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A378" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>16</v>
@@ -8966,12 +8966,12 @@
         <v>7</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A379" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>16</v>
@@ -8980,12 +8980,12 @@
         <v>7</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A380" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>16</v>
@@ -8994,12 +8994,12 @@
         <v>7</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A381" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>16</v>
@@ -9008,12 +9008,12 @@
         <v>7</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A382" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>16</v>
@@ -9022,12 +9022,12 @@
         <v>7</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A383" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>16</v>
@@ -9036,12 +9036,12 @@
         <v>7</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A384" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>16</v>
@@ -9050,12 +9050,12 @@
         <v>7</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A385" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>16</v>
@@ -9064,12 +9064,12 @@
         <v>7</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A386" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>16</v>
@@ -9078,12 +9078,12 @@
         <v>7</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A387" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>16</v>
@@ -9092,12 +9092,12 @@
         <v>7</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A388" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>16</v>
@@ -9106,7 +9106,7 @@
         <v>7</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.35">
@@ -9120,7 +9120,7 @@
         <v>7</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.35">
@@ -9134,12 +9134,12 @@
         <v>7</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A391" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>16</v>
@@ -9148,12 +9148,12 @@
         <v>7</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A392" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>16</v>
@@ -9162,12 +9162,12 @@
         <v>7</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A393" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>16</v>
@@ -9176,12 +9176,12 @@
         <v>7</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A394" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>16</v>
@@ -9190,12 +9190,12 @@
         <v>7</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A395" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>16</v>
@@ -9204,12 +9204,12 @@
         <v>7</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A396" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>16</v>
@@ -9218,12 +9218,12 @@
         <v>7</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A397" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>16</v>
@@ -9232,12 +9232,12 @@
         <v>7</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A398" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>16</v>
@@ -9246,12 +9246,12 @@
         <v>7</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A399" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>16</v>
@@ -9260,12 +9260,12 @@
         <v>7</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A400" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>16</v>
@@ -9274,12 +9274,12 @@
         <v>7</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A401" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>16</v>
@@ -9288,12 +9288,12 @@
         <v>7</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A402" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>16</v>
@@ -9302,12 +9302,12 @@
         <v>7</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A403" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>16</v>
@@ -9316,12 +9316,12 @@
         <v>7</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A404" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>16</v>
@@ -9330,12 +9330,12 @@
         <v>7</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A405" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>16</v>
@@ -9344,12 +9344,12 @@
         <v>7</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A406" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>16</v>
@@ -9358,7 +9358,7 @@
         <v>7</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.35">
@@ -9372,7 +9372,7 @@
         <v>3</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.35">
@@ -9386,12 +9386,12 @@
         <v>3</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A409" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>16</v>
@@ -9400,12 +9400,12 @@
         <v>3</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A410" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>16</v>
@@ -9414,12 +9414,12 @@
         <v>3</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A411" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>16</v>
@@ -9428,7 +9428,7 @@
         <v>3</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.35">
@@ -9442,12 +9442,12 @@
         <v>3</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A413" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>16</v>
@@ -9456,12 +9456,12 @@
         <v>3</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A414" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>16</v>
@@ -9470,12 +9470,12 @@
         <v>3</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A415" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>16</v>
@@ -9484,12 +9484,12 @@
         <v>3</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A416" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>16</v>
@@ -9498,12 +9498,12 @@
         <v>3</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A417" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>16</v>
@@ -9512,12 +9512,12 @@
         <v>3</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A418" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>16</v>
@@ -9526,12 +9526,12 @@
         <v>3</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A419" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>16</v>
@@ -9540,12 +9540,12 @@
         <v>3</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A420" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>16</v>
@@ -9554,12 +9554,12 @@
         <v>3</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A421" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>16</v>
@@ -9568,7 +9568,7 @@
         <v>3</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.35">
@@ -9582,12 +9582,12 @@
         <v>3</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A423" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>16</v>
@@ -9596,12 +9596,12 @@
         <v>3</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A424" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>16</v>
@@ -9610,12 +9610,12 @@
         <v>3</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A425" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>16</v>
@@ -9624,12 +9624,12 @@
         <v>3</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A426" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>16</v>
@@ -9638,12 +9638,12 @@
         <v>3</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A427" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>16</v>
@@ -9652,12 +9652,12 @@
         <v>3</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A428" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>16</v>
@@ -9666,12 +9666,12 @@
         <v>3</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A429" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>16</v>
@@ -9680,12 +9680,12 @@
         <v>3</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A430" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>16</v>
@@ -9694,12 +9694,12 @@
         <v>3</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A431" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>16</v>
@@ -9708,12 +9708,12 @@
         <v>3</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A432" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>16</v>
@@ -9722,12 +9722,12 @@
         <v>3</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A433" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>16</v>
@@ -9736,12 +9736,12 @@
         <v>3</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A434" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>16</v>
@@ -9750,12 +9750,12 @@
         <v>3</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A435" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>16</v>
@@ -9764,12 +9764,12 @@
         <v>3</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A436" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>16</v>
@@ -9778,12 +9778,12 @@
         <v>3</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A437" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>16</v>
@@ -9792,12 +9792,12 @@
         <v>3</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A438" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>16</v>
@@ -9806,12 +9806,12 @@
         <v>3</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A439" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>16</v>
@@ -9820,12 +9820,12 @@
         <v>3</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A440" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>16</v>
@@ -9834,12 +9834,12 @@
         <v>3</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A441" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>16</v>
@@ -9848,12 +9848,12 @@
         <v>3</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A442" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>16</v>
@@ -9862,12 +9862,12 @@
         <v>3</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A443" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>16</v>
@@ -9876,12 +9876,12 @@
         <v>3</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A444" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>16</v>
@@ -9890,12 +9890,12 @@
         <v>3</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A445" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>16</v>
@@ -9904,12 +9904,12 @@
         <v>3</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A446" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>16</v>
@@ -9918,12 +9918,12 @@
         <v>3</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A447" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>16</v>
@@ -9932,12 +9932,12 @@
         <v>3</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A448" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>16</v>
@@ -9946,12 +9946,12 @@
         <v>3</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A449" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>16</v>
@@ -9960,12 +9960,12 @@
         <v>3</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A450" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>16</v>
@@ -9974,12 +9974,12 @@
         <v>3</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A451" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>16</v>
@@ -9988,12 +9988,12 @@
         <v>3</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A452" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>16</v>
@@ -10002,12 +10002,12 @@
         <v>3</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A453" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>16</v>
@@ -10016,12 +10016,12 @@
         <v>3</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A454" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>16</v>
@@ -10030,12 +10030,12 @@
         <v>3</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A455" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>16</v>
@@ -10044,12 +10044,12 @@
         <v>3</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A456" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>16</v>
@@ -10058,12 +10058,12 @@
         <v>3</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A457" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>16</v>
@@ -10072,12 +10072,12 @@
         <v>3</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A458" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>16</v>
@@ -10086,12 +10086,12 @@
         <v>3</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A459" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>16</v>
@@ -10100,12 +10100,12 @@
         <v>3</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A460" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>16</v>
@@ -10114,12 +10114,12 @@
         <v>3</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A461" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>16</v>
@@ -10128,12 +10128,12 @@
         <v>3</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A462" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>16</v>
@@ -10142,12 +10142,12 @@
         <v>3</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A463" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>16</v>
@@ -10156,12 +10156,12 @@
         <v>3</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A464" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>16</v>
@@ -10170,12 +10170,12 @@
         <v>3</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A465" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>16</v>
@@ -10184,12 +10184,12 @@
         <v>3</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A466" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B466" s="3" t="s">
         <v>16</v>
@@ -10198,12 +10198,12 @@
         <v>3</v>
       </c>
       <c r="D466" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A467" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B467" s="3" t="s">
         <v>16</v>
@@ -10212,12 +10212,12 @@
         <v>3</v>
       </c>
       <c r="D467" s="3" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A468" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B468" s="3" t="s">
         <v>16</v>
@@ -10226,7 +10226,7 @@
         <v>3</v>
       </c>
       <c r="D468" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.35">
@@ -10240,7 +10240,7 @@
         <v>5</v>
       </c>
       <c r="D469" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.35">
@@ -10254,12 +10254,12 @@
         <v>5</v>
       </c>
       <c r="D470" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A471" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B471" s="3" t="s">
         <v>16</v>
@@ -10268,12 +10268,12 @@
         <v>5</v>
       </c>
       <c r="D471" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A472" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B472" s="3" t="s">
         <v>16</v>
@@ -10282,12 +10282,12 @@
         <v>5</v>
       </c>
       <c r="D472" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A473" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B473" s="3" t="s">
         <v>16</v>
@@ -10296,12 +10296,12 @@
         <v>5</v>
       </c>
       <c r="D473" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A474" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>16</v>
@@ -10310,12 +10310,12 @@
         <v>5</v>
       </c>
       <c r="D474" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A475" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B475" s="3" t="s">
         <v>16</v>
@@ -10324,12 +10324,12 @@
         <v>5</v>
       </c>
       <c r="D475" s="3" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A476" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B476" s="3" t="s">
         <v>16</v>
@@ -10338,12 +10338,12 @@
         <v>5</v>
       </c>
       <c r="D476" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A477" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B477" s="3" t="s">
         <v>16</v>
@@ -10352,12 +10352,12 @@
         <v>5</v>
       </c>
       <c r="D477" s="3" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A478" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B478" s="3" t="s">
         <v>16</v>
@@ -10366,7 +10366,7 @@
         <v>5</v>
       </c>
       <c r="D478" s="3" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.35">
@@ -10380,7 +10380,7 @@
         <v>5</v>
       </c>
       <c r="D479" s="3" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.35">
@@ -10394,12 +10394,12 @@
         <v>5</v>
       </c>
       <c r="D480" s="3" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A481" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B481" s="3" t="s">
         <v>16</v>
@@ -10408,12 +10408,12 @@
         <v>5</v>
       </c>
       <c r="D481" s="3" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A482" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B482" s="3" t="s">
         <v>16</v>
@@ -10422,12 +10422,12 @@
         <v>5</v>
       </c>
       <c r="D482" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A483" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B483" s="3" t="s">
         <v>16</v>
@@ -10436,12 +10436,12 @@
         <v>5</v>
       </c>
       <c r="D483" s="3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A484" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B484" s="3" t="s">
         <v>16</v>
@@ -10450,7 +10450,7 @@
         <v>5</v>
       </c>
       <c r="D484" s="3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.35">
@@ -10464,12 +10464,12 @@
         <v>5</v>
       </c>
       <c r="D485" s="3" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A486" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B486" s="3" t="s">
         <v>16</v>
@@ -10478,12 +10478,12 @@
         <v>5</v>
       </c>
       <c r="D486" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A487" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B487" s="3" t="s">
         <v>16</v>
@@ -10492,12 +10492,12 @@
         <v>5</v>
       </c>
       <c r="D487" s="3" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A488" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B488" s="3" t="s">
         <v>16</v>
@@ -10506,12 +10506,12 @@
         <v>5</v>
       </c>
       <c r="D488" s="3" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A489" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B489" s="3" t="s">
         <v>16</v>
@@ -10520,7 +10520,7 @@
         <v>5</v>
       </c>
       <c r="D489" s="3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.35">
@@ -10534,7 +10534,7 @@
         <v>5</v>
       </c>
       <c r="D490" s="3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.35">
@@ -10548,12 +10548,12 @@
         <v>5</v>
       </c>
       <c r="D491" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A492" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>16</v>
@@ -10562,12 +10562,12 @@
         <v>5</v>
       </c>
       <c r="D492" s="3" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A493" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>16</v>
@@ -10576,12 +10576,12 @@
         <v>5</v>
       </c>
       <c r="D493" s="3" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A494" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>16</v>
@@ -10590,12 +10590,12 @@
         <v>5</v>
       </c>
       <c r="D494" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A495" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>16</v>
@@ -10604,12 +10604,12 @@
         <v>5</v>
       </c>
       <c r="D495" s="3" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A496" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B496" s="3" t="s">
         <v>16</v>
@@ -10618,7 +10618,7 @@
         <v>5</v>
       </c>
       <c r="D496" s="3" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.35">
@@ -10632,7 +10632,7 @@
         <v>5</v>
       </c>
       <c r="D497" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.35">
@@ -10646,12 +10646,12 @@
         <v>5</v>
       </c>
       <c r="D498" s="3" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A499" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B499" s="3" t="s">
         <v>16</v>
@@ -10660,12 +10660,12 @@
         <v>5</v>
       </c>
       <c r="D499" s="3" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A500" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B500" s="3" t="s">
         <v>16</v>
@@ -10674,12 +10674,12 @@
         <v>5</v>
       </c>
       <c r="D500" s="3" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A501" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>16</v>
@@ -10688,7 +10688,7 @@
         <v>5</v>
       </c>
       <c r="D501" s="3" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.35">
@@ -10702,12 +10702,12 @@
         <v>5</v>
       </c>
       <c r="D502" s="3" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A503" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>16</v>
@@ -10716,12 +10716,12 @@
         <v>5</v>
       </c>
       <c r="D503" s="3" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A504" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>16</v>
@@ -10730,12 +10730,12 @@
         <v>5</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A505" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>16</v>
@@ -10744,12 +10744,12 @@
         <v>5</v>
       </c>
       <c r="D505" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A506" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>16</v>
@@ -10758,12 +10758,12 @@
         <v>5</v>
       </c>
       <c r="D506" s="3" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A507" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>16</v>
@@ -10772,12 +10772,12 @@
         <v>5</v>
       </c>
       <c r="D507" s="3" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A508" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>16</v>
@@ -10786,12 +10786,12 @@
         <v>5</v>
       </c>
       <c r="D508" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A509" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B509" s="3" t="s">
         <v>16</v>
@@ -10800,12 +10800,12 @@
         <v>5</v>
       </c>
       <c r="D509" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A510" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B510" s="3" t="s">
         <v>16</v>
@@ -10814,12 +10814,12 @@
         <v>5</v>
       </c>
       <c r="D510" s="3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A511" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B511" s="3" t="s">
         <v>16</v>
@@ -10828,12 +10828,12 @@
         <v>5</v>
       </c>
       <c r="D511" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A512" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>16</v>
@@ -10842,12 +10842,12 @@
         <v>5</v>
       </c>
       <c r="D512" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A513" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>16</v>
@@ -10856,12 +10856,12 @@
         <v>5</v>
       </c>
       <c r="D513" s="3" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A514" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>16</v>
@@ -10870,7 +10870,7 @@
         <v>5</v>
       </c>
       <c r="D514" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.35">
@@ -10881,10 +10881,10 @@
         <v>16</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D515" s="3" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.35">
@@ -10895,10 +10895,10 @@
         <v>16</v>
       </c>
       <c r="C516" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D516" s="5" t="s">
         <v>633</v>
-      </c>
-      <c r="D516" s="5" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.35">
@@ -10909,10 +10909,10 @@
         <v>16</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D517" s="5" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.35">
@@ -10923,10 +10923,10 @@
         <v>16</v>
       </c>
       <c r="C518" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D518" s="5" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.35">
@@ -10937,10 +10937,10 @@
         <v>16</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D519" s="5" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.35">
@@ -10951,10 +10951,10 @@
         <v>16</v>
       </c>
       <c r="C520" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D520" s="5" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.35">
@@ -10965,10 +10965,10 @@
         <v>16</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D521" s="5" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.35">
@@ -10979,10 +10979,10 @@
         <v>16</v>
       </c>
       <c r="C522" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D522" s="5" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.35">
@@ -10993,10 +10993,10 @@
         <v>16</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D523" s="5" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.35">
@@ -11007,10 +11007,10 @@
         <v>16</v>
       </c>
       <c r="C524" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D524" s="5" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.35">
@@ -11021,10 +11021,10 @@
         <v>16</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D525" s="5" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.35">
@@ -11035,10 +11035,10 @@
         <v>16</v>
       </c>
       <c r="C526" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D526" s="5" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.35">
@@ -11049,10 +11049,10 @@
         <v>16</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D527" s="5" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.35">
@@ -11063,10 +11063,10 @@
         <v>16</v>
       </c>
       <c r="C528" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D528" s="5" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.35">
@@ -11077,10 +11077,10 @@
         <v>16</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D529" s="3" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.35">
@@ -11091,10 +11091,10 @@
         <v>16</v>
       </c>
       <c r="C530" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D530" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.35">
@@ -11105,10 +11105,10 @@
         <v>16</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D531" s="5" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.35">
@@ -11119,10 +11119,10 @@
         <v>16</v>
       </c>
       <c r="C532" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D532" s="5" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.35">
@@ -11133,10 +11133,10 @@
         <v>16</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D533" s="5" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.35">
@@ -11147,10 +11147,10 @@
         <v>16</v>
       </c>
       <c r="C534" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D534" s="5" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.35">
@@ -11161,10 +11161,10 @@
         <v>16</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D535" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.35">
@@ -11175,10 +11175,10 @@
         <v>16</v>
       </c>
       <c r="C536" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D536" s="5" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.35">
@@ -11189,10 +11189,10 @@
         <v>16</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D537" s="5" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.35">
@@ -11203,10 +11203,10 @@
         <v>16</v>
       </c>
       <c r="C538" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D538" s="5" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.35">
@@ -11217,10 +11217,10 @@
         <v>16</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D539" s="3" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.35">
@@ -11231,122 +11231,122 @@
         <v>16</v>
       </c>
       <c r="C540" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D540" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A541" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B541" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D541" s="3" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A542" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B542" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C542" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D542" s="3" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A543" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B543" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D543" s="3" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A544" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B544" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C544" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D544" s="3" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A545" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B545" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D545" s="3" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A546" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B546" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C546" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D546" s="3" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A547" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B547" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D547" s="3" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A548" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B548" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C548" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D548" s="3" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.35">
@@ -11357,10 +11357,10 @@
         <v>16</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D549" s="3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.35">
@@ -11371,52 +11371,52 @@
         <v>16</v>
       </c>
       <c r="C550" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D550" s="3" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A551" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B551" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D551" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A552" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B552" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C552" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D552" s="3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A553" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B553" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D553" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.35">
@@ -11427,66 +11427,66 @@
         <v>16</v>
       </c>
       <c r="C554" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D554" s="3" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A555" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B555" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D555" s="3" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A556" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B556" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C556" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D556" s="3" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A557" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B557" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D557" s="3" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A558" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B558" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C558" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D558" s="3" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.35">
@@ -11497,10 +11497,10 @@
         <v>16</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D559" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.35">
@@ -11511,66 +11511,66 @@
         <v>16</v>
       </c>
       <c r="C560" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D560" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A561" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B561" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C561" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D561" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A562" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B562" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C562" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D562" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A563" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B563" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D563" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A564" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B564" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C564" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D564" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.35">
@@ -11581,10 +11581,10 @@
         <v>16</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D565" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.35">
@@ -11595,52 +11595,52 @@
         <v>16</v>
       </c>
       <c r="C566" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D566" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A567" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B567" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D567" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A568" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B568" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C568" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D568" s="3" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A569" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B569" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C569" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D569" s="3" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.35">
@@ -11651,164 +11651,164 @@
         <v>16</v>
       </c>
       <c r="C570" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D570" s="3" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A571" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B571" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C571" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D571" s="3" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A572" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B572" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C572" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D572" s="3" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A573" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B573" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D573" s="3" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A574" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B574" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C574" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D574" s="3" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A575" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B575" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D575" s="3" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A576" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B576" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C576" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D576" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A577" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B577" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C577" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D577" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A578" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B578" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C578" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D578" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A579" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B579" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C579" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D579" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A580" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B580" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C580" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D580" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A581" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B581" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C581" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D581" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.35">
@@ -11819,10 +11819,10 @@
         <v>16</v>
       </c>
       <c r="C582" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D582" s="5" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.35">
@@ -11833,10 +11833,10 @@
         <v>16</v>
       </c>
       <c r="C583" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="D583" s="3" t="s">
         <v>701</v>
-      </c>
-      <c r="D583" s="3" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.35">
@@ -11847,10 +11847,10 @@
         <v>16</v>
       </c>
       <c r="C584" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D584" s="3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.35">
@@ -11861,10 +11861,10 @@
         <v>16</v>
       </c>
       <c r="C585" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D585" s="5" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.35">
@@ -11875,10 +11875,10 @@
         <v>16</v>
       </c>
       <c r="C586" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D586" s="5" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.35">
@@ -11889,10 +11889,10 @@
         <v>16</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D587" s="5" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.35">
@@ -11903,10 +11903,10 @@
         <v>16</v>
       </c>
       <c r="C588" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D588" s="5" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.35">
@@ -11917,10 +11917,10 @@
         <v>16</v>
       </c>
       <c r="C589" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D589" s="5" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.35">
@@ -11931,10 +11931,10 @@
         <v>16</v>
       </c>
       <c r="C590" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D590" s="5" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.35">
@@ -11945,10 +11945,10 @@
         <v>16</v>
       </c>
       <c r="C591" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D591" s="5" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.35">
@@ -11959,10 +11959,10 @@
         <v>16</v>
       </c>
       <c r="C592" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D592" s="5" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.35">
@@ -11973,10 +11973,10 @@
         <v>16</v>
       </c>
       <c r="C593" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D593" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.35">
@@ -11987,10 +11987,10 @@
         <v>16</v>
       </c>
       <c r="C594" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D594" s="5" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.35">
@@ -12001,10 +12001,10 @@
         <v>16</v>
       </c>
       <c r="C595" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D595" s="5" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.35">
@@ -12015,10 +12015,10 @@
         <v>16</v>
       </c>
       <c r="C596" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D596" s="5" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.35">
@@ -12029,10 +12029,10 @@
         <v>16</v>
       </c>
       <c r="C597" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D597" s="5" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.35">
@@ -12043,10 +12043,10 @@
         <v>16</v>
       </c>
       <c r="C598" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D598" s="5" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.35">
@@ -12057,10 +12057,10 @@
         <v>16</v>
       </c>
       <c r="C599" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D599" s="5" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.35">
@@ -12071,10 +12071,10 @@
         <v>16</v>
       </c>
       <c r="C600" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D600" s="5" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.35">
@@ -12085,10 +12085,10 @@
         <v>16</v>
       </c>
       <c r="C601" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D601" s="5" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.35">
@@ -12099,10 +12099,10 @@
         <v>16</v>
       </c>
       <c r="C602" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D602" s="5" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.35">
@@ -12113,10 +12113,10 @@
         <v>16</v>
       </c>
       <c r="C603" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D603" s="5" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.35">
@@ -12127,10 +12127,10 @@
         <v>16</v>
       </c>
       <c r="C604" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D604" s="5" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.35">
@@ -12141,10 +12141,10 @@
         <v>16</v>
       </c>
       <c r="C605" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D605" s="5" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.35">
@@ -12155,10 +12155,10 @@
         <v>16</v>
       </c>
       <c r="C606" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D606" s="5" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.35">
@@ -12169,10 +12169,10 @@
         <v>16</v>
       </c>
       <c r="C607" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D607" s="29" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.35">
@@ -12183,10 +12183,10 @@
         <v>16</v>
       </c>
       <c r="C608" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D608" s="5" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.35">
@@ -12197,10 +12197,10 @@
         <v>16</v>
       </c>
       <c r="C609" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D609" s="3" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.35">
@@ -12211,10 +12211,10 @@
         <v>16</v>
       </c>
       <c r="C610" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D610" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.35">
@@ -12225,10 +12225,10 @@
         <v>16</v>
       </c>
       <c r="C611" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D611" s="5" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.35">
@@ -12239,10 +12239,10 @@
         <v>16</v>
       </c>
       <c r="C612" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D612" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.35">
@@ -12253,290 +12253,290 @@
         <v>16</v>
       </c>
       <c r="C613" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D613" s="3" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A614" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B614" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C614" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D614" s="3" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A615" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B615" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C615" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D615" s="3" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A616" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B616" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C616" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D616" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A617" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B617" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C617" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D617" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A618" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B618" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C618" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D618" s="3" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A619" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B619" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C619" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D619" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A620" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B620" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C620" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D620" s="3" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A621" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B621" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C621" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D621" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A622" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B622" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C622" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D622" s="3" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A623" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B623" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C623" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D623" s="3" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A624" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B624" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C624" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D624" s="3" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A625" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B625" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C625" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D625" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A626" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B626" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C626" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D626" s="5" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A627" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B627" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C627" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D627" s="5" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A628" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B628" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C628" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D628" s="5" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A629" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B629" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C629" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D629" s="5" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A630" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B630" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C630" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D630" s="5" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A631" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B631" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D631" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A632" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B632" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D632" s="5" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A633" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B633" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D633" s="5" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.35">
@@ -12547,66 +12547,66 @@
         <v>16</v>
       </c>
       <c r="C634" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D634" s="5" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A635" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B635" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C635" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D635" s="5" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A636" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B636" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C636" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D636" s="5" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A637" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B637" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C637" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D637" s="5" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A638" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B638" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D638" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E638" s="3"/>
       <c r="F638" s="5"/>
@@ -12614,44 +12614,44 @@
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A639" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B639" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D639" s="5" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A640" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B640" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C640" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D640" s="5" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A641" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B641" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C641" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D641" s="5" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.35">
@@ -12662,10 +12662,10 @@
         <v>16</v>
       </c>
       <c r="C642" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D642" s="5" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.35">
@@ -12676,10 +12676,10 @@
         <v>16</v>
       </c>
       <c r="C643" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="D643" s="5" t="s">
         <v>761</v>
-      </c>
-      <c r="D643" s="5" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.35">
@@ -12690,10 +12690,10 @@
         <v>16</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D644" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.35">
@@ -12704,10 +12704,10 @@
         <v>16</v>
       </c>
       <c r="C645" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D645" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.35">
@@ -12718,38 +12718,38 @@
         <v>16</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D646" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A647" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B647" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D647" s="5" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A648" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B648" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C648" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D648" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.35">
@@ -12760,10 +12760,10 @@
         <v>16</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D649" s="5" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.35">
@@ -12774,10 +12774,10 @@
         <v>16</v>
       </c>
       <c r="C650" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D650" s="5" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.35">
@@ -12788,24 +12788,24 @@
         <v>16</v>
       </c>
       <c r="C651" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D651" s="5" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A652" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B652" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C652" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D652" s="5" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.35">
@@ -12816,38 +12816,38 @@
         <v>16</v>
       </c>
       <c r="C653" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D653" s="5" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A654" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B654" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C654" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D654" s="5" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A655" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B655" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C655" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D655" s="5" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.35">
@@ -12858,10 +12858,10 @@
         <v>16</v>
       </c>
       <c r="C656" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D656" s="5" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.35">
@@ -12872,10 +12872,10 @@
         <v>16</v>
       </c>
       <c r="C657" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D657" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.35">
@@ -12886,38 +12886,38 @@
         <v>16</v>
       </c>
       <c r="C658" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D658" s="5" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A659" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B659" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C659" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D659" s="5" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A660" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B660" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C660" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D660" s="5" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.35">
@@ -12928,10 +12928,10 @@
         <v>16</v>
       </c>
       <c r="C661" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D661" s="5" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.35">
@@ -12942,38 +12942,38 @@
         <v>16</v>
       </c>
       <c r="C662" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D662" s="5" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A663" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B663" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C663" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D663" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A664" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B664" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C664" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D664" s="5" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.35">
@@ -12984,10 +12984,10 @@
         <v>16</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D665" s="5" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.35">
@@ -12998,24 +12998,24 @@
         <v>16</v>
       </c>
       <c r="C666" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D666" s="5" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A667" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B667" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C667" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D667" s="5" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.35">
@@ -13026,10 +13026,10 @@
         <v>16</v>
       </c>
       <c r="C668" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D668" s="5" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.35">
@@ -13040,10 +13040,10 @@
         <v>16</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D669" s="5" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.35">
@@ -13054,122 +13054,122 @@
         <v>16</v>
       </c>
       <c r="C670" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D670" s="5" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A671" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B671" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C671" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D671" s="5" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A672" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B672" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C672" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D672" s="5" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A673" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B673" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C673" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D673" s="5" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A674" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B674" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C674" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D674" s="5" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A675" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B675" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C675" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D675" s="5" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A676" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B676" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C676" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D676" s="5" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A677" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B677" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C677" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D677" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A678" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B678" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C678" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D678" s="5" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.35">
@@ -13180,66 +13180,66 @@
         <v>16</v>
       </c>
       <c r="C679" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D679" s="5" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A680" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B680" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C680" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D680" s="5" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A681" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B681" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C681" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D681" s="5" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A682" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B682" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C682" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D682" s="5" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A683" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B683" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C683" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D683" s="5" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.35">
@@ -13250,10 +13250,10 @@
         <v>16</v>
       </c>
       <c r="C684" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D684" s="5" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.35">
@@ -13264,10 +13264,10 @@
         <v>16</v>
       </c>
       <c r="C685" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D685" s="5" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.35">
@@ -13278,66 +13278,66 @@
         <v>16</v>
       </c>
       <c r="C686" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D686" s="5" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A687" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B687" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C687" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D687" s="5" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A688" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B688" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C688" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D688" s="5" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A689" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B689" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C689" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D689" s="5" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A690" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B690" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C690" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D690" s="5" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.35">
@@ -13348,24 +13348,24 @@
         <v>16</v>
       </c>
       <c r="C691" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D691" s="5" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A692" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B692" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C692" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D692" s="5" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.35">
@@ -13376,10 +13376,10 @@
         <v>16</v>
       </c>
       <c r="C693" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D693" s="5" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.35">
@@ -13390,80 +13390,80 @@
         <v>16</v>
       </c>
       <c r="C694" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D694" s="5" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A695" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B695" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C695" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D695" s="5" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A696" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B696" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C696" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D696" s="5" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A697" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B697" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C697" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D697" s="5" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A698" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B698" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C698" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D698" s="5" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A699" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B699" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C699" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D699" s="5" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.35">
@@ -13474,108 +13474,108 @@
         <v>16</v>
       </c>
       <c r="C700" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D700" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A701" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B701" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C701" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D701" s="5" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A702" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B702" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C702" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D702" s="5" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A703" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B703" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C703" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D703" s="5" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A704" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B704" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C704" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D704" s="5" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A705" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B705" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C705" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D705" s="5" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A706" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B706" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C706" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D706" s="5" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A707" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B707" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C707" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D707" s="5" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.35">
@@ -13586,10 +13586,10 @@
         <v>16</v>
       </c>
       <c r="C708" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D708" s="5" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.35">
@@ -13600,10 +13600,10 @@
         <v>16</v>
       </c>
       <c r="C709" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D709" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.35">
@@ -13614,24 +13614,24 @@
         <v>16</v>
       </c>
       <c r="C710" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D710" s="5" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A711" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B711" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C711" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D711" s="5" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.35">
@@ -13642,10 +13642,10 @@
         <v>16</v>
       </c>
       <c r="C712" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D712" s="5" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.35">
@@ -13656,52 +13656,52 @@
         <v>16</v>
       </c>
       <c r="C713" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D713" s="5" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A714" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B714" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C714" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D714" s="5" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A715" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B715" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C715" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D715" s="5" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A716" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B716" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C716" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D716" s="5" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.35">
@@ -13712,10 +13712,10 @@
         <v>16</v>
       </c>
       <c r="C717" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D717" s="5" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.35">
@@ -13726,14 +13726,14 @@
         <v>16</v>
       </c>
       <c r="C718" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D718" s="5" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D581" xr:uid="{2C4ECE9E-4A28-6340-B936-CE442F4057E5}"/>
+  <autoFilter ref="A1:D718" xr:uid="{2C4ECE9E-4A28-6340-B936-CE442F4057E5}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D704" r:id="rId1" xr:uid="{C4A764D9-65E4-467B-BC7B-5C3E51C52CDA}"/>

--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMSIERRA\Documents\ISDIN_Shopping_de_precios\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E9D405-B267-4FEA-9EDE-0AF11983F712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17C2D9C-DA6D-4AD1-A119-24743F144A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-72" yWindow="12852" windowWidth="23256" windowHeight="13896" xr2:uid="{60233B49-B589-B346-B71C-4D486694C55A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$721</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$706</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2884" uniqueCount="842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2824" uniqueCount="827">
   <si>
     <t>Producto</t>
   </si>
@@ -1796,18 +1796,12 @@
     <t>https://www.falabella.com.co/falabella-co/product/12682128/Bloqueador-Solar-Eryfotona-AK-NMSC-Isdin-para-Piel-Sensible-50-ml/12682128</t>
   </si>
   <si>
-    <t>https://www.falabella.com.co/falabella-co/product/12682132/Bloqueador-Solar-Fusion-Water-con-Color-Isdin-para-Piel-Mixta-50-ml/12682132</t>
-  </si>
-  <si>
     <t>https://www.falabella.com.co/falabella-co/product/29086847/Bloqueador-Solar-Foto-Ultra-100-Active-Unify-Isdin-para-Todo-tipo-de-piel-50-ml/29086847</t>
   </si>
   <si>
     <t>https://www.falabella.com.co/falabella-co/product/29086848/Bloqueador-Solar-Fotoultra-Active-Unify-Color-50-ml-Isdin-para-Todo-tipo-de-piel-50-ml/29086848</t>
   </si>
   <si>
-    <t>https://www.falabella.com.co/falabella-co/product/73148089/Protector-solar-FUSION-WATER-MAGIC-REPAIR-SPF50-50ML-Crema-ISDIN-Crema-50ml/73148089</t>
-  </si>
-  <si>
     <t>https://www.falabella.com.co/falabella-co/product/31652096/Serum-Isdinceutics-Rejuvenate-Flavo-C-Isdin-para-Todo-tipo-de-piel-30-ml/31652096</t>
   </si>
   <si>
@@ -1823,27 +1817,15 @@
     <t>https://www.falabella.com.co/falabella-co/product/73133689/Bloqueador-Fp-Invisible-Stick-Spf50-10G-en-barra-Isdin-10-gr/73133689</t>
   </si>
   <si>
-    <t>https://www.falabella.com.co/falabella-co/product/12682170/Tratamiento-antiedad-Age-Reverse-Night-Noche-Isdin-para-Piel-Normal-50-ml/12682170</t>
-  </si>
-  <si>
     <t>https://www.falabella.com.co/falabella-co/product/73259531/Protector-solar-Fotoprotector-Fusion-Water-Magic-By-Alcaraz-Emulsion-Isdin-50-ml/73259531</t>
   </si>
   <si>
     <t>https://www.falabella.com.co/falabella-co/product/20233919/Hidratante-Facial-Isdinceutics-Hyaluronic-Concentrate-Isdin-para-Todo-tipo-de-piel-30-ml/20233919</t>
   </si>
   <si>
-    <t>https://www.falabella.com.co/falabella-co/product/19508501/Contorno-de-Ojos-Rejuvenate-Vital-Eyes-Noche-Isdin-para-Todo-tipo-de-piel-15-ml/19508501</t>
-  </si>
-  <si>
-    <t>https://www.falabella.com.co/falabella-co/product/73051045/Protector-solar-Isdin-FotoUltra-100-Fotoprotecto-Spot-Prevent-Color-SPF-50+-Crema-ISDIN-Crema-50ml/73051045</t>
-  </si>
-  <si>
     <t>https://www.falabella.com.co/falabella-co/product/73148088/Protector-solar-Fusion-Water-MAgic-REPAIR-COLOR-SPF50-50ML-Crema-ISDIN-Crema-50ml/73148088</t>
   </si>
   <si>
-    <t>https://www.falabella.com.co/falabella-co/product/73265847/Fotoprotector-ISDIN-Fusion-Gel-SPORT-SPF50-Protector-solar-corporal-para-el-deporte-Isdin-para-Todo-tipo-de-piel-100-ml/73265847</t>
-  </si>
-  <si>
     <t>https://www.falabella.com.co/falabella-co/product/73129676/Bloqueador-FP-GEL-CREAM-SPF50-250ML-Crema-ISDIN-Gel-250ml/73129676</t>
   </si>
   <si>
@@ -1868,15 +1850,6 @@
     <t>https://www.falabella.com.co/falabella-co/product/72914713/Jabon-Babynaturals-Gel-Shampoo-Isdin-para-Bebes-400-ml/72914713</t>
   </si>
   <si>
-    <t>https://www.falabella.com.co/falabella-co/product/72914711/Crema-Babynaturals-Pomada-Isdin-para-Bebes-100-ml/72914711</t>
-  </si>
-  <si>
-    <t>https://www.falabella.com.co/falabella-co/product/73390088/Protector-solar-Fotoprotector-Pediatrics-Stick-en-Barra-Isdin-20-Gr/73390088</t>
-  </si>
-  <si>
-    <t>https://www.falabella.com.co/falabella-co/product/122877665/Fotoprotector-Isdin-Uv-Mineral-Brush-Polvo-50spf-X-2g/122877666</t>
-  </si>
-  <si>
     <t>https://www.falabella.com.co/falabella-co/product/122787136/Polvo-Compacto-Isdin-Fotoprotector-Spf50-Arena-10g/122787137</t>
   </si>
   <si>
@@ -1889,12 +1862,6 @@
     <t>https://www.falabella.com.co/falabella-co/product/73390092/Protector-solar-Fotoprotector-Fusion-Water-Magic-Glow-en-Crema-Isdin-50-ml/73390092</t>
   </si>
   <si>
-    <t>https://www.falabella.com.co/falabella-co/product/122877557/Fotoprotector-Isdin-Hydrolotion-+-50spf-200ml/122877558</t>
-  </si>
-  <si>
-    <t>https://www.falabella.com.co/falabella-co/product/123173276/Fotoprotector-Isdin-Hydro-Oil-SPF-30-Proteccion-Alta-X-200-Ml/123173278</t>
-  </si>
-  <si>
     <t>https://www.falabella.com.co/falabella-co/product/73531835/bloqueador-fp-fw-body-glow-spf-30-en-crema-isdin-200-ml/73531835</t>
   </si>
   <si>
@@ -1904,12 +1871,6 @@
     <t>https://www.falabella.com.co/falabella-co/product/73051046/Fotoprotector-para-labios-FP-LIPSTICK-SPF-50+-4G-Barra-ISDIN-4-g/73051046</t>
   </si>
   <si>
-    <t>https://www.falabella.com.co/falabella-co/product/12682168/Limpiador-Germisdin-Gel-de-Bano-Isdin-para-Piel-Normal-500-ml/12682168</t>
-  </si>
-  <si>
-    <t>https://www.falabella.com.co/falabella-co/product/125963015/locion-isdin-lambdapil-anticaida-x-125ml/125963016</t>
-  </si>
-  <si>
     <t>https://www.falabella.com.co/falabella-co/product/12682156/Hidratante-Facial-Nutratopic-Pro-AMP-Emoliente-Isdin-para-Todo-tipo-de-piel-50-ml/12682156</t>
   </si>
   <si>
@@ -1937,21 +1898,12 @@
     <t>https://www.falabella.com.co/falabella-co/product/12682150/Tratamiento-para-Unas-Si-Nails-Isdin-para-Todo-tipo-de-piel-2.5-ml/12682150</t>
   </si>
   <si>
-    <t>https://www.falabella.com.co/falabella-co/product/12682151/Agua-Micelar-Solution-4-en-1-Isdin-para-Piel-Normal-400-ml/12682151</t>
-  </si>
-  <si>
-    <t>https://www.falabella.com.co/falabella-co/product/12682152/Agua-Micelar-Solution-4-en-1-Isdin-para-Piel-Normal-100-ml/12682152</t>
-  </si>
-  <si>
     <t>https://www.falabella.com.co/falabella-co/product/12682160/Tratamiento-para-Pies-Ureadin-Podos-Isdin-para-Piel-Normal-75-ml/12682160</t>
   </si>
   <si>
     <t>https://www.falabella.com.co/falabella-co/product/12682161/Tratamiento-para-Manos-Ureadin-Plus-Repair-Isdin-para-Piel-Normal-50-ml/12682161</t>
   </si>
   <si>
-    <t>https://www.falabella.com.co/falabella-co/product/46172382/Reafirmante-para-Cuerpo-Isdin-250-ml/46172382</t>
-  </si>
-  <si>
     <t>https://www.falabella.com.co/falabella-co/product/73398122/Contorno-de-ojos-Ceutics-Hyaluronic-Eyes-Isdin-para-Todo-tipo-de-piel-15-gr/73398122</t>
   </si>
   <si>
@@ -2249,9 +2201,6 @@
     <t>https://www.falabella.com.co/falabella-co/product/126491433/fusion-water-pediatrics-spf-50-x-50ml-isdin/126491434</t>
   </si>
   <si>
-    <t>https://www.falabella.com.co/falabella-co/product/136677712/Isdinceutics-Melaclear-Advanced-Serum.-/136677713</t>
-  </si>
-  <si>
     <t>https://lineaestetica.co/product/isdin-fotoultra-100-active-unify-50-x-50-ml/</t>
   </si>
   <si>
@@ -2565,6 +2514,12 @@
   </si>
   <si>
     <t>https://www.farmaciaspasteur.com.co/dermocosmetica-iluminadores-bases-isdin-base-coverage-5-0-bronze-spf-50--frasco-30-g-867053/p</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/73534257/fotoprotector-fusion-water-color/73534257</t>
+  </si>
+  <si>
+    <t>https://www.falabella.com.co/falabella-co/product/20947099/Bloqueador-Solar-Fusion-Gel-Sport-Wet-Skin-Isdin-para-Todo-tipo-de-piel-100-ml/20947099</t>
   </si>
 </sst>
 </file>
@@ -3123,7 +3078,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C4ECE9E-4A28-6340-B936-CE442F4057E5}">
-  <dimension ref="A1:N721"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:N706"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.375" customWidth="1"/>
@@ -3146,7 +3102,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>40</v>
       </c>
@@ -3160,7 +3116,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>42</v>
       </c>
@@ -3174,7 +3130,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>32</v>
       </c>
@@ -3198,7 +3154,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>33</v>
       </c>
@@ -3222,7 +3178,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>35</v>
       </c>
@@ -3246,7 +3202,7 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>38</v>
       </c>
@@ -3270,7 +3226,7 @@
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>39</v>
       </c>
@@ -3294,7 +3250,7 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
@@ -3318,7 +3274,7 @@
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
@@ -3342,7 +3298,7 @@
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>36</v>
       </c>
@@ -3366,7 +3322,7 @@
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
     </row>
-    <row r="12" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>2</v>
       </c>
@@ -3390,7 +3346,7 @@
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
     </row>
-    <row r="13" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
@@ -3414,7 +3370,7 @@
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
     </row>
-    <row r="14" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>18</v>
       </c>
@@ -3438,7 +3394,7 @@
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
     </row>
-    <row r="15" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
@@ -3462,7 +3418,7 @@
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
     </row>
-    <row r="16" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -3486,7 +3442,7 @@
       <c r="M16" s="14"/>
       <c r="N16" s="14"/>
     </row>
-    <row r="17" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>26</v>
       </c>
@@ -3510,7 +3466,7 @@
       <c r="M17" s="14"/>
       <c r="N17" s="14"/>
     </row>
-    <row r="18" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -3534,7 +3490,7 @@
       <c r="M18" s="14"/>
       <c r="N18" s="14"/>
     </row>
-    <row r="19" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>29</v>
       </c>
@@ -3558,7 +3514,7 @@
       <c r="M19" s="14"/>
       <c r="N19" s="14"/>
     </row>
-    <row r="20" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
@@ -3582,7 +3538,7 @@
       <c r="M20" s="14"/>
       <c r="N20" s="14"/>
     </row>
-    <row r="21" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>21</v>
       </c>
@@ -3606,7 +3562,7 @@
       <c r="M21" s="14"/>
       <c r="N21" s="14"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>28</v>
       </c>
@@ -3630,7 +3586,7 @@
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
@@ -3654,7 +3610,7 @@
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>44</v>
       </c>
@@ -3678,7 +3634,7 @@
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>46</v>
       </c>
@@ -3702,7 +3658,7 @@
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>45</v>
       </c>
@@ -3726,7 +3682,7 @@
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>47</v>
       </c>
@@ -3750,7 +3706,7 @@
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
     </row>
-    <row r="28" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" s="16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>43</v>
       </c>
@@ -3774,7 +3730,7 @@
       <c r="M28" s="17"/>
       <c r="N28" s="17"/>
     </row>
-    <row r="29" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" s="16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>49</v>
       </c>
@@ -3798,7 +3754,7 @@
       <c r="M29" s="17"/>
       <c r="N29" s="17"/>
     </row>
-    <row r="30" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" s="16" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>50</v>
       </c>
@@ -3822,7 +3778,7 @@
       <c r="M30" s="17"/>
       <c r="N30" s="17"/>
     </row>
-    <row r="31" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>19</v>
       </c>
@@ -3845,7 +3801,7 @@
       <c r="L31" s="20"/>
       <c r="M31" s="20"/>
     </row>
-    <row r="32" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>48</v>
       </c>
@@ -3868,7 +3824,7 @@
       <c r="L32" s="20"/>
       <c r="M32" s="20"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>22</v>
       </c>
@@ -3891,7 +3847,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
@@ -3915,7 +3871,7 @@
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
     </row>
-    <row r="35" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>47</v>
       </c>
@@ -3939,7 +3895,7 @@
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>45</v>
       </c>
@@ -3963,7 +3919,7 @@
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>24</v>
       </c>
@@ -3987,7 +3943,7 @@
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
     </row>
-    <row r="38" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" s="23" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>22</v>
       </c>
@@ -4011,7 +3967,7 @@
       <c r="M38" s="24"/>
       <c r="N38" s="24"/>
     </row>
-    <row r="39" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" s="23" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>40</v>
       </c>
@@ -4035,7 +3991,7 @@
       <c r="M39" s="24"/>
       <c r="N39" s="24"/>
     </row>
-    <row r="40" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" s="23" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>31</v>
       </c>
@@ -4059,7 +4015,7 @@
       <c r="M40" s="24"/>
       <c r="N40" s="24"/>
     </row>
-    <row r="41" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" s="23" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>32</v>
       </c>
@@ -4083,7 +4039,7 @@
       <c r="M41" s="24"/>
       <c r="N41" s="24"/>
     </row>
-    <row r="42" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" s="23" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>27</v>
       </c>
@@ -4107,7 +4063,7 @@
       <c r="M42" s="24"/>
       <c r="N42" s="24"/>
     </row>
-    <row r="43" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" s="23" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>36</v>
       </c>
@@ -4131,7 +4087,7 @@
       <c r="M43" s="24"/>
       <c r="N43" s="24"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>33</v>
       </c>
@@ -4155,7 +4111,7 @@
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>26</v>
       </c>
@@ -4179,7 +4135,7 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>38</v>
       </c>
@@ -4203,7 +4159,7 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>39</v>
       </c>
@@ -4227,7 +4183,7 @@
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
     </row>
-    <row r="48" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>46</v>
       </c>
@@ -4251,7 +4207,7 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
     </row>
-    <row r="49" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>2</v>
       </c>
@@ -4275,7 +4231,7 @@
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
     </row>
-    <row r="50" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>21</v>
       </c>
@@ -4299,7 +4255,7 @@
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>28</v>
       </c>
@@ -4323,7 +4279,7 @@
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>29</v>
       </c>
@@ -4347,7 +4303,7 @@
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>30</v>
       </c>
@@ -4371,7 +4327,7 @@
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>35</v>
       </c>
@@ -4395,7 +4351,7 @@
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
     </row>
-    <row r="55" spans="1:14" s="27" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" s="27" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>23</v>
       </c>
@@ -4419,7 +4375,7 @@
       <c r="M55" s="26"/>
       <c r="N55" s="26"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>20</v>
       </c>
@@ -4443,7 +4399,7 @@
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>44</v>
       </c>
@@ -4467,7 +4423,7 @@
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>25</v>
       </c>
@@ -4491,7 +4447,7 @@
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>48</v>
       </c>
@@ -4515,7 +4471,7 @@
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>49</v>
       </c>
@@ -4539,7 +4495,7 @@
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
     </row>
-    <row r="61" spans="1:14" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>16</v>
       </c>
@@ -4563,7 +4519,7 @@
       <c r="M61" s="32"/>
       <c r="N61" s="32"/>
     </row>
-    <row r="62" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>24</v>
       </c>
@@ -4577,7 +4533,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="63" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>43</v>
       </c>
@@ -4591,7 +4547,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>34</v>
       </c>
@@ -4605,7 +4561,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>36</v>
       </c>
@@ -4619,7 +4575,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="66" spans="1:4" s="31" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" s="31" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>28</v>
       </c>
@@ -4633,7 +4589,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="67" spans="1:4" s="31" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" s="31" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>26</v>
       </c>
@@ -4647,7 +4603,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="1:4" s="31" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" s="31" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>31</v>
       </c>
@@ -4661,7 +4617,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="69" spans="1:4" s="31" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" s="31" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>32</v>
       </c>
@@ -4675,7 +4631,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="70" spans="1:4" s="31" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" s="31" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>27</v>
       </c>
@@ -4689,7 +4645,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="71" spans="1:4" s="31" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" s="31" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>33</v>
       </c>
@@ -4703,7 +4659,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>35</v>
       </c>
@@ -4717,7 +4673,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>39</v>
       </c>
@@ -4731,7 +4687,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>38</v>
       </c>
@@ -4745,7 +4701,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="75" spans="1:4" s="5" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" s="5" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
@@ -4759,7 +4715,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="1:4" s="5" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" s="5" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>2</v>
       </c>
@@ -4773,7 +4729,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:4" s="5" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" s="5" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>30</v>
       </c>
@@ -4787,7 +4743,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>19</v>
       </c>
@@ -4801,7 +4757,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>41</v>
       </c>
@@ -4815,7 +4771,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>42</v>
       </c>
@@ -4829,7 +4785,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>44</v>
       </c>
@@ -4843,7 +4799,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>46</v>
       </c>
@@ -4857,7 +4813,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>45</v>
       </c>
@@ -4871,7 +4827,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="84" spans="1:4" s="33" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" s="33" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>47</v>
       </c>
@@ -4885,7 +4841,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="85" spans="1:4" s="33" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" s="33" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>48</v>
       </c>
@@ -4899,7 +4855,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="86" spans="1:4" s="33" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" s="33" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>50</v>
       </c>
@@ -4913,7 +4869,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="87" spans="1:4" s="33" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" s="33" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>49</v>
       </c>
@@ -4927,7 +4883,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="88" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>45</v>
       </c>
@@ -4941,7 +4897,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="89" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>23</v>
       </c>
@@ -4955,7 +4911,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="90" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>20</v>
       </c>
@@ -4969,7 +4925,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="91" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>24</v>
       </c>
@@ -4983,7 +4939,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>32</v>
       </c>
@@ -4997,7 +4953,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>39</v>
       </c>
@@ -5011,7 +4967,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>38</v>
       </c>
@@ -5025,7 +4981,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>30</v>
       </c>
@@ -5039,7 +4995,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>33</v>
       </c>
@@ -5053,7 +5009,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="97" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>44</v>
       </c>
@@ -5067,7 +5023,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>41</v>
       </c>
@@ -5081,7 +5037,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="99" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>47</v>
       </c>
@@ -5095,7 +5051,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="100" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>21</v>
       </c>
@@ -5109,7 +5065,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>36</v>
       </c>
@@ -5123,7 +5079,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>42</v>
       </c>
@@ -5137,7 +5093,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="103" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>28</v>
       </c>
@@ -5151,7 +5107,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="104" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>46</v>
       </c>
@@ -5165,7 +5121,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="105" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>50</v>
       </c>
@@ -5179,7 +5135,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="106" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>25</v>
       </c>
@@ -5193,7 +5149,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>40</v>
       </c>
@@ -5207,7 +5163,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>29</v>
       </c>
@@ -5221,7 +5177,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>26</v>
       </c>
@@ -5235,7 +5191,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>35</v>
       </c>
@@ -5249,7 +5205,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="111" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>31</v>
       </c>
@@ -5263,7 +5219,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>43</v>
       </c>
@@ -5277,7 +5233,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>37</v>
       </c>
@@ -5291,7 +5247,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>49</v>
       </c>
@@ -5305,7 +5261,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="115" spans="1:4" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" s="29" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="28" t="s">
         <v>27</v>
       </c>
@@ -5319,7 +5275,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="116" spans="1:4" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" s="29" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="28" t="s">
         <v>34</v>
       </c>
@@ -5333,7 +5289,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="117" spans="1:4" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" s="29" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="28" t="s">
         <v>17</v>
       </c>
@@ -5347,7 +5303,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="118" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
         <v>2</v>
       </c>
@@ -5361,7 +5317,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>16</v>
       </c>
@@ -5375,7 +5331,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="120" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>18</v>
       </c>
@@ -5389,7 +5345,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="121" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>48</v>
       </c>
@@ -5403,7 +5359,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>42</v>
       </c>
@@ -5414,10 +5370,10 @@
         <v>4</v>
       </c>
       <c r="D122" s="40" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>41</v>
       </c>
@@ -5428,10 +5384,10 @@
         <v>4</v>
       </c>
       <c r="D123" s="40" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>44</v>
       </c>
@@ -5442,10 +5398,10 @@
         <v>4</v>
       </c>
       <c r="D124" s="42" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>29</v>
       </c>
@@ -5456,10 +5412,10 @@
         <v>4</v>
       </c>
       <c r="D125" s="42" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>26</v>
       </c>
@@ -5470,10 +5426,10 @@
         <v>4</v>
       </c>
       <c r="D126" s="40" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>39</v>
       </c>
@@ -5484,10 +5440,10 @@
         <v>4</v>
       </c>
       <c r="D127" s="40" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>30</v>
       </c>
@@ -5498,10 +5454,10 @@
         <v>4</v>
       </c>
       <c r="D128" s="40" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>35</v>
       </c>
@@ -5512,10 +5468,10 @@
         <v>4</v>
       </c>
       <c r="D129" s="40" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>32</v>
       </c>
@@ -5526,10 +5482,10 @@
         <v>4</v>
       </c>
       <c r="D130" s="40" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>33</v>
       </c>
@@ -5540,10 +5496,10 @@
         <v>4</v>
       </c>
       <c r="D131" s="40" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>40</v>
       </c>
@@ -5554,10 +5510,10 @@
         <v>4</v>
       </c>
       <c r="D132" s="40" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>38</v>
       </c>
@@ -5568,10 +5524,10 @@
         <v>4</v>
       </c>
       <c r="D133" s="40" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>37</v>
       </c>
@@ -5582,10 +5538,10 @@
         <v>4</v>
       </c>
       <c r="D134" s="40" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>16</v>
       </c>
@@ -5596,10 +5552,10 @@
         <v>4</v>
       </c>
       <c r="D135" s="40" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
         <v>2</v>
       </c>
@@ -5610,10 +5566,10 @@
         <v>4</v>
       </c>
       <c r="D136" s="40" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>18</v>
       </c>
@@ -5624,10 +5580,10 @@
         <v>4</v>
       </c>
       <c r="D137" s="40" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>25</v>
       </c>
@@ -5641,7 +5597,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>43</v>
       </c>
@@ -5652,10 +5608,10 @@
         <v>4</v>
       </c>
       <c r="D139" s="40" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>31</v>
       </c>
@@ -5666,10 +5622,10 @@
         <v>4</v>
       </c>
       <c r="D140" s="40" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>28</v>
       </c>
@@ -5683,7 +5639,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -5697,7 +5653,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>36</v>
       </c>
@@ -5711,7 +5667,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>34</v>
       </c>
@@ -5725,7 +5681,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>46</v>
       </c>
@@ -5736,10 +5692,10 @@
         <v>4</v>
       </c>
       <c r="D145" s="40" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>45</v>
       </c>
@@ -5753,7 +5709,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>47</v>
       </c>
@@ -5764,10 +5720,10 @@
         <v>4</v>
       </c>
       <c r="D147" s="40" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>19</v>
       </c>
@@ -5778,10 +5734,10 @@
         <v>4</v>
       </c>
       <c r="D148" s="40" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>50</v>
       </c>
@@ -5792,10 +5748,10 @@
         <v>4</v>
       </c>
       <c r="D149" s="40" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>48</v>
       </c>
@@ -5806,10 +5762,10 @@
         <v>4</v>
       </c>
       <c r="D150" s="40" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>49</v>
       </c>
@@ -5820,10 +5776,10 @@
         <v>4</v>
       </c>
       <c r="D151" s="40" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>20</v>
       </c>
@@ -5834,10 +5790,10 @@
         <v>4</v>
       </c>
       <c r="D152" s="40" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>21</v>
       </c>
@@ -5848,10 +5804,10 @@
         <v>4</v>
       </c>
       <c r="D153" s="40" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>22</v>
       </c>
@@ -5862,10 +5818,10 @@
         <v>4</v>
       </c>
       <c r="D154" s="40" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" s="35" customFormat="1" x14ac:dyDescent="0.25">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>23</v>
       </c>
@@ -5876,10 +5832,10 @@
         <v>4</v>
       </c>
       <c r="D155" s="40" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>41</v>
       </c>
@@ -5893,7 +5849,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="157" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>16</v>
       </c>
@@ -5907,7 +5863,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="158" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
         <v>2</v>
       </c>
@@ -5921,7 +5877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
         <v>18</v>
       </c>
@@ -5935,7 +5891,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="160" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>24</v>
       </c>
@@ -5949,7 +5905,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="161" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>25</v>
       </c>
@@ -5960,10 +5916,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>44</v>
       </c>
@@ -5977,7 +5933,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="163" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>38</v>
       </c>
@@ -5991,7 +5947,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="164" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>39</v>
       </c>
@@ -6005,7 +5961,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="165" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>26</v>
       </c>
@@ -6019,7 +5975,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="166" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>28</v>
       </c>
@@ -6033,7 +5989,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="167" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>27</v>
       </c>
@@ -6047,7 +6003,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="168" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>29</v>
       </c>
@@ -6061,7 +6017,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="169" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>31</v>
       </c>
@@ -6072,10 +6028,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="38" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>35</v>
       </c>
@@ -6089,7 +6045,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>36</v>
       </c>
@@ -6103,7 +6059,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>33</v>
       </c>
@@ -6117,7 +6073,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>34</v>
       </c>
@@ -6131,7 +6087,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>37</v>
       </c>
@@ -6145,7 +6101,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="175" spans="1:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
         <v>46</v>
       </c>
@@ -6159,7 +6115,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="176" spans="1:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>45</v>
       </c>
@@ -6173,7 +6129,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="177" spans="1:4" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>19</v>
       </c>
@@ -6187,7 +6143,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="178" spans="1:4" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>42</v>
       </c>
@@ -6201,7 +6157,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="179" spans="1:4" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>43</v>
       </c>
@@ -6212,10 +6168,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>48</v>
       </c>
@@ -6229,7 +6185,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="181" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>50</v>
       </c>
@@ -6240,10 +6196,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>47</v>
       </c>
@@ -6257,7 +6213,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>20</v>
       </c>
@@ -6271,7 +6227,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="184" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>21</v>
       </c>
@@ -6285,7 +6241,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="185" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>40</v>
       </c>
@@ -6299,7 +6255,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="186" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>49</v>
       </c>
@@ -6313,7 +6269,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>22</v>
       </c>
@@ -6324,10 +6280,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>23</v>
       </c>
@@ -6341,7 +6297,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
         <v>200</v>
       </c>
@@ -6355,7 +6311,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>202</v>
       </c>
@@ -6366,10 +6322,10 @@
         <v>8</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>203</v>
       </c>
@@ -6383,7 +6339,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>205</v>
       </c>
@@ -6397,7 +6353,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="193" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
         <v>207</v>
       </c>
@@ -6411,7 +6367,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="194" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>209</v>
       </c>
@@ -6425,7 +6381,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="195" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
         <v>211</v>
       </c>
@@ -6439,7 +6395,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="196" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>213</v>
       </c>
@@ -6453,7 +6409,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="197" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
         <v>215</v>
       </c>
@@ -6467,7 +6423,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
         <v>217</v>
       </c>
@@ -6481,7 +6437,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
         <v>219</v>
       </c>
@@ -6495,7 +6451,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>221</v>
       </c>
@@ -6509,7 +6465,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>223</v>
       </c>
@@ -6523,7 +6479,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
         <v>225</v>
       </c>
@@ -6537,7 +6493,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>227</v>
       </c>
@@ -6551,7 +6507,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="204" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
         <v>229</v>
       </c>
@@ -6565,7 +6521,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="205" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
         <v>231</v>
       </c>
@@ -6579,7 +6535,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="206" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>233</v>
       </c>
@@ -6593,7 +6549,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="207" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
         <v>235</v>
       </c>
@@ -6607,7 +6563,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="208" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>237</v>
       </c>
@@ -6621,7 +6577,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="209" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
         <v>239</v>
       </c>
@@ -6635,7 +6591,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="210" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
         <v>241</v>
       </c>
@@ -6649,7 +6605,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="211" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
         <v>243</v>
       </c>
@@ -6660,10 +6616,10 @@
         <v>8</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>244</v>
       </c>
@@ -6677,7 +6633,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="213" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
         <v>246</v>
       </c>
@@ -6691,7 +6647,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="214" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
         <v>248</v>
       </c>
@@ -6705,7 +6661,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="215" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
         <v>250</v>
       </c>
@@ -6719,7 +6675,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>252</v>
       </c>
@@ -6733,7 +6689,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
         <v>254</v>
       </c>
@@ -6747,7 +6703,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
         <v>256</v>
       </c>
@@ -6761,7 +6717,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
         <v>258</v>
       </c>
@@ -6775,7 +6731,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
         <v>20</v>
       </c>
@@ -6789,7 +6745,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
         <v>261</v>
       </c>
@@ -6803,7 +6759,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="222" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
         <v>263</v>
       </c>
@@ -6817,7 +6773,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="223" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
         <v>265</v>
       </c>
@@ -6831,7 +6787,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="224" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
         <v>267</v>
       </c>
@@ -6845,7 +6801,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="225" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
         <v>23</v>
       </c>
@@ -6859,7 +6815,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="226" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
         <v>270</v>
       </c>
@@ -6873,7 +6829,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="227" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
         <v>272</v>
       </c>
@@ -6887,7 +6843,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="228" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>274</v>
       </c>
@@ -6901,7 +6857,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="229" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
         <v>276</v>
       </c>
@@ -6915,7 +6871,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="230" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>278</v>
       </c>
@@ -6929,7 +6885,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="231" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
         <v>280</v>
       </c>
@@ -6943,7 +6899,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="232" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
         <v>282</v>
       </c>
@@ -6957,7 +6913,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="233" spans="1:4" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" s="13" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
         <v>284</v>
       </c>
@@ -6971,7 +6927,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>286</v>
       </c>
@@ -6985,7 +6941,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
         <v>288</v>
       </c>
@@ -6999,7 +6955,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
         <v>290</v>
       </c>
@@ -7013,7 +6969,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>292</v>
       </c>
@@ -7027,7 +6983,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
         <v>294</v>
       </c>
@@ -7041,7 +6997,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
         <v>296</v>
       </c>
@@ -7055,7 +7011,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="240" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>298</v>
       </c>
@@ -7069,7 +7025,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="241" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
         <v>300</v>
       </c>
@@ -7083,7 +7039,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="242" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
         <v>302</v>
       </c>
@@ -7097,7 +7053,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="243" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
         <v>304</v>
       </c>
@@ -7111,7 +7067,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="244" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
         <v>306</v>
       </c>
@@ -7125,7 +7081,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="245" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
         <v>308</v>
       </c>
@@ -7139,7 +7095,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
         <v>310</v>
       </c>
@@ -7153,7 +7109,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
         <v>312</v>
       </c>
@@ -7167,7 +7123,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
         <v>314</v>
       </c>
@@ -7181,7 +7137,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
         <v>24</v>
       </c>
@@ -7192,10 +7148,10 @@
         <v>4</v>
       </c>
       <c r="D249" s="40" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
         <v>200</v>
       </c>
@@ -7206,10 +7162,10 @@
         <v>4</v>
       </c>
       <c r="D250" s="40" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
         <v>202</v>
       </c>
@@ -7220,10 +7176,10 @@
         <v>4</v>
       </c>
       <c r="D251" s="40" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
         <v>203</v>
       </c>
@@ -7237,7 +7193,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
         <v>317</v>
       </c>
@@ -7248,10 +7204,10 @@
         <v>4</v>
       </c>
       <c r="D253" s="40" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
         <v>207</v>
       </c>
@@ -7262,10 +7218,10 @@
         <v>4</v>
       </c>
       <c r="D254" s="40" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
         <v>209</v>
       </c>
@@ -7276,10 +7232,10 @@
         <v>4</v>
       </c>
       <c r="D255" s="40" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
         <v>211</v>
       </c>
@@ -7290,10 +7246,10 @@
         <v>4</v>
       </c>
       <c r="D256" s="40" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
         <v>213</v>
       </c>
@@ -7304,10 +7260,10 @@
         <v>4</v>
       </c>
       <c r="D257" s="40" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
         <v>215</v>
       </c>
@@ -7321,7 +7277,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
         <v>217</v>
       </c>
@@ -7332,10 +7288,10 @@
         <v>4</v>
       </c>
       <c r="D259" s="40" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
         <v>219</v>
       </c>
@@ -7346,10 +7302,10 @@
         <v>4</v>
       </c>
       <c r="D260" s="40" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
         <v>221</v>
       </c>
@@ -7360,10 +7316,10 @@
         <v>4</v>
       </c>
       <c r="D261" s="40" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
         <v>223</v>
       </c>
@@ -7374,10 +7330,10 @@
         <v>4</v>
       </c>
       <c r="D262" s="40" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
         <v>225</v>
       </c>
@@ -7391,7 +7347,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
         <v>227</v>
       </c>
@@ -7402,10 +7358,10 @@
         <v>4</v>
       </c>
       <c r="D264" s="40" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
         <v>320</v>
       </c>
@@ -7416,10 +7372,10 @@
         <v>4</v>
       </c>
       <c r="D265" s="40" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
         <v>229</v>
       </c>
@@ -7430,10 +7386,10 @@
         <v>4</v>
       </c>
       <c r="D266" s="40" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
         <v>231</v>
       </c>
@@ -7444,10 +7400,10 @@
         <v>4</v>
       </c>
       <c r="D267" s="40" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
         <v>237</v>
       </c>
@@ -7458,10 +7414,10 @@
         <v>4</v>
       </c>
       <c r="D268" s="40" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
         <v>239</v>
       </c>
@@ -7472,10 +7428,10 @@
         <v>4</v>
       </c>
       <c r="D269" s="40" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
         <v>241</v>
       </c>
@@ -7486,10 +7442,10 @@
         <v>4</v>
       </c>
       <c r="D270" s="40" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
         <v>243</v>
       </c>
@@ -7500,10 +7456,10 @@
         <v>4</v>
       </c>
       <c r="D271" s="40" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
         <v>244</v>
       </c>
@@ -7514,10 +7470,10 @@
         <v>4</v>
       </c>
       <c r="D272" s="40" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
         <v>246</v>
       </c>
@@ -7528,10 +7484,10 @@
         <v>4</v>
       </c>
       <c r="D273" s="40" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
         <v>248</v>
       </c>
@@ -7542,10 +7498,10 @@
         <v>4</v>
       </c>
       <c r="D274" s="40" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
         <v>250</v>
       </c>
@@ -7556,10 +7512,10 @@
         <v>4</v>
       </c>
       <c r="D275" s="40" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
         <v>252</v>
       </c>
@@ -7573,7 +7529,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
         <v>254</v>
       </c>
@@ -7587,7 +7543,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
         <v>323</v>
       </c>
@@ -7601,7 +7557,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
         <v>256</v>
       </c>
@@ -7612,10 +7568,10 @@
         <v>4</v>
       </c>
       <c r="D279" s="40" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
         <v>258</v>
       </c>
@@ -7626,10 +7582,10 @@
         <v>4</v>
       </c>
       <c r="D280" s="40" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
         <v>261</v>
       </c>
@@ -7640,10 +7596,10 @@
         <v>4</v>
       </c>
       <c r="D281" s="40" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
         <v>325</v>
       </c>
@@ -7654,10 +7610,10 @@
         <v>4</v>
       </c>
       <c r="D282" s="40" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
         <v>263</v>
       </c>
@@ -7668,10 +7624,10 @@
         <v>4</v>
       </c>
       <c r="D283" s="40" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
         <v>265</v>
       </c>
@@ -7682,10 +7638,10 @@
         <v>4</v>
       </c>
       <c r="D284" s="40" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
         <v>267</v>
       </c>
@@ -7696,10 +7652,10 @@
         <v>4</v>
       </c>
       <c r="D285" s="40" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
         <v>270</v>
       </c>
@@ -7710,10 +7666,10 @@
         <v>4</v>
       </c>
       <c r="D286" s="40" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
         <v>272</v>
       </c>
@@ -7724,10 +7680,10 @@
         <v>4</v>
       </c>
       <c r="D287" s="40" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
         <v>274</v>
       </c>
@@ -7738,10 +7694,10 @@
         <v>4</v>
       </c>
       <c r="D288" s="40" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
         <v>276</v>
       </c>
@@ -7752,10 +7708,10 @@
         <v>4</v>
       </c>
       <c r="D289" s="40" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
         <v>278</v>
       </c>
@@ -7766,10 +7722,10 @@
         <v>4</v>
       </c>
       <c r="D290" s="40" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
         <v>280</v>
       </c>
@@ -7780,10 +7736,10 @@
         <v>4</v>
       </c>
       <c r="D291" s="40" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
         <v>282</v>
       </c>
@@ -7794,10 +7750,10 @@
         <v>4</v>
       </c>
       <c r="D292" s="40" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
         <v>326</v>
       </c>
@@ -7811,7 +7767,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
         <v>328</v>
       </c>
@@ -7822,10 +7778,10 @@
         <v>4</v>
       </c>
       <c r="D294" s="40" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
         <v>284</v>
       </c>
@@ -7836,10 +7792,10 @@
         <v>4</v>
       </c>
       <c r="D295" s="40" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
         <v>286</v>
       </c>
@@ -7850,10 +7806,10 @@
         <v>4</v>
       </c>
       <c r="D296" s="40" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
         <v>329</v>
       </c>
@@ -7864,10 +7820,10 @@
         <v>4</v>
       </c>
       <c r="D297" s="40" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
         <v>330</v>
       </c>
@@ -7878,10 +7834,10 @@
         <v>4</v>
       </c>
       <c r="D298" s="40" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
         <v>290</v>
       </c>
@@ -7892,10 +7848,10 @@
         <v>4</v>
       </c>
       <c r="D299" s="40" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
         <v>292</v>
       </c>
@@ -7909,7 +7865,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
         <v>294</v>
       </c>
@@ -7923,7 +7879,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
         <v>296</v>
       </c>
@@ -7937,7 +7893,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
         <v>298</v>
       </c>
@@ -7951,7 +7907,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
         <v>302</v>
       </c>
@@ -7962,10 +7918,10 @@
         <v>4</v>
       </c>
       <c r="D304" s="40" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
         <v>304</v>
       </c>
@@ -7976,10 +7932,10 @@
         <v>4</v>
       </c>
       <c r="D305" s="40" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
         <v>306</v>
       </c>
@@ -7993,7 +7949,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
         <v>308</v>
       </c>
@@ -8007,7 +7963,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
         <v>310</v>
       </c>
@@ -8021,7 +7977,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="3" t="s">
         <v>314</v>
       </c>
@@ -8035,7 +7991,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="310" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
         <v>202</v>
       </c>
@@ -8049,7 +8005,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="311" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
         <v>205</v>
       </c>
@@ -8063,7 +8019,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="312" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
         <v>207</v>
       </c>
@@ -8077,7 +8033,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="313" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="3" t="s">
         <v>209</v>
       </c>
@@ -8091,7 +8047,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="314" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
         <v>211</v>
       </c>
@@ -8105,7 +8061,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="315" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
         <v>213</v>
       </c>
@@ -8119,7 +8075,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="316" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
         <v>215</v>
       </c>
@@ -8133,7 +8089,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="317" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
         <v>217</v>
       </c>
@@ -8147,7 +8103,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="318" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
         <v>219</v>
       </c>
@@ -8161,7 +8117,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="319" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
         <v>221</v>
       </c>
@@ -8175,7 +8131,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="320" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
         <v>37</v>
       </c>
@@ -8189,7 +8145,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="321" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
         <v>225</v>
       </c>
@@ -8203,7 +8159,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="322" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="3" t="s">
         <v>227</v>
       </c>
@@ -8217,7 +8173,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="323" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="3" t="s">
         <v>320</v>
       </c>
@@ -8231,7 +8187,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="324" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
         <v>237</v>
       </c>
@@ -8245,7 +8201,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="3" t="s">
         <v>241</v>
       </c>
@@ -8259,7 +8215,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
         <v>244</v>
       </c>
@@ -8273,7 +8229,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="3" t="s">
         <v>246</v>
       </c>
@@ -8287,7 +8243,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="3" t="s">
         <v>248</v>
       </c>
@@ -8301,7 +8257,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="3" t="s">
         <v>18</v>
       </c>
@@ -8315,7 +8271,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="3" t="s">
         <v>252</v>
       </c>
@@ -8329,7 +8285,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="3" t="s">
         <v>254</v>
       </c>
@@ -8343,7 +8299,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="3" t="s">
         <v>323</v>
       </c>
@@ -8357,7 +8313,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="3" t="s">
         <v>256</v>
       </c>
@@ -8371,7 +8327,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="3" t="s">
         <v>258</v>
       </c>
@@ -8385,7 +8341,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="3" t="s">
         <v>261</v>
       </c>
@@ -8399,7 +8355,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
         <v>325</v>
       </c>
@@ -8413,7 +8369,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="3" t="s">
         <v>265</v>
       </c>
@@ -8427,7 +8383,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
         <v>267</v>
       </c>
@@ -8441,7 +8397,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
         <v>272</v>
       </c>
@@ -8455,7 +8411,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
         <v>274</v>
       </c>
@@ -8469,7 +8425,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="3" t="s">
         <v>276</v>
       </c>
@@ -8483,7 +8439,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="3" t="s">
         <v>278</v>
       </c>
@@ -8497,7 +8453,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="3" t="s">
         <v>373</v>
       </c>
@@ -8511,7 +8467,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
         <v>375</v>
       </c>
@@ -8525,7 +8481,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="3" t="s">
         <v>377</v>
       </c>
@@ -8539,7 +8495,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="3" t="s">
         <v>280</v>
       </c>
@@ -8553,7 +8509,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="3" t="s">
         <v>282</v>
       </c>
@@ -8567,7 +8523,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
         <v>326</v>
       </c>
@@ -8581,7 +8537,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="3" t="s">
         <v>328</v>
       </c>
@@ -8595,7 +8551,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
         <v>292</v>
       </c>
@@ -8609,7 +8565,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="3" t="s">
         <v>294</v>
       </c>
@@ -8623,7 +8579,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
         <v>296</v>
       </c>
@@ -8637,7 +8593,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="3" t="s">
         <v>298</v>
       </c>
@@ -8651,7 +8607,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
         <v>200</v>
       </c>
@@ -8665,7 +8621,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="3" t="s">
         <v>202</v>
       </c>
@@ -8679,7 +8635,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
         <v>203</v>
       </c>
@@ -8693,7 +8649,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="3" t="s">
         <v>211</v>
       </c>
@@ -8707,7 +8663,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
         <v>213</v>
       </c>
@@ -8721,7 +8677,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="3" t="s">
         <v>215</v>
       </c>
@@ -8735,7 +8691,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
         <v>217</v>
       </c>
@@ -8749,7 +8705,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="3" t="s">
         <v>219</v>
       </c>
@@ -8763,7 +8719,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
         <v>221</v>
       </c>
@@ -8777,7 +8733,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="3" t="s">
         <v>223</v>
       </c>
@@ -8791,7 +8747,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="3" t="s">
         <v>225</v>
       </c>
@@ -8805,7 +8761,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
         <v>227</v>
       </c>
@@ -8819,7 +8775,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
         <v>320</v>
       </c>
@@ -8833,7 +8789,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="3" t="s">
         <v>229</v>
       </c>
@@ -8847,7 +8803,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
         <v>231</v>
       </c>
@@ -8861,7 +8817,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="3" t="s">
         <v>235</v>
       </c>
@@ -8875,7 +8831,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
         <v>237</v>
       </c>
@@ -8889,7 +8845,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="3" t="s">
         <v>239</v>
       </c>
@@ -8903,7 +8859,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
         <v>241</v>
       </c>
@@ -8917,7 +8873,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="3" t="s">
         <v>243</v>
       </c>
@@ -8931,7 +8887,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
         <v>244</v>
       </c>
@@ -8945,7 +8901,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="3" t="s">
         <v>246</v>
       </c>
@@ -8959,7 +8915,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
         <v>248</v>
       </c>
@@ -8973,7 +8929,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
         <v>250</v>
       </c>
@@ -8987,7 +8943,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
         <v>252</v>
       </c>
@@ -9001,7 +8957,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="3" t="s">
         <v>254</v>
       </c>
@@ -9015,7 +8971,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
         <v>323</v>
       </c>
@@ -9029,7 +8985,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="3" t="s">
         <v>256</v>
       </c>
@@ -9043,7 +8999,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="3" t="s">
         <v>19</v>
       </c>
@@ -9057,7 +9013,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="3" t="s">
         <v>22</v>
       </c>
@@ -9071,7 +9027,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="3" t="s">
         <v>261</v>
       </c>
@@ -9085,7 +9041,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="3" t="s">
         <v>325</v>
       </c>
@@ -9099,7 +9055,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="3" t="s">
         <v>265</v>
       </c>
@@ -9113,7 +9069,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="3" t="s">
         <v>267</v>
       </c>
@@ -9127,7 +9083,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="3" t="s">
         <v>270</v>
       </c>
@@ -9141,7 +9097,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="3" t="s">
         <v>272</v>
       </c>
@@ -9155,7 +9111,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="3" t="s">
         <v>278</v>
       </c>
@@ -9169,7 +9125,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="3" t="s">
         <v>280</v>
       </c>
@@ -9183,7 +9139,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="3" t="s">
         <v>282</v>
       </c>
@@ -9197,7 +9153,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="3" t="s">
         <v>326</v>
       </c>
@@ -9211,7 +9167,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="3" t="s">
         <v>292</v>
       </c>
@@ -9225,7 +9181,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="3" t="s">
         <v>296</v>
       </c>
@@ -9239,7 +9195,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
         <v>306</v>
       </c>
@@ -9253,7 +9209,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="3" t="s">
         <v>308</v>
       </c>
@@ -9267,7 +9223,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="3" t="s">
         <v>310</v>
       </c>
@@ -9281,7 +9237,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="3" t="s">
         <v>314</v>
       </c>
@@ -9295,7 +9251,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="3" t="s">
         <v>200</v>
       </c>
@@ -9309,7 +9265,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="3" t="s">
         <v>203</v>
       </c>
@@ -9323,7 +9279,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="3" t="s">
         <v>205</v>
       </c>
@@ -9337,7 +9293,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="3" t="s">
         <v>209</v>
       </c>
@@ -9351,7 +9307,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="3" t="s">
         <v>32</v>
       </c>
@@ -9365,7 +9321,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="3" t="s">
         <v>211</v>
       </c>
@@ -9379,7 +9335,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="3" t="s">
         <v>215</v>
       </c>
@@ -9393,7 +9349,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="3" t="s">
         <v>217</v>
       </c>
@@ -9404,10 +9360,10 @@
         <v>3</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="3" t="s">
         <v>219</v>
       </c>
@@ -9421,7 +9377,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="3" t="s">
         <v>221</v>
       </c>
@@ -9435,7 +9391,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="3" t="s">
         <v>223</v>
       </c>
@@ -9446,10 +9402,10 @@
         <v>3</v>
       </c>
       <c r="D410" s="38" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="3" t="s">
         <v>225</v>
       </c>
@@ -9463,7 +9419,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="3" t="s">
         <v>227</v>
       </c>
@@ -9477,7 +9433,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="3" t="s">
         <v>30</v>
       </c>
@@ -9491,7 +9447,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="3" t="s">
         <v>320</v>
       </c>
@@ -9505,7 +9461,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="3" t="s">
         <v>229</v>
       </c>
@@ -9519,7 +9475,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="3" t="s">
         <v>231</v>
       </c>
@@ -9533,7 +9489,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="3" t="s">
         <v>235</v>
       </c>
@@ -9544,10 +9500,10 @@
         <v>3</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="3" t="s">
         <v>237</v>
       </c>
@@ -9561,7 +9517,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="3" t="s">
         <v>239</v>
       </c>
@@ -9575,7 +9531,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="3" t="s">
         <v>241</v>
       </c>
@@ -9586,10 +9542,10 @@
         <v>3</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="3" t="s">
         <v>243</v>
       </c>
@@ -9603,7 +9559,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="3" t="s">
         <v>244</v>
       </c>
@@ -9617,7 +9573,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="3" t="s">
         <v>246</v>
       </c>
@@ -9628,10 +9584,10 @@
         <v>3</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="3" t="s">
         <v>248</v>
       </c>
@@ -9645,7 +9601,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="3" t="s">
         <v>323</v>
       </c>
@@ -9659,7 +9615,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="3" t="s">
         <v>256</v>
       </c>
@@ -9673,7 +9629,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="3" t="s">
         <v>258</v>
       </c>
@@ -9687,7 +9643,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="3" t="s">
         <v>261</v>
       </c>
@@ -9698,10 +9654,10 @@
         <v>3</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="3" t="s">
         <v>263</v>
       </c>
@@ -9715,7 +9671,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="3" t="s">
         <v>265</v>
       </c>
@@ -9729,7 +9685,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="3" t="s">
         <v>270</v>
       </c>
@@ -9743,7 +9699,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="3" t="s">
         <v>272</v>
       </c>
@@ -9757,7 +9713,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="3" t="s">
         <v>274</v>
       </c>
@@ -9771,7 +9727,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="3" t="s">
         <v>276</v>
       </c>
@@ -9785,7 +9741,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="3" t="s">
         <v>278</v>
       </c>
@@ -9796,10 +9752,10 @@
         <v>3</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="3" t="s">
         <v>280</v>
       </c>
@@ -9813,7 +9769,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="3" t="s">
         <v>282</v>
       </c>
@@ -9827,7 +9783,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="3" t="s">
         <v>326</v>
       </c>
@@ -9841,7 +9797,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="3" t="s">
         <v>328</v>
       </c>
@@ -9852,10 +9808,10 @@
         <v>3</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="3" t="s">
         <v>286</v>
       </c>
@@ -9869,7 +9825,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="3" t="s">
         <v>290</v>
       </c>
@@ -9880,10 +9836,10 @@
         <v>3</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="3" t="s">
         <v>292</v>
       </c>
@@ -9897,7 +9853,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="3" t="s">
         <v>296</v>
       </c>
@@ -9911,7 +9867,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="3" t="s">
         <v>302</v>
       </c>
@@ -9922,10 +9878,10 @@
         <v>3</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="3" t="s">
         <v>306</v>
       </c>
@@ -9939,7 +9895,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="3" t="s">
         <v>308</v>
       </c>
@@ -9953,7 +9909,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="3" t="s">
         <v>310</v>
       </c>
@@ -9967,7 +9923,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="3" t="s">
         <v>314</v>
       </c>
@@ -9981,7 +9937,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="3" t="s">
         <v>200</v>
       </c>
@@ -9995,7 +9951,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="3" t="s">
         <v>205</v>
       </c>
@@ -10009,7 +9965,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="3" t="s">
         <v>209</v>
       </c>
@@ -10023,7 +9979,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="3" t="s">
         <v>211</v>
       </c>
@@ -10037,7 +9993,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="3" t="s">
         <v>213</v>
       </c>
@@ -10051,7 +10007,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="3" t="s">
         <v>215</v>
       </c>
@@ -10065,7 +10021,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="3" t="s">
         <v>221</v>
       </c>
@@ -10079,7 +10035,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="3" t="s">
         <v>225</v>
       </c>
@@ -10093,7 +10049,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="3" t="s">
         <v>227</v>
       </c>
@@ -10107,7 +10063,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="3" t="s">
         <v>40</v>
       </c>
@@ -10118,10 +10074,10 @@
         <v>5</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="3" t="s">
         <v>29</v>
       </c>
@@ -10135,7 +10091,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="3" t="s">
         <v>320</v>
       </c>
@@ -10149,7 +10105,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="3" t="s">
         <v>235</v>
       </c>
@@ -10163,7 +10119,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="3" t="s">
         <v>237</v>
       </c>
@@ -10177,7 +10133,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="3" t="s">
         <v>241</v>
       </c>
@@ -10191,7 +10147,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="3" t="s">
         <v>21</v>
       </c>
@@ -10205,7 +10161,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="3" t="s">
         <v>244</v>
       </c>
@@ -10219,7 +10175,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="3" t="s">
         <v>246</v>
       </c>
@@ -10233,7 +10189,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="3" t="s">
         <v>248</v>
       </c>
@@ -10247,7 +10203,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="3" t="s">
         <v>250</v>
       </c>
@@ -10261,7 +10217,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="3" t="s">
         <v>18</v>
       </c>
@@ -10272,10 +10228,10 @@
         <v>5</v>
       </c>
       <c r="D469" s="3" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="3" t="s">
         <v>16</v>
       </c>
@@ -10289,7 +10245,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="3" t="s">
         <v>252</v>
       </c>
@@ -10303,7 +10259,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="3" t="s">
         <v>254</v>
       </c>
@@ -10317,7 +10273,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="3" t="s">
         <v>323</v>
       </c>
@@ -10331,7 +10287,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="3" t="s">
         <v>256</v>
       </c>
@@ -10345,7 +10301,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="3" t="s">
         <v>258</v>
       </c>
@@ -10359,7 +10315,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="3" t="s">
         <v>22</v>
       </c>
@@ -10373,7 +10329,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="3" t="s">
         <v>20</v>
       </c>
@@ -10387,7 +10343,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="3" t="s">
         <v>261</v>
       </c>
@@ -10401,7 +10357,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="3" t="s">
         <v>263</v>
       </c>
@@ -10415,7 +10371,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="3" t="s">
         <v>265</v>
       </c>
@@ -10429,7 +10385,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="3" t="s">
         <v>23</v>
       </c>
@@ -10443,7 +10399,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="3" t="s">
         <v>270</v>
       </c>
@@ -10457,7 +10413,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="3" t="s">
         <v>272</v>
       </c>
@@ -10471,7 +10427,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="3" t="s">
         <v>274</v>
       </c>
@@ -10482,10 +10438,10 @@
         <v>5</v>
       </c>
       <c r="D484" s="3" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="3" t="s">
         <v>278</v>
       </c>
@@ -10499,7 +10455,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="3" t="s">
         <v>282</v>
       </c>
@@ -10513,7 +10469,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="3" t="s">
         <v>292</v>
       </c>
@@ -10527,7 +10483,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="3" t="s">
         <v>296</v>
       </c>
@@ -10541,7 +10497,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="3" t="s">
         <v>335</v>
       </c>
@@ -10555,7 +10511,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="3" t="s">
         <v>306</v>
       </c>
@@ -10569,7 +10525,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="3" t="s">
         <v>308</v>
       </c>
@@ -10583,7 +10539,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="3" t="s">
         <v>310</v>
       </c>
@@ -10597,7 +10553,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="3" t="s">
         <v>314</v>
       </c>
@@ -10611,7 +10567,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="3" t="s">
         <v>24</v>
       </c>
@@ -10625,7 +10581,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="3" t="s">
         <v>43</v>
       </c>
@@ -10639,7 +10595,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="3" t="s">
         <v>34</v>
       </c>
@@ -10653,7 +10609,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="3" t="s">
         <v>36</v>
       </c>
@@ -10667,7 +10623,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="3" t="s">
         <v>28</v>
       </c>
@@ -10681,7 +10637,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="3" t="s">
         <v>26</v>
       </c>
@@ -10695,7 +10651,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="3" t="s">
         <v>31</v>
       </c>
@@ -10709,7 +10665,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="3" t="s">
         <v>32</v>
       </c>
@@ -10723,7 +10679,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="3" t="s">
         <v>27</v>
       </c>
@@ -10737,7 +10693,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="3" t="s">
         <v>33</v>
       </c>
@@ -10751,7 +10707,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="3" t="s">
         <v>35</v>
       </c>
@@ -10765,7 +10721,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="3" t="s">
         <v>39</v>
       </c>
@@ -10779,7 +10735,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="3" t="s">
         <v>38</v>
       </c>
@@ -10793,7 +10749,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="3" t="s">
         <v>30</v>
       </c>
@@ -10807,7 +10763,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="3" t="s">
         <v>19</v>
       </c>
@@ -10821,7 +10777,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="3" t="s">
         <v>41</v>
       </c>
@@ -10835,7 +10791,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="3" t="s">
         <v>42</v>
       </c>
@@ -10849,7 +10805,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="3" t="s">
         <v>44</v>
       </c>
@@ -10863,7 +10819,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="3" t="s">
         <v>46</v>
       </c>
@@ -10877,7 +10833,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="3" t="s">
         <v>45</v>
       </c>
@@ -10891,7 +10847,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="3" t="s">
         <v>47</v>
       </c>
@@ -10905,7 +10861,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="3" t="s">
         <v>48</v>
       </c>
@@ -10919,7 +10875,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="3" t="s">
         <v>50</v>
       </c>
@@ -10933,7 +10889,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="3" t="s">
         <v>49</v>
       </c>
@@ -10947,7 +10903,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="3" t="s">
         <v>200</v>
       </c>
@@ -10961,7 +10917,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="3" t="s">
         <v>202</v>
       </c>
@@ -10975,7 +10931,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="3" t="s">
         <v>205</v>
       </c>
@@ -10989,7 +10945,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="3" t="s">
         <v>209</v>
       </c>
@@ -11003,7 +10959,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="3" t="s">
         <v>211</v>
       </c>
@@ -11017,7 +10973,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="3" t="s">
         <v>213</v>
       </c>
@@ -11031,7 +10987,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="3" t="s">
         <v>215</v>
       </c>
@@ -11045,7 +11001,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="3" t="s">
         <v>221</v>
       </c>
@@ -11059,7 +11015,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="3" t="s">
         <v>225</v>
       </c>
@@ -11073,7 +11029,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="3" t="s">
         <v>227</v>
       </c>
@@ -11087,7 +11043,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="3" t="s">
         <v>40</v>
       </c>
@@ -11101,7 +11057,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="3" t="s">
         <v>29</v>
       </c>
@@ -11115,7 +11071,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="3" t="s">
         <v>235</v>
       </c>
@@ -11129,7 +11085,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="3" t="s">
         <v>237</v>
       </c>
@@ -11143,7 +11099,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="3" t="s">
         <v>241</v>
       </c>
@@ -11157,7 +11113,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="3" t="s">
         <v>21</v>
       </c>
@@ -11171,7 +11127,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="3" t="s">
         <v>244</v>
       </c>
@@ -11185,7 +11141,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="3" t="s">
         <v>246</v>
       </c>
@@ -11199,7 +11155,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="3" t="s">
         <v>248</v>
       </c>
@@ -11213,7 +11169,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="3" t="s">
         <v>250</v>
       </c>
@@ -11227,7 +11183,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="3" t="s">
         <v>18</v>
       </c>
@@ -11241,7 +11197,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="3" t="s">
         <v>16</v>
       </c>
@@ -11255,7 +11211,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="3" t="s">
         <v>252</v>
       </c>
@@ -11269,7 +11225,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="3" t="s">
         <v>254</v>
       </c>
@@ -11283,7 +11239,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="3" t="s">
         <v>323</v>
       </c>
@@ -11297,7 +11253,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="3" t="s">
         <v>256</v>
       </c>
@@ -11311,7 +11267,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="3" t="s">
         <v>22</v>
       </c>
@@ -11325,7 +11281,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="3" t="s">
         <v>20</v>
       </c>
@@ -11339,7 +11295,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="3" t="s">
         <v>261</v>
       </c>
@@ -11353,7 +11309,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="3" t="s">
         <v>263</v>
       </c>
@@ -11367,7 +11323,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="3" t="s">
         <v>265</v>
       </c>
@@ -11381,7 +11337,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="3" t="s">
         <v>23</v>
       </c>
@@ -11395,7 +11351,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="3" t="s">
         <v>270</v>
       </c>
@@ -11409,7 +11365,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="3" t="s">
         <v>272</v>
       </c>
@@ -11423,7 +11379,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="3" t="s">
         <v>278</v>
       </c>
@@ -11437,7 +11393,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="3" t="s">
         <v>282</v>
       </c>
@@ -11451,7 +11407,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="3" t="s">
         <v>292</v>
       </c>
@@ -11465,7 +11421,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="3" t="s">
         <v>296</v>
       </c>
@@ -11479,7 +11435,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="3" t="s">
         <v>335</v>
       </c>
@@ -11493,7 +11449,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="3" t="s">
         <v>306</v>
       </c>
@@ -11507,7 +11463,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="3" t="s">
         <v>308</v>
       </c>
@@ -11521,7 +11477,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="3" t="s">
         <v>310</v>
       </c>
@@ -11535,7 +11491,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="3" t="s">
         <v>314</v>
       </c>
@@ -11601,8 +11557,8 @@
       <c r="C564" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="D564" s="5" t="s">
-        <v>585</v>
+      <c r="D564" s="38" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.25">
@@ -11616,7 +11572,7 @@
         <v>581</v>
       </c>
       <c r="D565" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.25">
@@ -11630,12 +11586,12 @@
         <v>581</v>
       </c>
       <c r="D566" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B567" s="5" t="s">
         <v>15</v>
@@ -11644,12 +11600,12 @@
         <v>581</v>
       </c>
       <c r="D567" s="5" t="s">
-        <v>588</v>
+        <v>719</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B568" s="5" t="s">
         <v>15</v>
@@ -11658,12 +11614,12 @@
         <v>581</v>
       </c>
       <c r="D568" s="5" t="s">
-        <v>735</v>
+        <v>587</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B569" s="5" t="s">
         <v>15</v>
@@ -11672,12 +11628,12 @@
         <v>581</v>
       </c>
       <c r="D569" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B570" s="5" t="s">
         <v>15</v>
@@ -11686,40 +11642,40 @@
         <v>581</v>
       </c>
       <c r="D570" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B571" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B571" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C571" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="D571" s="5" t="s">
-        <v>591</v>
+      <c r="D571" s="3" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B572" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B572" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C572" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="D572" s="3" t="s">
-        <v>592</v>
+      <c r="D572" s="5" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B573" s="5" t="s">
         <v>15</v>
@@ -11728,12 +11684,12 @@
         <v>581</v>
       </c>
       <c r="D573" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B574" s="5" t="s">
         <v>15</v>
@@ -11742,12 +11698,12 @@
         <v>581</v>
       </c>
       <c r="D574" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B575" s="5" t="s">
         <v>15</v>
@@ -11756,12 +11712,12 @@
         <v>581</v>
       </c>
       <c r="D575" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B576" s="5" t="s">
         <v>15</v>
@@ -11769,13 +11725,13 @@
       <c r="C576" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="D576" s="5" t="s">
-        <v>596</v>
+      <c r="D576" s="38" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" s="3" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B577" s="5" t="s">
         <v>15</v>
@@ -11784,12 +11740,12 @@
         <v>581</v>
       </c>
       <c r="D577" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B578" s="5" t="s">
         <v>15</v>
@@ -11798,12 +11754,12 @@
         <v>581</v>
       </c>
       <c r="D578" s="5" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A579" s="3" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B579" s="5" t="s">
         <v>15</v>
@@ -11811,13 +11767,13 @@
       <c r="C579" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="D579" s="5" t="s">
-        <v>599</v>
+      <c r="D579" s="38" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A580" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B580" s="5" t="s">
         <v>15</v>
@@ -11826,12 +11782,12 @@
         <v>581</v>
       </c>
       <c r="D580" s="5" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" s="3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B581" s="5" t="s">
         <v>15</v>
@@ -11840,96 +11796,96 @@
         <v>581</v>
       </c>
       <c r="D581" s="5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A582" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B582" s="5" t="s">
+      <c r="A582" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B582" s="29" t="s">
         <v>15</v>
       </c>
       <c r="C582" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="D582" s="5" t="s">
-        <v>602</v>
+      <c r="D582" s="29" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A583" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B583" s="5" t="s">
+      <c r="A583" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B583" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C583" s="5" t="s">
         <v>581</v>
       </c>
       <c r="D583" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B584" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B584" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C584" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="D584" s="5" t="s">
-        <v>604</v>
+      <c r="D584" s="3" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B585" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B585" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C585" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="D585" s="5" t="s">
-        <v>605</v>
+      <c r="D585" s="3" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A586" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B586" s="29" t="s">
+      <c r="A586" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B586" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C586" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="D586" s="29" t="s">
-        <v>606</v>
+      <c r="D586" s="3" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A587" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B587" s="6" t="s">
+      <c r="A587" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B587" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C587" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="D587" s="5" t="s">
-        <v>607</v>
+      <c r="D587" s="3" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" s="3" t="s">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c r="B588" s="3" t="s">
         <v>15</v>
@@ -11938,12 +11894,12 @@
         <v>581</v>
       </c>
       <c r="D588" s="3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" s="3" t="s">
-        <v>18</v>
+        <v>221</v>
       </c>
       <c r="B589" s="3" t="s">
         <v>15</v>
@@ -11952,26 +11908,26 @@
         <v>581</v>
       </c>
       <c r="D589" s="3" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B590" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B590" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C590" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="D590" s="5" t="s">
-        <v>736</v>
+      <c r="D590" s="3" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" s="3" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="B591" s="3" t="s">
         <v>15</v>
@@ -11980,12 +11936,12 @@
         <v>581</v>
       </c>
       <c r="D591" s="3" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A592" s="3" t="s">
-        <v>202</v>
+        <v>320</v>
       </c>
       <c r="B592" s="3" t="s">
         <v>15</v>
@@ -11994,180 +11950,183 @@
         <v>581</v>
       </c>
       <c r="D592" s="3" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A593" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B593" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C593" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D593" s="5" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A594" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B594" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C594" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D594" s="5" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A593" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B593" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C593" s="5" t="s">
+    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A595" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B595" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C595" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D593" s="3" t="s">
+      <c r="D595" s="5" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A594" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B594" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C594" s="5" t="s">
+    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A596" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B596" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C596" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D594" s="3" t="s">
+      <c r="D596" s="5" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A595" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B595" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C595" s="5" t="s">
+    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A597" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B597" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C597" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D595" s="3" t="s">
+      <c r="D597" s="5" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A596" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B596" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C596" s="5" t="s">
+    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A598" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B598" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C598" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D596" s="3" t="s">
+      <c r="D598" s="5" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A597" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B597" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C597" s="5" t="s">
+    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A599" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B599" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C599" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D597" s="3" t="s">
+      <c r="D599" s="5" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A598" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B598" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C598" s="5" t="s">
+    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A600" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B600" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C600" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D598" s="3" t="s">
+      <c r="D600" s="5" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A599" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B599" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C599" s="5" t="s">
+    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A601" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B601" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C601" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D599" s="3" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A600" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B600" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C600" s="5" t="s">
+      <c r="D601" s="5" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A602" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B602" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C602" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D600" s="3" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A601" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B601" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C601" s="5" t="s">
+      <c r="D602" s="5" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A603" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B603" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C603" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D601" s="3" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A602" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B602" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C602" s="5" t="s">
+      <c r="D603" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="E603" s="3"/>
+      <c r="F603" s="5"/>
+      <c r="G603" s="3"/>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A604" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B604" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C604" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D602" s="3" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A603" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B603" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C603" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="D603" s="3" t="s">
+      <c r="D604" s="5" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A604" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="B604" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C604" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="D604" s="3" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A605" s="3" t="s">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="B605" s="3" t="s">
         <v>15</v>
@@ -12176,1640 +12135,1434 @@
         <v>581</v>
       </c>
       <c r="D605" s="5" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="606" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A606" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B606" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C606" s="3" t="s">
         <v>623</v>
-      </c>
-    </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A606" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B606" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C606" s="3" t="s">
-        <v>581</v>
       </c>
       <c r="D606" s="5" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="3" t="s">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="B607" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C607" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D607" s="5" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="3" t="s">
-        <v>252</v>
+        <v>36</v>
       </c>
       <c r="B608" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C608" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D608" s="5" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="3" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="B609" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C609" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D609" s="5" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="3" t="s">
-        <v>323</v>
+        <v>202</v>
       </c>
       <c r="B610" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C610" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D610" s="5" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="3" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="B611" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C611" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D611" s="5" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="3" t="s">
-        <v>258</v>
+        <v>209</v>
       </c>
       <c r="B612" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C612" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D612" s="5" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B613" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C613" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D613" s="5" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="3" t="s">
-        <v>261</v>
+        <v>27</v>
       </c>
       <c r="B614" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C614" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D614" s="5" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="3" t="s">
-        <v>325</v>
+        <v>32</v>
       </c>
       <c r="B615" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C615" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D615" s="5" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="3" t="s">
-        <v>265</v>
+        <v>211</v>
       </c>
       <c r="B616" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C616" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D616" s="5" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="3" t="s">
-        <v>278</v>
+        <v>31</v>
       </c>
       <c r="B617" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C617" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="D617" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D617" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="E617" s="3"/>
-      <c r="F617" s="5"/>
-      <c r="G617" s="3"/>
-    </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="618" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="3" t="s">
-        <v>280</v>
+        <v>213</v>
       </c>
       <c r="B618" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C618" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D618" s="5" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="3" t="s">
-        <v>292</v>
+        <v>215</v>
       </c>
       <c r="B619" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C619" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D619" s="5" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="3" t="s">
-        <v>296</v>
+        <v>33</v>
       </c>
       <c r="B620" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C620" s="3" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="D620" s="5" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B621" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C621" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D621" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="D621" s="5" t="s">
+    </row>
+    <row r="622" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A622" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B622" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C622" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D622" s="5" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A622" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B622" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C622" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D622" s="5" t="s">
+    <row r="623" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A623" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B623" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D623" s="5" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A623" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B623" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C623" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D623" s="5" t="s">
+    <row r="624" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A624" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B624" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C624" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D624" s="5" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A624" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B624" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C624" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D624" s="5" t="s">
+    <row r="625" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A625" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B625" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C625" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D625" s="5" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A625" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B625" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C625" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D625" s="5" t="s">
+    <row r="626" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A626" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B626" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C626" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D626" s="5" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A626" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B626" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C626" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D626" s="5" t="s">
+    <row r="627" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A627" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B627" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C627" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D627" s="5" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A627" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B627" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C627" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D627" s="5" t="s">
+    <row r="628" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A628" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B628" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C628" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D628" s="5" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A628" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B628" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C628" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D628" s="5" t="s">
+    <row r="629" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A629" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B629" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C629" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D629" s="5" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A629" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B629" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C629" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D629" s="5" t="s">
+    <row r="630" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A630" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B630" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C630" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D630" s="5" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A630" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B630" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C630" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D630" s="5" t="s">
+    <row r="631" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A631" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B631" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C631" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D631" s="5" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A631" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B631" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C631" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D631" s="5" t="s">
+    <row r="632" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A632" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B632" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C632" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D632" s="5" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A632" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B632" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C632" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D632" s="5" t="s">
+    <row r="633" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A633" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B633" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C633" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D633" s="5" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A633" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B633" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C633" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D633" s="5" t="s">
+    <row r="634" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A634" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B634" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C634" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D634" s="5" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A634" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B634" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C634" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D634" s="5" t="s">
+    <row r="635" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A635" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B635" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C635" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D635" s="5" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A635" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B635" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C635" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D635" s="5" t="s">
+    <row r="636" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A636" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B636" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C636" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D636" s="5" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A636" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B636" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C636" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D636" s="5" t="s">
+    <row r="637" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A637" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B637" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C637" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D637" s="5" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A637" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B637" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C637" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D637" s="5" t="s">
+    <row r="638" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A638" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B638" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C638" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D638" s="5" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A638" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B638" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C638" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D638" s="5" t="s">
+    <row r="639" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A639" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B639" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C639" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D639" s="5" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A639" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B639" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C639" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D639" s="5" t="s">
+    <row r="640" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A640" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B640" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C640" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D640" s="5" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A640" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B640" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C640" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D640" s="5" t="s">
+    <row r="641" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A641" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B641" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C641" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D641" s="5" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A641" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B641" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C641" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D641" s="5" t="s">
+    <row r="642" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A642" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B642" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C642" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D642" s="5" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A642" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B642" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C642" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D642" s="5" t="s">
+    <row r="643" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A643" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B643" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C643" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D643" s="5" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A643" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B643" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C643" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D643" s="5" t="s">
+    <row r="644" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A644" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B644" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C644" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D644" s="5" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A644" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B644" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C644" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D644" s="5" t="s">
+    <row r="645" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A645" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B645" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C645" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D645" s="5" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A645" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B645" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C645" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D645" s="5" t="s">
+    <row r="646" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A646" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B646" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C646" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D646" s="5" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A646" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B646" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C646" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D646" s="5" t="s">
+    <row r="647" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A647" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B647" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C647" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D647" s="5" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A647" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B647" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C647" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D647" s="5" t="s">
+    <row r="648" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A648" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B648" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C648" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D648" s="5" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A648" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B648" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C648" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D648" s="5" t="s">
+    <row r="649" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A649" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B649" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C649" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D649" s="5" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A649" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B649" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C649" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D649" s="5" t="s">
+    <row r="650" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A650" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B650" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C650" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D650" s="5" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A650" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B650" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C650" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D650" s="5" t="s">
+    <row r="651" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A651" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B651" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C651" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D651" s="5" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A651" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B651" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C651" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D651" s="5" t="s">
+    <row r="652" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A652" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B652" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C652" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D652" s="5" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A652" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B652" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C652" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D652" s="5" t="s">
+    <row r="653" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A653" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C653" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D653" s="5" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A653" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B653" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C653" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D653" s="5" t="s">
+    <row r="654" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A654" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B654" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D654" s="5" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A654" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B654" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C654" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D654" s="5" t="s">
+    <row r="655" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A655" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B655" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C655" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D655" s="5" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A655" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B655" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C655" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D655" s="5" t="s">
+    <row r="656" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A656" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B656" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D656" s="5" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A656" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B656" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C656" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D656" s="5" t="s">
+    <row r="657" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A657" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B657" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C657" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D657" s="5" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A657" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="B657" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C657" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D657" s="5" t="s">
+    <row r="658" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A658" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B658" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D658" s="5" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A658" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B658" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C658" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D658" s="5" t="s">
+    <row r="659" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A659" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B659" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C659" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D659" s="5" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A659" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B659" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C659" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D659" s="5" t="s">
+    <row r="660" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A660" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B660" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D660" s="5" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A660" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B660" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C660" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D660" s="5" t="s">
+    <row r="661" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A661" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B661" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C661" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D661" s="5" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A661" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B661" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C661" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D661" s="5" t="s">
+    <row r="662" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A662" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B662" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C662" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D662" s="5" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A662" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B662" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C662" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D662" s="5" t="s">
+    <row r="663" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A663" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B663" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C663" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D663" s="5" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A663" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B663" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C663" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D663" s="5" t="s">
+    <row r="664" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A664" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B664" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D664" s="5" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A664" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B664" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C664" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D664" s="5" t="s">
+    <row r="665" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A665" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B665" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C665" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D665" s="5" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A665" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B665" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C665" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D665" s="5" t="s">
+    <row r="666" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A666" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B666" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D666" s="5" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A666" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B666" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C666" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D666" s="5" t="s">
+    <row r="667" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A667" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B667" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C667" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D667" s="5" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A667" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B667" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C667" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D667" s="5" t="s">
+    <row r="668" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A668" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B668" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D668" s="5" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A668" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B668" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C668" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D668" s="5" t="s">
+    <row r="669" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A669" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B669" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D669" s="5" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A669" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B669" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C669" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D669" s="5" t="s">
+    <row r="670" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A670" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B670" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D670" s="5" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A670" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B670" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C670" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D670" s="5" t="s">
+    <row r="671" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A671" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B671" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D671" s="5" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A671" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B671" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C671" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D671" s="5" t="s">
+    <row r="672" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A672" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B672" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D672" s="5" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A672" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B672" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C672" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D672" s="5" t="s">
+    <row r="673" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A673" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B673" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C673" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D673" s="5" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A673" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B673" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C673" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D673" s="5" t="s">
+    <row r="674" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A674" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B674" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C674" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D674" s="5" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A674" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B674" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C674" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D674" s="5" t="s">
+    <row r="675" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A675" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B675" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C675" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D675" s="5" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A675" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B675" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C675" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D675" s="5" t="s">
+    <row r="676" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A676" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B676" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C676" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D676" s="5" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A676" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B676" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C676" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D676" s="5" t="s">
+    <row r="677" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A677" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B677" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C677" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D677" s="5" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A677" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B677" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C677" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D677" s="5" t="s">
+    <row r="678" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A678" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B678" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C678" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D678" s="5" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A678" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B678" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C678" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D678" s="5" t="s">
+    <row r="679" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A679" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B679" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C679" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D679" s="5" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A679" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B679" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C679" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D679" s="5" t="s">
+    <row r="680" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A680" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B680" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C680" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D680" s="5" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A680" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B680" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C680" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D680" s="5" t="s">
+    <row r="681" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A681" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B681" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C681" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D681" s="5" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A681" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B681" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C681" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D681" s="5" t="s">
+    <row r="682" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A682" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B682" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C682" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D682" s="5" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A682" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B682" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C682" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D682" s="5" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B683" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C683" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D683" s="5" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+        <v>795</v>
+      </c>
+      <c r="B683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C683" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D683" s="41" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B684" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C684" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D684" s="5" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+        <v>796</v>
+      </c>
+      <c r="B684" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C684" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D684" s="41" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B685" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C685" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D685" s="5" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+        <v>797</v>
+      </c>
+      <c r="B685" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C685" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D685" s="41" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B686" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C686" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D686" s="5" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
+        <v>798</v>
+      </c>
+      <c r="B686" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C686" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D686" s="41" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B687" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C687" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D687" s="5" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
+        <v>795</v>
+      </c>
+      <c r="B687" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C687" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D687" s="41" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B688" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C688" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D688" s="5" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
+        <v>796</v>
+      </c>
+      <c r="B688" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C688" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D688" s="41" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B689" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C689" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D689" s="5" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
+        <v>797</v>
+      </c>
+      <c r="B689" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C689" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D689" s="41" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B690" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C690" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D690" s="5" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
+        <v>798</v>
+      </c>
+      <c r="B690" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C690" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D690" s="41" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B691" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C691" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D691" s="5" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
+        <v>799</v>
+      </c>
+      <c r="B691" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C691" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D691" s="41" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B692" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C692" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D692" s="5" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
+        <v>795</v>
+      </c>
+      <c r="B692" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C692" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D692" s="41" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B693" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C693" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D693" s="5" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
+        <v>796</v>
+      </c>
+      <c r="B693" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C693" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D693" s="41" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B694" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C694" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D694" s="5" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
+        <v>797</v>
+      </c>
+      <c r="B694" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C694" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D694" s="41" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B695" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C695" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D695" s="5" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
+        <v>798</v>
+      </c>
+      <c r="B695" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C695" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D695" s="41" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B696" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C696" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D696" s="5" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
+        <v>799</v>
+      </c>
+      <c r="B696" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C696" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D696" s="41" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B697" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C697" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D697" s="5" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
+        <v>795</v>
+      </c>
+      <c r="B697" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C697" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D697" s="41" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" s="3" t="s">
-        <v>812</v>
+        <v>796</v>
       </c>
       <c r="B698" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C698" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D698" s="41" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A699" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="B699" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C699" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D699" s="41" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A699" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="B699" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C699" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D699" s="41" t="s">
+    <row r="700" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A700" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="B700" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C700" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D700" s="41" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A700" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="B700" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C700" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D700" s="41" t="s">
+    <row r="701" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A701" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="B701" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C701" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D701" s="41" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A701" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="B701" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C701" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D701" s="41" t="s">
+    <row r="702" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A702" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="B702" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C702" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="D702" s="41" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A702" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="B702" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C702" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D702" s="41" t="s">
+    <row r="703" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A703" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="B703" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C703" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="D703" s="41" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A704" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="B704" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C704" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="D704" s="41" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A703" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="B703" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C703" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D703" s="41" t="s">
+    <row r="705" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A705" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="B705" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C705" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="D705" s="41" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A704" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="B704" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C704" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D704" s="41" t="s">
+    <row r="706" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A706" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="B706" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C706" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="D706" s="41" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A705" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="B705" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C705" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D705" s="41" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A706" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="B706" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C706" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D706" s="41" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A707" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="B707" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C707" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D707" s="41" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A708" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="B708" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C708" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D708" s="41" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A709" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="B709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C709" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D709" s="41" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A710" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="B710" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C710" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D710" s="41" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A711" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="B711" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C711" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D711" s="41" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="712" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A712" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="B712" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C712" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D712" s="41" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A713" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="B713" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C713" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D713" s="41" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A714" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="B714" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C714" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D714" s="41" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A715" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="B715" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C715" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D715" s="41" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A716" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="B716" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C716" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D716" s="41" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A717" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="B717" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C717" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="D717" s="41" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A718" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="B718" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C718" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="D718" s="41" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A719" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="B719" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C719" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="D719" s="41" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="720" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A720" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="B720" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C720" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="D720" s="41" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="721" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A721" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="B721" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C721" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="D721" s="41" t="s">
-        <v>841</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:D706" xr:uid="{2C4ECE9E-4A28-6340-B936-CE442F4057E5}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Falabella"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D683" r:id="rId1" xr:uid="{C4A764D9-65E4-467B-BC7B-5C3E51C52CDA}"/>
+    <hyperlink ref="D668" r:id="rId1" xr:uid="{C4A764D9-65E4-467B-BC7B-5C3E51C52CDA}"/>
     <hyperlink ref="D404" r:id="rId2" xr:uid="{D651BCB1-3ED9-4F19-8693-954A866AE24A}"/>
     <hyperlink ref="D169" r:id="rId3" xr:uid="{7086FFCC-885D-4084-BB2F-A88AC858A9CB}"/>
     <hyperlink ref="D130" r:id="rId4" xr:uid="{69561AFA-C503-44D5-8510-6B92EECD75D3}"/>
@@ -13873,8 +13626,10 @@
     <hyperlink ref="D289" r:id="rId62" xr:uid="{0D74648B-9A00-4261-A628-6A92A024DD1D}"/>
     <hyperlink ref="D304" r:id="rId63" xr:uid="{B4E261E2-2852-4723-A6C5-B4DB99125375}"/>
     <hyperlink ref="D410" r:id="rId64" xr:uid="{DE0EAE0D-94D1-44E6-9100-BB86FBDDC6A7}"/>
+    <hyperlink ref="D576" r:id="rId65" xr:uid="{37E52712-D7EB-4125-871E-21725163FA4B}"/>
+    <hyperlink ref="D579" r:id="rId66" xr:uid="{E6455D81-4205-46DC-9D19-8D489A6C5901}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId65"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId67"/>
 </worksheet>
 </file>
--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMSIERRA\Documents\ISDIN_Shopping_de_precios\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{770D789F-FC00-40FD-B61C-842FE001F10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B9B3C0-7256-407C-9BFB-D7E5E4C512BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{60233B49-B589-B346-B71C-4D486694C55A}"/>
   </bookViews>
@@ -929,9 +929,6 @@
     <t>https://www.bellapiel.com.co/isdinceutics-serum-salicylic-renewal-x-30-ml-6663/p</t>
   </si>
   <si>
-    <t>https://www.lineaestetica.co/producto/isdin-fotoprotector-compacto-spf-50-tono-light-x10-gr/</t>
-  </si>
-  <si>
     <t>FP COMPACT BRONCE SPF50+ 10G</t>
   </si>
   <si>
@@ -2243,9 +2240,6 @@
     <t>https://lineaestetica.co/product/isdin-flavo-c-ultraglican-melatonin-x10-ampollas/</t>
   </si>
   <si>
-    <t>https://lineaestetica.co/product/isdin-instant-flash-efecto-lifting-x1-ampolla/</t>
-  </si>
-  <si>
     <t>https://www.medipiel.com.co/essential-cleansing-isdin/p?skuId=14664&amp;_sgm_campaign=product&amp;_sgm_source=14664&amp;_sgm_action=search&amp;_sgm_term=essential%20clean&amp;_sgm_pinned=false</t>
   </si>
   <si>
@@ -2400,6 +2394,12 @@
   </si>
   <si>
     <t>https://lineaestetica.co/product/isdin-hydration-ureadin-lotion-10/?attribute_pa_tamano=400ml</t>
+  </si>
+  <si>
+    <t>https://lineaestetica.co/product/isdin-fotoprotector-compacto-spf-50/?attribute_pa_color=light</t>
+  </si>
+  <si>
+    <t>https://lineaestetica.co/product/isdin-instant-flash-efecto-lifting/?attribute_pa_unidades=1-ampolla</t>
   </si>
 </sst>
 </file>
@@ -5163,7 +5163,7 @@
         <v>3</v>
       </c>
       <c r="D120" s="40" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -5177,7 +5177,7 @@
         <v>3</v>
       </c>
       <c r="D121" s="40" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -5191,7 +5191,7 @@
         <v>3</v>
       </c>
       <c r="D122" s="42" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -5205,7 +5205,7 @@
         <v>3</v>
       </c>
       <c r="D123" s="42" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -5219,7 +5219,7 @@
         <v>3</v>
       </c>
       <c r="D124" s="40" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -5233,7 +5233,7 @@
         <v>3</v>
       </c>
       <c r="D125" s="40" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -5247,7 +5247,7 @@
         <v>3</v>
       </c>
       <c r="D126" s="40" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -5261,7 +5261,7 @@
         <v>3</v>
       </c>
       <c r="D127" s="40" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -5275,7 +5275,7 @@
         <v>3</v>
       </c>
       <c r="D128" s="40" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -5289,7 +5289,7 @@
         <v>3</v>
       </c>
       <c r="D129" s="40" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
@@ -5303,7 +5303,7 @@
         <v>3</v>
       </c>
       <c r="D130" s="40" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
@@ -5317,7 +5317,7 @@
         <v>3</v>
       </c>
       <c r="D131" s="40" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
@@ -5331,7 +5331,7 @@
         <v>3</v>
       </c>
       <c r="D132" s="40" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
@@ -5345,7 +5345,7 @@
         <v>3</v>
       </c>
       <c r="D133" s="40" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
@@ -5359,7 +5359,7 @@
         <v>3</v>
       </c>
       <c r="D134" s="40" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
@@ -5373,7 +5373,7 @@
         <v>3</v>
       </c>
       <c r="D135" s="40" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -5401,7 +5401,7 @@
         <v>3</v>
       </c>
       <c r="D137" s="40" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -5415,7 +5415,7 @@
         <v>3</v>
       </c>
       <c r="D138" s="40" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
@@ -5443,7 +5443,7 @@
         <v>3</v>
       </c>
       <c r="D140" s="40" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -5485,7 +5485,7 @@
         <v>3</v>
       </c>
       <c r="D143" s="40" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
@@ -5513,7 +5513,7 @@
         <v>3</v>
       </c>
       <c r="D145" s="40" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
@@ -5527,7 +5527,7 @@
         <v>3</v>
       </c>
       <c r="D146" s="40" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -5541,7 +5541,7 @@
         <v>3</v>
       </c>
       <c r="D147" s="40" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
@@ -5555,7 +5555,7 @@
         <v>3</v>
       </c>
       <c r="D148" s="40" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
@@ -5569,7 +5569,7 @@
         <v>3</v>
       </c>
       <c r="D149" s="40" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
@@ -5583,7 +5583,7 @@
         <v>3</v>
       </c>
       <c r="D150" s="40" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
@@ -5597,7 +5597,7 @@
         <v>3</v>
       </c>
       <c r="D151" s="40" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
@@ -5611,7 +5611,7 @@
         <v>3</v>
       </c>
       <c r="D152" s="40" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="153" spans="1:4" s="35" customFormat="1" x14ac:dyDescent="0.3">
@@ -5625,7 +5625,7 @@
         <v>3</v>
       </c>
       <c r="D153" s="40" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
@@ -5636,7 +5636,7 @@
         <v>13</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>147</v>
@@ -5650,7 +5650,7 @@
         <v>13</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>50</v>
@@ -5664,7 +5664,7 @@
         <v>13</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>8</v>
@@ -5678,7 +5678,7 @@
         <v>13</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>56</v>
@@ -5692,7 +5692,7 @@
         <v>13</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>73</v>
@@ -5706,10 +5706,10 @@
         <v>13</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="160" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.3">
@@ -5720,7 +5720,7 @@
         <v>13</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>160</v>
@@ -5734,7 +5734,7 @@
         <v>13</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>134</v>
@@ -5748,7 +5748,7 @@
         <v>13</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>140</v>
@@ -5762,7 +5762,7 @@
         <v>13</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>83</v>
@@ -5776,7 +5776,7 @@
         <v>13</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>95</v>
@@ -5790,7 +5790,7 @@
         <v>13</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>87</v>
@@ -5804,7 +5804,7 @@
         <v>13</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>100</v>
@@ -5818,10 +5818,10 @@
         <v>13</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D167" s="38" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="168" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -5832,7 +5832,7 @@
         <v>13</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>122</v>
@@ -5846,7 +5846,7 @@
         <v>13</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>127</v>
@@ -5860,7 +5860,7 @@
         <v>13</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>194</v>
@@ -5874,7 +5874,7 @@
         <v>13</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>117</v>
@@ -5888,7 +5888,7 @@
         <v>13</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>131</v>
@@ -5902,7 +5902,7 @@
         <v>13</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>171</v>
@@ -5916,7 +5916,7 @@
         <v>13</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D174" s="5" t="s">
         <v>167</v>
@@ -5930,7 +5930,7 @@
         <v>13</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>57</v>
@@ -5944,7 +5944,7 @@
         <v>13</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>151</v>
@@ -5958,10 +5958,10 @@
         <v>13</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
@@ -5972,7 +5972,7 @@
         <v>13</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>181</v>
@@ -5986,10 +5986,10 @@
         <v>13</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="180" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -6000,7 +6000,7 @@
         <v>13</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>176</v>
@@ -6014,7 +6014,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>62</v>
@@ -6028,7 +6028,7 @@
         <v>13</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>63</v>
@@ -6042,7 +6042,7 @@
         <v>13</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>144</v>
@@ -6056,7 +6056,7 @@
         <v>13</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>185</v>
@@ -6070,10 +6070,10 @@
         <v>13</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
@@ -6084,7 +6084,7 @@
         <v>13</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>69</v>
@@ -6115,7 +6115,7 @@
         <v>7</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
@@ -6395,7 +6395,7 @@
         <v>7</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="209" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -6829,7 +6829,7 @@
         <v>3</v>
       </c>
       <c r="D239" s="40" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
@@ -6843,7 +6843,7 @@
         <v>3</v>
       </c>
       <c r="D240" s="40" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
@@ -6857,7 +6857,7 @@
         <v>3</v>
       </c>
       <c r="D241" s="40" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
@@ -6871,12 +6871,12 @@
         <v>3</v>
       </c>
       <c r="D242" s="40" t="s">
-        <v>296</v>
+        <v>785</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>13</v>
@@ -6885,7 +6885,7 @@
         <v>3</v>
       </c>
       <c r="D243" s="40" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
@@ -6899,7 +6899,7 @@
         <v>3</v>
       </c>
       <c r="D244" s="40" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
@@ -6913,7 +6913,7 @@
         <v>3</v>
       </c>
       <c r="D245" s="40" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
@@ -6927,7 +6927,7 @@
         <v>3</v>
       </c>
       <c r="D246" s="40" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
@@ -6941,7 +6941,7 @@
         <v>3</v>
       </c>
       <c r="D247" s="40" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
@@ -6955,7 +6955,7 @@
         <v>3</v>
       </c>
       <c r="D248" s="40" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
@@ -6969,7 +6969,7 @@
         <v>3</v>
       </c>
       <c r="D249" s="40" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
@@ -6983,7 +6983,7 @@
         <v>3</v>
       </c>
       <c r="D250" s="40" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
@@ -6997,7 +6997,7 @@
         <v>3</v>
       </c>
       <c r="D251" s="40" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
@@ -7011,7 +7011,7 @@
         <v>3</v>
       </c>
       <c r="D252" s="40" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
@@ -7025,12 +7025,12 @@
         <v>3</v>
       </c>
       <c r="D253" s="40" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>13</v>
@@ -7039,7 +7039,7 @@
         <v>3</v>
       </c>
       <c r="D254" s="40" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
@@ -7053,7 +7053,7 @@
         <v>3</v>
       </c>
       <c r="D255" s="40" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
@@ -7067,7 +7067,7 @@
         <v>3</v>
       </c>
       <c r="D256" s="40" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
@@ -7081,7 +7081,7 @@
         <v>3</v>
       </c>
       <c r="D257" s="40" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
@@ -7095,7 +7095,7 @@
         <v>3</v>
       </c>
       <c r="D258" s="40" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
@@ -7109,7 +7109,7 @@
         <v>3</v>
       </c>
       <c r="D259" s="40" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
@@ -7123,7 +7123,7 @@
         <v>3</v>
       </c>
       <c r="D260" s="40" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
@@ -7137,7 +7137,7 @@
         <v>3</v>
       </c>
       <c r="D261" s="40" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
@@ -7151,7 +7151,7 @@
         <v>3</v>
       </c>
       <c r="D262" s="40" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
@@ -7165,7 +7165,7 @@
         <v>3</v>
       </c>
       <c r="D263" s="40" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
@@ -7179,7 +7179,7 @@
         <v>3</v>
       </c>
       <c r="D264" s="40" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
@@ -7193,7 +7193,7 @@
         <v>3</v>
       </c>
       <c r="D265" s="40" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
@@ -7207,12 +7207,12 @@
         <v>3</v>
       </c>
       <c r="D266" s="40" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>13</v>
@@ -7221,7 +7221,7 @@
         <v>3</v>
       </c>
       <c r="D267" s="40" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
@@ -7235,7 +7235,7 @@
         <v>3</v>
       </c>
       <c r="D268" s="40" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
@@ -7249,7 +7249,7 @@
         <v>3</v>
       </c>
       <c r="D269" s="40" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
@@ -7263,12 +7263,12 @@
         <v>3</v>
       </c>
       <c r="D270" s="40" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>13</v>
@@ -7277,7 +7277,7 @@
         <v>3</v>
       </c>
       <c r="D271" s="40" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
@@ -7291,7 +7291,7 @@
         <v>3</v>
       </c>
       <c r="D272" s="40" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
@@ -7305,7 +7305,7 @@
         <v>3</v>
       </c>
       <c r="D273" s="40" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
@@ -7319,7 +7319,7 @@
         <v>3</v>
       </c>
       <c r="D274" s="40" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
@@ -7333,7 +7333,7 @@
         <v>3</v>
       </c>
       <c r="D275" s="40" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
@@ -7347,7 +7347,7 @@
         <v>3</v>
       </c>
       <c r="D276" s="40" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
@@ -7361,7 +7361,7 @@
         <v>3</v>
       </c>
       <c r="D277" s="40" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
@@ -7375,7 +7375,7 @@
         <v>3</v>
       </c>
       <c r="D278" s="40" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
@@ -7389,7 +7389,7 @@
         <v>3</v>
       </c>
       <c r="D279" s="40" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
@@ -7403,7 +7403,7 @@
         <v>3</v>
       </c>
       <c r="D280" s="40" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
@@ -7417,12 +7417,12 @@
         <v>3</v>
       </c>
       <c r="D281" s="40" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>13</v>
@@ -7431,12 +7431,12 @@
         <v>3</v>
       </c>
       <c r="D282" s="40" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>13</v>
@@ -7445,12 +7445,12 @@
         <v>3</v>
       </c>
       <c r="D283" s="40" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>13</v>
@@ -7459,7 +7459,7 @@
         <v>3</v>
       </c>
       <c r="D284" s="40" t="s">
-        <v>734</v>
+        <v>786</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
@@ -7473,7 +7473,7 @@
         <v>3</v>
       </c>
       <c r="D285" s="40" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
@@ -7487,7 +7487,7 @@
         <v>3</v>
       </c>
       <c r="D286" s="40" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
@@ -7501,7 +7501,7 @@
         <v>3</v>
       </c>
       <c r="D287" s="40" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
@@ -7515,7 +7515,7 @@
         <v>3</v>
       </c>
       <c r="D288" s="40" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
@@ -7529,7 +7529,7 @@
         <v>3</v>
       </c>
       <c r="D289" s="40" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
@@ -7543,7 +7543,7 @@
         <v>3</v>
       </c>
       <c r="D290" s="40" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
@@ -7557,7 +7557,7 @@
         <v>3</v>
       </c>
       <c r="D291" s="40" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
@@ -7571,7 +7571,7 @@
         <v>3</v>
       </c>
       <c r="D292" s="40" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="293" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.3">
@@ -7585,7 +7585,7 @@
         <v>5</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="294" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.3">
@@ -7599,7 +7599,7 @@
         <v>5</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="295" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.3">
@@ -7613,7 +7613,7 @@
         <v>5</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="296" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -7627,7 +7627,7 @@
         <v>5</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="297" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -7641,7 +7641,7 @@
         <v>5</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="298" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -7655,7 +7655,7 @@
         <v>5</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="299" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -7669,7 +7669,7 @@
         <v>5</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="300" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -7683,7 +7683,7 @@
         <v>5</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="301" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -7697,7 +7697,7 @@
         <v>5</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="302" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -7711,7 +7711,7 @@
         <v>5</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="303" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -7725,7 +7725,7 @@
         <v>5</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="304" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -7739,12 +7739,12 @@
         <v>5</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="305" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>13</v>
@@ -7753,7 +7753,7 @@
         <v>5</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="306" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -7767,7 +7767,7 @@
         <v>5</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
@@ -7781,7 +7781,7 @@
         <v>5</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
@@ -7795,7 +7795,7 @@
         <v>5</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
@@ -7809,7 +7809,7 @@
         <v>5</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
@@ -7823,7 +7823,7 @@
         <v>5</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
@@ -7837,7 +7837,7 @@
         <v>5</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
@@ -7851,7 +7851,7 @@
         <v>5</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
@@ -7865,12 +7865,12 @@
         <v>5</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>13</v>
@@ -7879,7 +7879,7 @@
         <v>5</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
@@ -7893,7 +7893,7 @@
         <v>5</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
@@ -7907,7 +7907,7 @@
         <v>5</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
@@ -7921,12 +7921,12 @@
         <v>5</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>13</v>
@@ -7935,7 +7935,7 @@
         <v>5</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
@@ -7949,7 +7949,7 @@
         <v>5</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
@@ -7963,7 +7963,7 @@
         <v>5</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
@@ -7977,7 +7977,7 @@
         <v>5</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
@@ -7991,7 +7991,7 @@
         <v>5</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
@@ -8005,7 +8005,7 @@
         <v>5</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
@@ -8019,12 +8019,12 @@
         <v>5</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>13</v>
@@ -8033,12 +8033,12 @@
         <v>5</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>13</v>
@@ -8047,12 +8047,12 @@
         <v>5</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>13</v>
@@ -8061,7 +8061,7 @@
         <v>5</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
@@ -8075,7 +8075,7 @@
         <v>5</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
@@ -8089,12 +8089,12 @@
         <v>5</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>13</v>
@@ -8103,12 +8103,12 @@
         <v>5</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>13</v>
@@ -8117,7 +8117,7 @@
         <v>5</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
@@ -8131,7 +8131,7 @@
         <v>5</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
@@ -8145,7 +8145,7 @@
         <v>5</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
@@ -8159,7 +8159,7 @@
         <v>5</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
@@ -8173,7 +8173,7 @@
         <v>5</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
@@ -8187,7 +8187,7 @@
         <v>6</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
@@ -8201,7 +8201,7 @@
         <v>6</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
@@ -8215,7 +8215,7 @@
         <v>6</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
@@ -8229,7 +8229,7 @@
         <v>6</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
@@ -8243,7 +8243,7 @@
         <v>6</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
@@ -8257,7 +8257,7 @@
         <v>6</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
@@ -8271,7 +8271,7 @@
         <v>6</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
@@ -8285,7 +8285,7 @@
         <v>6</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
@@ -8299,7 +8299,7 @@
         <v>6</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
@@ -8313,7 +8313,7 @@
         <v>6</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
@@ -8327,7 +8327,7 @@
         <v>6</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.3">
@@ -8341,12 +8341,12 @@
         <v>6</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>13</v>
@@ -8355,7 +8355,7 @@
         <v>6</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.3">
@@ -8369,7 +8369,7 @@
         <v>6</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.3">
@@ -8383,7 +8383,7 @@
         <v>6</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.3">
@@ -8397,7 +8397,7 @@
         <v>6</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.3">
@@ -8411,7 +8411,7 @@
         <v>6</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.3">
@@ -8425,7 +8425,7 @@
         <v>6</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.3">
@@ -8439,7 +8439,7 @@
         <v>6</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.3">
@@ -8453,7 +8453,7 @@
         <v>6</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.3">
@@ -8467,7 +8467,7 @@
         <v>6</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.3">
@@ -8481,7 +8481,7 @@
         <v>6</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.3">
@@ -8495,7 +8495,7 @@
         <v>6</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.3">
@@ -8509,7 +8509,7 @@
         <v>6</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.3">
@@ -8523,7 +8523,7 @@
         <v>6</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.3">
@@ -8537,12 +8537,12 @@
         <v>6</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>13</v>
@@ -8551,7 +8551,7 @@
         <v>6</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.3">
@@ -8565,7 +8565,7 @@
         <v>6</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.3">
@@ -8579,7 +8579,7 @@
         <v>6</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.3">
@@ -8593,7 +8593,7 @@
         <v>6</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.3">
@@ -8607,12 +8607,12 @@
         <v>6</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>13</v>
@@ -8621,7 +8621,7 @@
         <v>6</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.3">
@@ -8635,7 +8635,7 @@
         <v>6</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.3">
@@ -8649,7 +8649,7 @@
         <v>6</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.3">
@@ -8663,7 +8663,7 @@
         <v>6</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.3">
@@ -8677,7 +8677,7 @@
         <v>6</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.3">
@@ -8691,7 +8691,7 @@
         <v>6</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.3">
@@ -8705,7 +8705,7 @@
         <v>6</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.3">
@@ -8719,12 +8719,12 @@
         <v>6</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>13</v>
@@ -8733,7 +8733,7 @@
         <v>6</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.3">
@@ -8747,7 +8747,7 @@
         <v>6</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.3">
@@ -8761,7 +8761,7 @@
         <v>6</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.3">
@@ -8775,7 +8775,7 @@
         <v>6</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.3">
@@ -8789,7 +8789,7 @@
         <v>6</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.3">
@@ -8803,7 +8803,7 @@
         <v>6</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.3">
@@ -8817,7 +8817,7 @@
         <v>6</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.3">
@@ -8828,10 +8828,10 @@
         <v>13</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.3">
@@ -8842,10 +8842,10 @@
         <v>13</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.3">
@@ -8856,10 +8856,10 @@
         <v>13</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.3">
@@ -8870,10 +8870,10 @@
         <v>13</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D385" s="38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.3">
@@ -8884,10 +8884,10 @@
         <v>13</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.3">
@@ -8898,10 +8898,10 @@
         <v>13</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.3">
@@ -8912,10 +8912,10 @@
         <v>13</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.3">
@@ -8926,10 +8926,10 @@
         <v>13</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.3">
@@ -8940,10 +8940,10 @@
         <v>13</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.3">
@@ -8954,10 +8954,10 @@
         <v>13</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D391" s="38" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.3">
@@ -8968,10 +8968,10 @@
         <v>13</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.3">
@@ -8982,10 +8982,10 @@
         <v>13</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
@@ -8996,24 +8996,24 @@
         <v>13</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.3">
@@ -9024,10 +9024,10 @@
         <v>13</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
@@ -9038,10 +9038,10 @@
         <v>13</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
@@ -9052,10 +9052,10 @@
         <v>13</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
@@ -9066,10 +9066,10 @@
         <v>13</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
@@ -9080,10 +9080,10 @@
         <v>13</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
@@ -9094,10 +9094,10 @@
         <v>13</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
@@ -9108,10 +9108,10 @@
         <v>13</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
@@ -9122,10 +9122,10 @@
         <v>13</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
@@ -9136,10 +9136,10 @@
         <v>13</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
@@ -9150,24 +9150,24 @@
         <v>13</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
@@ -9178,10 +9178,10 @@
         <v>13</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
@@ -9192,10 +9192,10 @@
         <v>13</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
@@ -9206,10 +9206,10 @@
         <v>13</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
@@ -9220,10 +9220,10 @@
         <v>13</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
@@ -9234,10 +9234,10 @@
         <v>13</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">
@@ -9248,10 +9248,10 @@
         <v>13</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.3">
@@ -9262,10 +9262,10 @@
         <v>13</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.3">
@@ -9276,10 +9276,10 @@
         <v>13</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.3">
@@ -9290,10 +9290,10 @@
         <v>13</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.3">
@@ -9304,10 +9304,10 @@
         <v>13</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.3">
@@ -9318,10 +9318,10 @@
         <v>13</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.3">
@@ -9332,38 +9332,38 @@
         <v>13</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A420" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.3">
@@ -9374,10 +9374,10 @@
         <v>13</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.3">
@@ -9388,10 +9388,10 @@
         <v>13</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.3">
@@ -9402,10 +9402,10 @@
         <v>13</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.3">
@@ -9416,10 +9416,10 @@
         <v>13</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.3">
@@ -9430,10 +9430,10 @@
         <v>13</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.3">
@@ -9444,10 +9444,10 @@
         <v>13</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.3">
@@ -9461,7 +9461,7 @@
         <v>4</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.3">
@@ -9475,7 +9475,7 @@
         <v>4</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.3">
@@ -9489,7 +9489,7 @@
         <v>4</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.3">
@@ -9503,7 +9503,7 @@
         <v>4</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.3">
@@ -9517,7 +9517,7 @@
         <v>4</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.3">
@@ -9531,7 +9531,7 @@
         <v>4</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.3">
@@ -9545,7 +9545,7 @@
         <v>4</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.3">
@@ -9559,7 +9559,7 @@
         <v>4</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.3">
@@ -9573,12 +9573,12 @@
         <v>4</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A436" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>13</v>
@@ -9587,7 +9587,7 @@
         <v>4</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.3">
@@ -9601,7 +9601,7 @@
         <v>4</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.3">
@@ -9615,7 +9615,7 @@
         <v>4</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.3">
@@ -9629,7 +9629,7 @@
         <v>4</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.3">
@@ -9643,7 +9643,7 @@
         <v>4</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.3">
@@ -9657,7 +9657,7 @@
         <v>4</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.3">
@@ -9671,7 +9671,7 @@
         <v>4</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.3">
@@ -9685,7 +9685,7 @@
         <v>4</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.3">
@@ -9699,7 +9699,7 @@
         <v>4</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.3">
@@ -9713,7 +9713,7 @@
         <v>4</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.3">
@@ -9727,12 +9727,12 @@
         <v>4</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>13</v>
@@ -9741,7 +9741,7 @@
         <v>4</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.3">
@@ -9755,7 +9755,7 @@
         <v>4</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.3">
@@ -9769,7 +9769,7 @@
         <v>4</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.3">
@@ -9783,7 +9783,7 @@
         <v>4</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.3">
@@ -9797,7 +9797,7 @@
         <v>4</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.3">
@@ -9811,7 +9811,7 @@
         <v>4</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.3">
@@ -9825,7 +9825,7 @@
         <v>4</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.3">
@@ -9839,7 +9839,7 @@
         <v>4</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.3">
@@ -9853,7 +9853,7 @@
         <v>4</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.3">
@@ -9867,7 +9867,7 @@
         <v>4</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.3">
@@ -9881,7 +9881,7 @@
         <v>4</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.3">
@@ -9895,7 +9895,7 @@
         <v>4</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.3">
@@ -9909,7 +9909,7 @@
         <v>4</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.3">
@@ -9923,7 +9923,7 @@
         <v>4</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.3">
@@ -9937,7 +9937,7 @@
         <v>4</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.3">
@@ -9951,7 +9951,7 @@
         <v>4</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.3">
@@ -9965,7 +9965,7 @@
         <v>4</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.3">
@@ -9979,7 +9979,7 @@
         <v>4</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.3">
@@ -9993,7 +9993,7 @@
         <v>4</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.3">
@@ -10007,7 +10007,7 @@
         <v>4</v>
       </c>
       <c r="D466" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.3">
@@ -10018,10 +10018,10 @@
         <v>13</v>
       </c>
       <c r="C467" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="D467" s="3" t="s">
         <v>481</v>
-      </c>
-      <c r="D467" s="3" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.3">
@@ -10032,10 +10032,10 @@
         <v>13</v>
       </c>
       <c r="C468" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D468" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.3">
@@ -10046,10 +10046,10 @@
         <v>13</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D469" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.3">
@@ -10060,10 +10060,10 @@
         <v>13</v>
       </c>
       <c r="C470" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D470" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.3">
@@ -10074,10 +10074,10 @@
         <v>13</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D471" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.3">
@@ -10088,10 +10088,10 @@
         <v>13</v>
       </c>
       <c r="C472" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D472" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.3">
@@ -10102,10 +10102,10 @@
         <v>13</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D473" s="5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.3">
@@ -10116,10 +10116,10 @@
         <v>13</v>
       </c>
       <c r="C474" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D474" s="5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.3">
@@ -10130,10 +10130,10 @@
         <v>13</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D475" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.3">
@@ -10144,10 +10144,10 @@
         <v>13</v>
       </c>
       <c r="C476" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D476" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.3">
@@ -10158,10 +10158,10 @@
         <v>13</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D477" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.3">
@@ -10172,10 +10172,10 @@
         <v>13</v>
       </c>
       <c r="C478" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D478" s="5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.3">
@@ -10186,10 +10186,10 @@
         <v>13</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D479" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.3">
@@ -10200,10 +10200,10 @@
         <v>13</v>
       </c>
       <c r="C480" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D480" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.3">
@@ -10214,10 +10214,10 @@
         <v>13</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D481" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.3">
@@ -10228,10 +10228,10 @@
         <v>13</v>
       </c>
       <c r="C482" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D482" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.3">
@@ -10242,10 +10242,10 @@
         <v>13</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D483" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.3">
@@ -10256,10 +10256,10 @@
         <v>13</v>
       </c>
       <c r="C484" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D484" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.3">
@@ -10270,10 +10270,10 @@
         <v>13</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D485" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.3">
@@ -10284,10 +10284,10 @@
         <v>13</v>
       </c>
       <c r="C486" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D486" s="5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.3">
@@ -10298,10 +10298,10 @@
         <v>13</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D487" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.3">
@@ -10312,10 +10312,10 @@
         <v>13</v>
       </c>
       <c r="C488" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D488" s="5" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.3">
@@ -10326,10 +10326,10 @@
         <v>13</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D489" s="5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.3">
@@ -10340,10 +10340,10 @@
         <v>13</v>
       </c>
       <c r="C490" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D490" s="5" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.3">
@@ -10354,10 +10354,10 @@
         <v>13</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D491" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.3">
@@ -10368,10 +10368,10 @@
         <v>13</v>
       </c>
       <c r="C492" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D492" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.3">
@@ -10382,10 +10382,10 @@
         <v>13</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D493" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.3">
@@ -10396,10 +10396,10 @@
         <v>13</v>
       </c>
       <c r="C494" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D494" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.3">
@@ -10410,10 +10410,10 @@
         <v>13</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D495" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.3">
@@ -10424,10 +10424,10 @@
         <v>13</v>
       </c>
       <c r="C496" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D496" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.3">
@@ -10438,10 +10438,10 @@
         <v>13</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D497" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.3">
@@ -10452,10 +10452,10 @@
         <v>13</v>
       </c>
       <c r="C498" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D498" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.3">
@@ -10466,10 +10466,10 @@
         <v>13</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D499" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.3">
@@ -10480,10 +10480,10 @@
         <v>13</v>
       </c>
       <c r="C500" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D500" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.3">
@@ -10494,10 +10494,10 @@
         <v>13</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D501" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.3">
@@ -10508,10 +10508,10 @@
         <v>13</v>
       </c>
       <c r="C502" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D502" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.3">
@@ -10522,10 +10522,10 @@
         <v>13</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D503" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.3">
@@ -10536,10 +10536,10 @@
         <v>13</v>
       </c>
       <c r="C504" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.3">
@@ -10550,10 +10550,10 @@
         <v>13</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D505" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.3">
@@ -10564,10 +10564,10 @@
         <v>13</v>
       </c>
       <c r="C506" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D506" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.3">
@@ -10578,10 +10578,10 @@
         <v>13</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D507" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.3">
@@ -10592,10 +10592,10 @@
         <v>13</v>
       </c>
       <c r="C508" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D508" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.3">
@@ -10606,10 +10606,10 @@
         <v>13</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D509" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.3">
@@ -10620,10 +10620,10 @@
         <v>13</v>
       </c>
       <c r="C510" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D510" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.3">
@@ -10634,10 +10634,10 @@
         <v>13</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D511" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.3">
@@ -10648,10 +10648,10 @@
         <v>13</v>
       </c>
       <c r="C512" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D512" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.3">
@@ -10662,24 +10662,24 @@
         <v>13</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D513" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A514" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C514" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D514" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.3">
@@ -10690,10 +10690,10 @@
         <v>13</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D515" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.3">
@@ -10704,10 +10704,10 @@
         <v>13</v>
       </c>
       <c r="C516" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D516" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.3">
@@ -10718,10 +10718,10 @@
         <v>13</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D517" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.3">
@@ -10732,10 +10732,10 @@
         <v>13</v>
       </c>
       <c r="C518" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D518" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.3">
@@ -10746,10 +10746,10 @@
         <v>13</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D519" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.3">
@@ -10760,10 +10760,10 @@
         <v>13</v>
       </c>
       <c r="C520" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D520" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.3">
@@ -10774,10 +10774,10 @@
         <v>13</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D521" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.3">
@@ -10788,10 +10788,10 @@
         <v>13</v>
       </c>
       <c r="C522" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D522" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.3">
@@ -10802,10 +10802,10 @@
         <v>13</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D523" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.3">
@@ -10816,10 +10816,10 @@
         <v>13</v>
       </c>
       <c r="C524" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D524" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.3">
@@ -10830,10 +10830,10 @@
         <v>13</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D525" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.3">
@@ -10844,10 +10844,10 @@
         <v>13</v>
       </c>
       <c r="C526" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D526" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.3">
@@ -10858,10 +10858,10 @@
         <v>13</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D527" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.3">
@@ -10872,10 +10872,10 @@
         <v>13</v>
       </c>
       <c r="C528" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D528" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.3">
@@ -10886,10 +10886,10 @@
         <v>13</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D529" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.3">
@@ -10900,10 +10900,10 @@
         <v>13</v>
       </c>
       <c r="C530" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D530" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.3">
@@ -10914,10 +10914,10 @@
         <v>13</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D531" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.3">
@@ -10928,10 +10928,10 @@
         <v>13</v>
       </c>
       <c r="C532" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="D532" s="5" t="s">
         <v>547</v>
-      </c>
-      <c r="D532" s="5" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.3">
@@ -10942,10 +10942,10 @@
         <v>13</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D533" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.3">
@@ -10956,10 +10956,10 @@
         <v>13</v>
       </c>
       <c r="C534" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D534" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.3">
@@ -10970,10 +10970,10 @@
         <v>13</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D535" s="38" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.3">
@@ -10984,10 +10984,10 @@
         <v>13</v>
       </c>
       <c r="C536" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D536" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.3">
@@ -10998,10 +10998,10 @@
         <v>13</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D537" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.3">
@@ -11012,10 +11012,10 @@
         <v>13</v>
       </c>
       <c r="C538" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D538" s="5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.3">
@@ -11026,10 +11026,10 @@
         <v>13</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D539" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.3">
@@ -11040,10 +11040,10 @@
         <v>13</v>
       </c>
       <c r="C540" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D540" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.3">
@@ -11054,10 +11054,10 @@
         <v>13</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D541" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.3">
@@ -11068,10 +11068,10 @@
         <v>13</v>
       </c>
       <c r="C542" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D542" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.3">
@@ -11082,10 +11082,10 @@
         <v>13</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D543" s="38" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.3">
@@ -11096,10 +11096,10 @@
         <v>13</v>
       </c>
       <c r="C544" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D544" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.3">
@@ -11110,10 +11110,10 @@
         <v>13</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D545" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.3">
@@ -11124,10 +11124,10 @@
         <v>13</v>
       </c>
       <c r="C546" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D546" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.3">
@@ -11138,10 +11138,10 @@
         <v>13</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D547" s="38" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.3">
@@ -11152,10 +11152,10 @@
         <v>13</v>
       </c>
       <c r="C548" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D548" s="5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.3">
@@ -11166,10 +11166,10 @@
         <v>13</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D549" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.3">
@@ -11180,10 +11180,10 @@
         <v>13</v>
       </c>
       <c r="C550" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D550" s="38" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.3">
@@ -11194,10 +11194,10 @@
         <v>13</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D551" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.3">
@@ -11208,10 +11208,10 @@
         <v>13</v>
       </c>
       <c r="C552" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D552" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.3">
@@ -11222,10 +11222,10 @@
         <v>13</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D553" s="29" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.3">
@@ -11236,10 +11236,10 @@
         <v>13</v>
       </c>
       <c r="C554" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D554" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.3">
@@ -11250,10 +11250,10 @@
         <v>13</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D555" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.3">
@@ -11264,10 +11264,10 @@
         <v>13</v>
       </c>
       <c r="C556" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D556" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.3">
@@ -11278,10 +11278,10 @@
         <v>13</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D557" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.3">
@@ -11292,10 +11292,10 @@
         <v>13</v>
       </c>
       <c r="C558" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D558" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.3">
@@ -11306,10 +11306,10 @@
         <v>13</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D559" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.3">
@@ -11320,10 +11320,10 @@
         <v>13</v>
       </c>
       <c r="C560" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D560" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.3">
@@ -11334,10 +11334,10 @@
         <v>13</v>
       </c>
       <c r="C561" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D561" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.3">
@@ -11348,24 +11348,24 @@
         <v>13</v>
       </c>
       <c r="C562" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D562" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B563" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D563" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.3">
@@ -11376,10 +11376,10 @@
         <v>13</v>
       </c>
       <c r="C564" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D564" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.3">
@@ -11390,10 +11390,10 @@
         <v>13</v>
       </c>
       <c r="C565" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D565" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.3">
@@ -11404,10 +11404,10 @@
         <v>13</v>
       </c>
       <c r="C566" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D566" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.3">
@@ -11418,10 +11418,10 @@
         <v>13</v>
       </c>
       <c r="C567" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D567" s="5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.3">
@@ -11432,24 +11432,24 @@
         <v>13</v>
       </c>
       <c r="C568" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D568" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B569" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C569" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D569" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.3">
@@ -11460,10 +11460,10 @@
         <v>13</v>
       </c>
       <c r="C570" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D570" s="5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.3">
@@ -11474,10 +11474,10 @@
         <v>13</v>
       </c>
       <c r="C571" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D571" s="5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.3">
@@ -11488,10 +11488,10 @@
         <v>13</v>
       </c>
       <c r="C572" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D572" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.3">
@@ -11502,10 +11502,10 @@
         <v>13</v>
       </c>
       <c r="C573" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D573" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.3">
@@ -11516,10 +11516,10 @@
         <v>13</v>
       </c>
       <c r="C574" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D574" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E574" s="5"/>
       <c r="F574" s="3"/>
@@ -11532,10 +11532,10 @@
         <v>13</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D575" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.3">
@@ -11546,10 +11546,10 @@
         <v>13</v>
       </c>
       <c r="C576" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D576" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.3">
@@ -11560,10 +11560,10 @@
         <v>13</v>
       </c>
       <c r="C577" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D577" s="5" t="s">
         <v>589</v>
-      </c>
-      <c r="D577" s="5" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.3">
@@ -11574,10 +11574,10 @@
         <v>13</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D578" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.3">
@@ -11588,10 +11588,10 @@
         <v>13</v>
       </c>
       <c r="C579" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D579" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.3">
@@ -11602,10 +11602,10 @@
         <v>13</v>
       </c>
       <c r="C580" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D580" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.3">
@@ -11616,10 +11616,10 @@
         <v>13</v>
       </c>
       <c r="C581" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D581" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.3">
@@ -11630,10 +11630,10 @@
         <v>13</v>
       </c>
       <c r="C582" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D582" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.3">
@@ -11644,10 +11644,10 @@
         <v>13</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D583" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.3">
@@ -11658,10 +11658,10 @@
         <v>13</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D584" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.3">
@@ -11672,10 +11672,10 @@
         <v>13</v>
       </c>
       <c r="C585" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D585" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.3">
@@ -11686,10 +11686,10 @@
         <v>13</v>
       </c>
       <c r="C586" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D586" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.3">
@@ -11700,10 +11700,10 @@
         <v>13</v>
       </c>
       <c r="C587" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D587" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.3">
@@ -11714,10 +11714,10 @@
         <v>13</v>
       </c>
       <c r="C588" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D588" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.3">
@@ -11728,10 +11728,10 @@
         <v>13</v>
       </c>
       <c r="C589" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D589" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.3">
@@ -11742,10 +11742,10 @@
         <v>13</v>
       </c>
       <c r="C590" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D590" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.3">
@@ -11756,10 +11756,10 @@
         <v>13</v>
       </c>
       <c r="C591" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D591" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.3">
@@ -11770,10 +11770,10 @@
         <v>13</v>
       </c>
       <c r="C592" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D592" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.3">
@@ -11784,10 +11784,10 @@
         <v>13</v>
       </c>
       <c r="C593" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D593" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.3">
@@ -11798,10 +11798,10 @@
         <v>13</v>
       </c>
       <c r="C594" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D594" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.3">
@@ -11812,10 +11812,10 @@
         <v>13</v>
       </c>
       <c r="C595" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D595" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.3">
@@ -11826,10 +11826,10 @@
         <v>13</v>
       </c>
       <c r="C596" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D596" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.3">
@@ -11840,10 +11840,10 @@
         <v>13</v>
       </c>
       <c r="C597" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D597" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.3">
@@ -11854,10 +11854,10 @@
         <v>13</v>
       </c>
       <c r="C598" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D598" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.3">
@@ -11868,10 +11868,10 @@
         <v>13</v>
       </c>
       <c r="C599" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D599" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.3">
@@ -11882,10 +11882,10 @@
         <v>13</v>
       </c>
       <c r="C600" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D600" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.3">
@@ -11896,10 +11896,10 @@
         <v>13</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D601" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.3">
@@ -11910,10 +11910,10 @@
         <v>13</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D602" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.3">
@@ -11924,10 +11924,10 @@
         <v>13</v>
       </c>
       <c r="C603" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D603" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.3">
@@ -11938,24 +11938,24 @@
         <v>13</v>
       </c>
       <c r="C604" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D604" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A605" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B605" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C605" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D605" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.3">
@@ -11966,10 +11966,10 @@
         <v>13</v>
       </c>
       <c r="C606" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D606" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.3">
@@ -11980,10 +11980,10 @@
         <v>13</v>
       </c>
       <c r="C607" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D607" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.3">
@@ -11994,10 +11994,10 @@
         <v>13</v>
       </c>
       <c r="C608" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D608" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.3">
@@ -12008,10 +12008,10 @@
         <v>13</v>
       </c>
       <c r="C609" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D609" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.3">
@@ -12022,10 +12022,10 @@
         <v>13</v>
       </c>
       <c r="C610" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D610" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.3">
@@ -12036,10 +12036,10 @@
         <v>13</v>
       </c>
       <c r="C611" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D611" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.3">
@@ -12050,10 +12050,10 @@
         <v>13</v>
       </c>
       <c r="C612" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D612" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.3">
@@ -12064,10 +12064,10 @@
         <v>13</v>
       </c>
       <c r="C613" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D613" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.3">
@@ -12078,10 +12078,10 @@
         <v>13</v>
       </c>
       <c r="C614" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D614" s="5" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.3">
@@ -12092,10 +12092,10 @@
         <v>13</v>
       </c>
       <c r="C615" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D615" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.3">
@@ -12106,10 +12106,10 @@
         <v>13</v>
       </c>
       <c r="C616" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D616" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.3">
@@ -12120,10 +12120,10 @@
         <v>13</v>
       </c>
       <c r="C617" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D617" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.3">
@@ -12134,10 +12134,10 @@
         <v>13</v>
       </c>
       <c r="C618" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D618" s="5" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.3">
@@ -12148,10 +12148,10 @@
         <v>13</v>
       </c>
       <c r="C619" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D619" s="5" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.3">
@@ -12162,10 +12162,10 @@
         <v>13</v>
       </c>
       <c r="C620" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D620" s="5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.3">
@@ -12176,10 +12176,10 @@
         <v>13</v>
       </c>
       <c r="C621" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D621" s="5" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.3">
@@ -12190,24 +12190,24 @@
         <v>13</v>
       </c>
       <c r="C622" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D622" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A623" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B623" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C623" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D623" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.3">
@@ -12218,10 +12218,10 @@
         <v>13</v>
       </c>
       <c r="C624" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D624" s="5" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.3">
@@ -12232,10 +12232,10 @@
         <v>13</v>
       </c>
       <c r="C625" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D625" s="5" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.3">
@@ -12246,10 +12246,10 @@
         <v>13</v>
       </c>
       <c r="C626" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D626" s="5" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.3">
@@ -12260,10 +12260,10 @@
         <v>13</v>
       </c>
       <c r="C627" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D627" s="5" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.3">
@@ -12274,10 +12274,10 @@
         <v>13</v>
       </c>
       <c r="C628" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D628" s="5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.3">
@@ -12288,24 +12288,24 @@
         <v>13</v>
       </c>
       <c r="C629" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D629" s="5" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A630" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B630" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C630" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D630" s="5" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.3">
@@ -12316,10 +12316,10 @@
         <v>13</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D631" s="5" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.3">
@@ -12330,10 +12330,10 @@
         <v>13</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D632" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.3">
@@ -12344,10 +12344,10 @@
         <v>13</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D633" s="5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.3">
@@ -12358,10 +12358,10 @@
         <v>13</v>
       </c>
       <c r="C634" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D634" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.3">
@@ -12372,10 +12372,10 @@
         <v>13</v>
       </c>
       <c r="C635" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D635" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.3">
@@ -12386,10 +12386,10 @@
         <v>13</v>
       </c>
       <c r="C636" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D636" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.3">
@@ -12400,10 +12400,10 @@
         <v>13</v>
       </c>
       <c r="C637" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D637" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.3">
@@ -12414,10 +12414,10 @@
         <v>13</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D638" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.3">
@@ -12428,10 +12428,10 @@
         <v>13</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D639" s="5" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.3">
@@ -12442,24 +12442,24 @@
         <v>13</v>
       </c>
       <c r="C640" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D640" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A641" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B641" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C641" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D641" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.3">
@@ -12470,10 +12470,10 @@
         <v>13</v>
       </c>
       <c r="C642" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D642" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.3">
@@ -12484,10 +12484,10 @@
         <v>13</v>
       </c>
       <c r="C643" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D643" s="5" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.3">
@@ -12498,10 +12498,10 @@
         <v>13</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D644" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.3">
@@ -12512,10 +12512,10 @@
         <v>13</v>
       </c>
       <c r="C645" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D645" s="5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.3">
@@ -12526,10 +12526,10 @@
         <v>13</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D646" s="5" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.3">
@@ -12540,10 +12540,10 @@
         <v>13</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D647" s="5" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.3">
@@ -12554,10 +12554,10 @@
         <v>13</v>
       </c>
       <c r="C648" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D648" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.3">
@@ -12568,10 +12568,10 @@
         <v>13</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D649" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.3">
@@ -12582,10 +12582,10 @@
         <v>13</v>
       </c>
       <c r="C650" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D650" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.3">
@@ -12596,10 +12596,10 @@
         <v>13</v>
       </c>
       <c r="C651" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D651" s="5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.3">
@@ -12610,71 +12610,71 @@
         <v>13</v>
       </c>
       <c r="C652" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D652" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A653" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B653" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C653" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D653" s="41" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A654" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B654" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C654" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D654" s="41" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A655" s="3" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B655" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C655" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D655" s="41" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A656" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B656" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C656" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D656" s="41" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A657" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B657" s="5" t="s">
         <v>13</v>
@@ -12683,12 +12683,12 @@
         <v>7</v>
       </c>
       <c r="D657" s="41" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A658" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B658" s="5" t="s">
         <v>13</v>
@@ -12697,12 +12697,12 @@
         <v>7</v>
       </c>
       <c r="D658" s="41" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A659" s="3" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B659" s="5" t="s">
         <v>13</v>
@@ -12711,12 +12711,12 @@
         <v>7</v>
       </c>
       <c r="D659" s="41" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A660" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B660" s="5" t="s">
         <v>13</v>
@@ -12725,12 +12725,12 @@
         <v>7</v>
       </c>
       <c r="D660" s="41" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A661" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B661" s="5" t="s">
         <v>13</v>
@@ -12739,12 +12739,12 @@
         <v>7</v>
       </c>
       <c r="D661" s="41" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A662" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B662" s="5" t="s">
         <v>13</v>
@@ -12753,12 +12753,12 @@
         <v>3</v>
       </c>
       <c r="D662" s="41" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A663" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B663" s="5" t="s">
         <v>13</v>
@@ -12767,12 +12767,12 @@
         <v>3</v>
       </c>
       <c r="D663" s="41" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A664" s="3" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B664" s="5" t="s">
         <v>13</v>
@@ -12781,12 +12781,12 @@
         <v>3</v>
       </c>
       <c r="D664" s="41" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A665" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B665" s="5" t="s">
         <v>13</v>
@@ -12795,12 +12795,12 @@
         <v>3</v>
       </c>
       <c r="D665" s="41" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A666" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B666" s="5" t="s">
         <v>13</v>
@@ -12809,12 +12809,12 @@
         <v>3</v>
       </c>
       <c r="D666" s="41" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A667" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B667" s="5" t="s">
         <v>13</v>
@@ -12823,12 +12823,12 @@
         <v>6</v>
       </c>
       <c r="D667" s="41" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A668" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B668" s="5" t="s">
         <v>13</v>
@@ -12837,12 +12837,12 @@
         <v>6</v>
       </c>
       <c r="D668" s="41" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A669" s="3" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B669" s="5" t="s">
         <v>13</v>
@@ -12851,12 +12851,12 @@
         <v>6</v>
       </c>
       <c r="D669" s="41" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A670" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B670" s="5" t="s">
         <v>13</v>
@@ -12865,12 +12865,12 @@
         <v>6</v>
       </c>
       <c r="D670" s="41" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A671" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B671" s="5" t="s">
         <v>13</v>
@@ -12879,77 +12879,77 @@
         <v>6</v>
       </c>
       <c r="D671" s="41" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A672" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B672" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C672" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D672" s="41" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A673" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B673" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C673" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D673" s="41" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A674" s="3" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B674" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C674" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D674" s="41" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A675" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B675" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C675" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D675" s="41" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A676" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B676" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C676" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D676" s="41" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
   </sheetData>
@@ -12979,49 +12979,48 @@
     <hyperlink ref="D239" r:id="rId22" xr:uid="{A7422901-C06E-4C23-86DE-D8AA4B770790}"/>
     <hyperlink ref="D240" r:id="rId23" xr:uid="{2549C4AC-9E11-474B-9F13-88A64AB6C362}"/>
     <hyperlink ref="D241" r:id="rId24" xr:uid="{956FA391-EB25-446D-9BF0-DB5F64A35E23}"/>
-    <hyperlink ref="D242" r:id="rId25" xr:uid="{9F0D64C6-7CDE-413E-9751-85BC785672F5}"/>
-    <hyperlink ref="D243" r:id="rId26" xr:uid="{91B1600E-DAD8-407A-98B6-BC6B5CA9C9A1}"/>
-    <hyperlink ref="D245" r:id="rId27" xr:uid="{3E449701-76E3-4327-9020-0711999EB14C}"/>
-    <hyperlink ref="D246" r:id="rId28" xr:uid="{2B276713-F3EB-42D8-94D5-D9977968F7C4}"/>
-    <hyperlink ref="D247" r:id="rId29" xr:uid="{86C35BF4-AA8E-4BF2-BB37-EF8A81B144A3}"/>
-    <hyperlink ref="D248" r:id="rId30" xr:uid="{575D790A-9F52-44E0-8812-1980455ACE6A}"/>
-    <hyperlink ref="D249" r:id="rId31" xr:uid="{05C515B5-1482-41BB-86B9-060CD8D86F6E}"/>
-    <hyperlink ref="D250" r:id="rId32" xr:uid="{A30C116F-9578-4A2D-84E1-349C7446B424}"/>
-    <hyperlink ref="D252" r:id="rId33" xr:uid="{17AECA23-51FA-4BAE-A59E-6F34376DFE92}"/>
-    <hyperlink ref="D258" r:id="rId34" xr:uid="{0EA52F71-8E7C-4988-AAF9-621EAD622EA3}"/>
-    <hyperlink ref="D259" r:id="rId35" xr:uid="{D86454B1-84CD-47DD-BC73-90DE2BBC47C0}"/>
-    <hyperlink ref="D260" r:id="rId36" xr:uid="{3F07E478-3C33-40D2-BF88-AEAD6F04698C}"/>
-    <hyperlink ref="D261" r:id="rId37" xr:uid="{A0594C39-A2DA-4A0E-9158-2333E42E241B}"/>
-    <hyperlink ref="D266" r:id="rId38" xr:uid="{ED4D3ED7-DF97-425D-969C-390D73FDDFCD}"/>
-    <hyperlink ref="D273" r:id="rId39" xr:uid="{DF4AD067-6E4A-4A82-8EC4-EE39679B07B1}"/>
-    <hyperlink ref="D276" r:id="rId40" xr:uid="{4D60D4AF-B7D3-4738-96EC-015D106234CD}"/>
-    <hyperlink ref="D281" r:id="rId41" xr:uid="{717469E5-08C7-4B50-AC06-F99668F52706}"/>
-    <hyperlink ref="D282" r:id="rId42" xr:uid="{6528A4D6-A50A-4E13-A2BF-B645EEBA60E4}"/>
-    <hyperlink ref="D285" r:id="rId43" xr:uid="{3A8D2F0D-ED66-4F1D-9AA6-7C84EB8A8F6A}"/>
-    <hyperlink ref="D287" r:id="rId44" xr:uid="{D051ED50-D6DB-48AE-86FE-CC70600AE69E}"/>
-    <hyperlink ref="D288" r:id="rId45" xr:uid="{EF0B74E7-DE2D-4CC9-8DAE-48F5D13BEE2E}"/>
-    <hyperlink ref="D286" r:id="rId46" xr:uid="{73E0CFC3-4342-4344-85F1-526579F3A429}"/>
-    <hyperlink ref="D289" r:id="rId47" xr:uid="{E00CE8EE-85DE-48A0-8002-C8BE18B96D70}"/>
-    <hyperlink ref="D290" r:id="rId48" xr:uid="{5F265E2C-4238-47E7-8069-5342A1912C59}"/>
-    <hyperlink ref="D291" r:id="rId49" xr:uid="{6A59EC90-1106-40B7-9AF7-08E2E9C0592C}"/>
-    <hyperlink ref="D292" r:id="rId50" xr:uid="{760E1B9E-8178-4807-8281-E3719799882C}"/>
-    <hyperlink ref="D278" r:id="rId51" xr:uid="{0D74648B-9A00-4261-A628-6A92A024DD1D}"/>
-    <hyperlink ref="D391" r:id="rId52" xr:uid="{DE0EAE0D-94D1-44E6-9100-BB86FBDDC6A7}"/>
-    <hyperlink ref="D547" r:id="rId53" xr:uid="{37E52712-D7EB-4125-871E-21725163FA4B}"/>
-    <hyperlink ref="D550" r:id="rId54" xr:uid="{E6455D81-4205-46DC-9D19-8D489A6C5901}"/>
-    <hyperlink ref="D543" r:id="rId55" xr:uid="{76D2BC15-F744-4E8E-95A6-CF6BE6D1712C}"/>
-    <hyperlink ref="D125" r:id="rId56" xr:uid="{2827ABD4-F3DC-4FBC-B59A-C8AF33AB5EAA}"/>
-    <hyperlink ref="D123" r:id="rId57" xr:uid="{80EEF2F5-2F23-4405-A739-DECF3450E89E}"/>
-    <hyperlink ref="D253" r:id="rId58" xr:uid="{F710E7AE-9855-40D1-8B4C-7F5F4983EB3A}"/>
-    <hyperlink ref="D265" r:id="rId59" xr:uid="{92DA10B3-6314-4824-BBFD-ED5868E98172}"/>
-    <hyperlink ref="D271" r:id="rId60" xr:uid="{0BA47127-40E1-436D-B847-1B45CFF2DD7B}"/>
-    <hyperlink ref="D153" r:id="rId61" xr:uid="{76383898-9E45-485C-B54A-7FBB5FAC78BF}"/>
-    <hyperlink ref="D274" r:id="rId62" xr:uid="{1BF81695-302B-4272-A37F-B1F82DFCC864}"/>
-    <hyperlink ref="D126" r:id="rId63" xr:uid="{B798115A-2494-40DA-9647-3F9D20A7DD75}"/>
-    <hyperlink ref="D131" r:id="rId64" xr:uid="{C601D573-7598-460B-96F9-1A1FA18576D2}"/>
-    <hyperlink ref="D132" r:id="rId65" xr:uid="{15EA25BC-1188-4E7B-9977-31DE4FE4EE9A}"/>
+    <hyperlink ref="D243" r:id="rId25" xr:uid="{91B1600E-DAD8-407A-98B6-BC6B5CA9C9A1}"/>
+    <hyperlink ref="D245" r:id="rId26" xr:uid="{3E449701-76E3-4327-9020-0711999EB14C}"/>
+    <hyperlink ref="D246" r:id="rId27" xr:uid="{2B276713-F3EB-42D8-94D5-D9977968F7C4}"/>
+    <hyperlink ref="D247" r:id="rId28" xr:uid="{86C35BF4-AA8E-4BF2-BB37-EF8A81B144A3}"/>
+    <hyperlink ref="D248" r:id="rId29" xr:uid="{575D790A-9F52-44E0-8812-1980455ACE6A}"/>
+    <hyperlink ref="D249" r:id="rId30" xr:uid="{05C515B5-1482-41BB-86B9-060CD8D86F6E}"/>
+    <hyperlink ref="D250" r:id="rId31" xr:uid="{A30C116F-9578-4A2D-84E1-349C7446B424}"/>
+    <hyperlink ref="D252" r:id="rId32" xr:uid="{17AECA23-51FA-4BAE-A59E-6F34376DFE92}"/>
+    <hyperlink ref="D258" r:id="rId33" xr:uid="{0EA52F71-8E7C-4988-AAF9-621EAD622EA3}"/>
+    <hyperlink ref="D259" r:id="rId34" xr:uid="{D86454B1-84CD-47DD-BC73-90DE2BBC47C0}"/>
+    <hyperlink ref="D260" r:id="rId35" xr:uid="{3F07E478-3C33-40D2-BF88-AEAD6F04698C}"/>
+    <hyperlink ref="D261" r:id="rId36" xr:uid="{A0594C39-A2DA-4A0E-9158-2333E42E241B}"/>
+    <hyperlink ref="D266" r:id="rId37" xr:uid="{ED4D3ED7-DF97-425D-969C-390D73FDDFCD}"/>
+    <hyperlink ref="D273" r:id="rId38" xr:uid="{DF4AD067-6E4A-4A82-8EC4-EE39679B07B1}"/>
+    <hyperlink ref="D276" r:id="rId39" xr:uid="{4D60D4AF-B7D3-4738-96EC-015D106234CD}"/>
+    <hyperlink ref="D281" r:id="rId40" xr:uid="{717469E5-08C7-4B50-AC06-F99668F52706}"/>
+    <hyperlink ref="D282" r:id="rId41" xr:uid="{6528A4D6-A50A-4E13-A2BF-B645EEBA60E4}"/>
+    <hyperlink ref="D285" r:id="rId42" xr:uid="{3A8D2F0D-ED66-4F1D-9AA6-7C84EB8A8F6A}"/>
+    <hyperlink ref="D287" r:id="rId43" xr:uid="{D051ED50-D6DB-48AE-86FE-CC70600AE69E}"/>
+    <hyperlink ref="D288" r:id="rId44" xr:uid="{EF0B74E7-DE2D-4CC9-8DAE-48F5D13BEE2E}"/>
+    <hyperlink ref="D286" r:id="rId45" xr:uid="{73E0CFC3-4342-4344-85F1-526579F3A429}"/>
+    <hyperlink ref="D289" r:id="rId46" xr:uid="{E00CE8EE-85DE-48A0-8002-C8BE18B96D70}"/>
+    <hyperlink ref="D290" r:id="rId47" xr:uid="{5F265E2C-4238-47E7-8069-5342A1912C59}"/>
+    <hyperlink ref="D291" r:id="rId48" xr:uid="{6A59EC90-1106-40B7-9AF7-08E2E9C0592C}"/>
+    <hyperlink ref="D292" r:id="rId49" xr:uid="{760E1B9E-8178-4807-8281-E3719799882C}"/>
+    <hyperlink ref="D278" r:id="rId50" xr:uid="{0D74648B-9A00-4261-A628-6A92A024DD1D}"/>
+    <hyperlink ref="D391" r:id="rId51" xr:uid="{DE0EAE0D-94D1-44E6-9100-BB86FBDDC6A7}"/>
+    <hyperlink ref="D547" r:id="rId52" xr:uid="{37E52712-D7EB-4125-871E-21725163FA4B}"/>
+    <hyperlink ref="D550" r:id="rId53" xr:uid="{E6455D81-4205-46DC-9D19-8D489A6C5901}"/>
+    <hyperlink ref="D543" r:id="rId54" xr:uid="{76D2BC15-F744-4E8E-95A6-CF6BE6D1712C}"/>
+    <hyperlink ref="D125" r:id="rId55" xr:uid="{2827ABD4-F3DC-4FBC-B59A-C8AF33AB5EAA}"/>
+    <hyperlink ref="D123" r:id="rId56" xr:uid="{80EEF2F5-2F23-4405-A739-DECF3450E89E}"/>
+    <hyperlink ref="D253" r:id="rId57" xr:uid="{F710E7AE-9855-40D1-8B4C-7F5F4983EB3A}"/>
+    <hyperlink ref="D265" r:id="rId58" xr:uid="{92DA10B3-6314-4824-BBFD-ED5868E98172}"/>
+    <hyperlink ref="D271" r:id="rId59" xr:uid="{0BA47127-40E1-436D-B847-1B45CFF2DD7B}"/>
+    <hyperlink ref="D153" r:id="rId60" xr:uid="{76383898-9E45-485C-B54A-7FBB5FAC78BF}"/>
+    <hyperlink ref="D274" r:id="rId61" xr:uid="{1BF81695-302B-4272-A37F-B1F82DFCC864}"/>
+    <hyperlink ref="D126" r:id="rId62" xr:uid="{B798115A-2494-40DA-9647-3F9D20A7DD75}"/>
+    <hyperlink ref="D131" r:id="rId63" xr:uid="{C601D573-7598-460B-96F9-1A1FA18576D2}"/>
+    <hyperlink ref="D132" r:id="rId64" xr:uid="{15EA25BC-1188-4E7B-9977-31DE4FE4EE9A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId66"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId65"/>
 </worksheet>
 </file>
--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMSIERRA\Documents\ISDIN_Shopping_de_precios\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B9B3C0-7256-407C-9BFB-D7E5E4C512BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EFF4E1-9A64-4EAD-AF65-0D75E7F3D9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{60233B49-B589-B346-B71C-4D486694C55A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$676</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$682</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2704" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2728" uniqueCount="793">
   <si>
     <t>Producto</t>
   </si>
@@ -2400,6 +2400,24 @@
   </si>
   <si>
     <t>https://lineaestetica.co/product/isdin-instant-flash-efecto-lifting/?attribute_pa_unidades=1-ampolla</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdin-coverage-1-0-pearl?_pos=2&amp;_psq=COVERAGE&amp;_ss=e&amp;_v=1.0</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdin-coverage-2-0-beige?_pos=1&amp;_psq=COVERAGE&amp;_ss=e&amp;_v=2.0</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/cicapost-crema-50-gr-isdin?_pos=2&amp;_psq=cica&amp;_ss=e&amp;_v=1.0</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdin-coverage-3-0-sand?_pos=1&amp;_psq=COVERAGE&amp;_ss=e&amp;_v=1.0</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdin-coverage-4-0-golden?_pos=1&amp;_psq=COVERAGE&amp;_ss=e&amp;_v=3.0</t>
+  </si>
+  <si>
+    <t>https://laskin.com.co/products/isdin-coverage-5-0-bronze?_pos=1&amp;_psq=COVERAGE&amp;_ss=e&amp;_v=3.0</t>
   </si>
 </sst>
 </file>
@@ -2578,7 +2596,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2628,6 +2646,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="6" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2958,7 +2979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C4ECE9E-4A28-6340-B936-CE442F4057E5}">
-  <dimension ref="A1:M676"/>
+  <dimension ref="A1:M682"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="62.3984375" customWidth="1"/>
@@ -12952,7 +12973,92 @@
         <v>763</v>
       </c>
     </row>
+    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A677" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="B677" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C677" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="D677" s="41" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A678" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="B678" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C678" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="D678" s="41" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A679" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="B679" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C679" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="D679" s="43" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A680" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="B680" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C680" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="D680" s="43" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A681" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="B681" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C681" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="D681" s="43" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A682" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B682" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C682" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="D682" s="41" t="s">
+        <v>789</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D682" xr:uid="{2C4ECE9E-4A28-6340-B936-CE442F4057E5}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D638" r:id="rId1" xr:uid="{C4A764D9-65E4-467B-BC7B-5C3E51C52CDA}"/>
@@ -13019,8 +13125,11 @@
     <hyperlink ref="D126" r:id="rId62" xr:uid="{B798115A-2494-40DA-9647-3F9D20A7DD75}"/>
     <hyperlink ref="D131" r:id="rId63" xr:uid="{C601D573-7598-460B-96F9-1A1FA18576D2}"/>
     <hyperlink ref="D132" r:id="rId64" xr:uid="{15EA25BC-1188-4E7B-9977-31DE4FE4EE9A}"/>
+    <hyperlink ref="D679" r:id="rId65" xr:uid="{96BA4FB7-0FCC-4C86-BE00-F7E6F4184E7D}"/>
+    <hyperlink ref="D680" r:id="rId66" xr:uid="{FC45698F-DD69-42C9-B450-C81797AA090B}"/>
+    <hyperlink ref="D681" r:id="rId67" xr:uid="{61D7CAA3-790C-47E0-9A37-6C45A4481FA1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId65"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId68"/>
 </worksheet>
 </file>